--- a/قائمة_المقررات_التخصصية_المفقودة_2026-09-10.xlsx
+++ b/قائمة_المقررات_التخصصية_المفقودة_2026-09-10.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الملخص" sheetId="1" r:id="R213e201e4d474ca3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المقررات المفقودة" sheetId="2" r:id="R9c36fe1ea9ee44ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مواضع الخطط" sheetId="3" r:id="Rf798283626e246c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الملخص" sheetId="1" r:id="R543ef7c7721a491d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المقررات المفقودة" sheetId="2" r:id="Rfbc63b27ce4042e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مواضع الخطط" sheetId="3" r:id="R6b82ed7f74454a9a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -254,7 +254,7 @@
         <x:color rgb="FF8A5800"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF1C7"/>
         </x:patternFill>
       </x:fill>
@@ -264,7 +264,7 @@
         <x:color rgb="FF24613D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE5F3EA"/>
         </x:patternFill>
       </x:fill>
@@ -274,7 +274,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MissingCourseIdentities" displayName="MissingCourseIdentities" ref="A5:L111" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="MissingCourseIdentities" displayName="MissingCourseIdentities" ref="A5:L106" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="م"/>
     <x:tableColumn id="2" name="رمز المقرر"/>
@@ -294,7 +294,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MissingCourseOccurrences" displayName="MissingCourseOccurrences" ref="A5:O145" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="MissingCourseOccurrences" displayName="MissingCourseOccurrences" ref="A5:O136" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="15">
     <x:tableColumn id="1" name="م"/>
     <x:tableColumn id="2" name="البرنامج"/>
@@ -622,19 +622,16 @@
         <x:v>194</x:v>
       </x:c>
       <x:c r="E7" s="30" t="n">
-        <x:f>D7-F7</x:f>
-        <x:v>158</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="F7" s="30" t="n">
-        <x:f>COUNTIFS('مواضع الخطط'!$B$6:$B$145,A7,'مواضع الخطط'!$C$6:$C$145,B7)</x:f>
-        <x:v>36</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G7" s="36" t="n">
-        <x:f>E7/D7</x:f>
-        <x:v>0.8144329896907216</x:v>
+        <x:v>0.8556701030927835</x:v>
       </x:c>
       <x:c r="H7" s="30" t="n">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="33" t="str">
         <x:f>IF(F7=0,"مكتمل","يحتاج استكمال")</x:f>
@@ -787,19 +784,16 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="E12" s="30" t="n">
-        <x:f>D12-F12</x:f>
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F12" s="30" t="n">
-        <x:f>COUNTIFS('مواضع الخطط'!$B$6:$B$145,A12,'مواضع الخطط'!$C$6:$C$145,B12)</x:f>
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G12" s="36" t="n">
-        <x:f>E12/D12</x:f>
-        <x:v>0.7637795275590551</x:v>
+        <x:v>0.7716535433070866</x:v>
       </x:c>
       <x:c r="H12" s="30" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I12" s="33" t="str">
         <x:f>IF(F12=0,"مكتمل","يحتاج استكمال")</x:f>
@@ -1081,19 +1075,16 @@
         <x:v>756</x:v>
       </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:f>SUM(E6:E20)</x:f>
-        <x:v>616</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="F21" s="31" t="n">
-        <x:f>SUM(F6:F20)</x:f>
-        <x:v>140</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G21" s="37" t="n">
-        <x:f>E21/D21</x:f>
-        <x:v>0.8148148148148148</x:v>
+        <x:v>0.8267195767195767</x:v>
       </x:c>
       <x:c r="H21" s="31" t="n">
-        <x:v>106</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="I21" s="34" t="str">
         <x:v>قائمة العمل الحالية</x:v>
@@ -1145,7 +1136,7 @@
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
       <x:c r="A3" s="6" t="str">
-        <x:v>عدد الهويات الفريدة: 106. قد يظهر المقرر نفسه في أكثر من برنامج أو خطة، وتوضح الأعمدة جميع المواضع المتأثرة.</x:v>
+        <x:v>عدد الهويات الفريدة: 101. قد يظهر المقرر نفسه في أكثر من برنامج أو خطة، وتوضح الأعمدة جميع المواضع المتأثرة.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1228,7 +1219,7 @@
       <x:c r="I6" s="38" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J6" s="38" t="str"/>
+      <x:c r="J6" s="38"/>
       <x:c r="K6" s="38" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -1264,7 +1255,7 @@
       <x:c r="I7" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J7" s="39" t="str"/>
+      <x:c r="J7" s="39"/>
       <x:c r="K7" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -1300,7 +1291,7 @@
       <x:c r="I8" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J8" s="39" t="str"/>
+      <x:c r="J8" s="39"/>
       <x:c r="K8" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -1336,7 +1327,7 @@
       <x:c r="I9" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J9" s="39" t="str"/>
+      <x:c r="J9" s="39"/>
       <x:c r="K9" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -1374,7 +1365,7 @@
       <x:c r="I10" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J10" s="39" t="str"/>
+      <x:c r="J10" s="39"/>
       <x:c r="K10" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -1410,7 +1401,7 @@
       <x:c r="I11" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J11" s="39" t="str"/>
+      <x:c r="J11" s="39"/>
       <x:c r="K11" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -1446,7 +1437,7 @@
       <x:c r="I12" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J12" s="39" t="str"/>
+      <x:c r="J12" s="39"/>
       <x:c r="K12" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -1482,7 +1473,7 @@
       <x:c r="I13" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J13" s="39" t="str"/>
+      <x:c r="J13" s="39"/>
       <x:c r="K13" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -1518,7 +1509,7 @@
       <x:c r="I14" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J14" s="39" t="str"/>
+      <x:c r="J14" s="39"/>
       <x:c r="K14" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -1556,7 +1547,7 @@
       <x:c r="I15" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J15" s="39" t="str"/>
+      <x:c r="J15" s="39"/>
       <x:c r="K15" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -1592,7 +1583,7 @@
       <x:c r="I16" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J16" s="39" t="str"/>
+      <x:c r="J16" s="39"/>
       <x:c r="K16" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -1628,7 +1619,7 @@
       <x:c r="I17" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J17" s="39" t="str"/>
+      <x:c r="J17" s="39"/>
       <x:c r="K17" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -1664,7 +1655,7 @@
       <x:c r="I18" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J18" s="39" t="str"/>
+      <x:c r="J18" s="39"/>
       <x:c r="K18" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -1700,7 +1691,7 @@
       <x:c r="I19" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J19" s="39" t="str"/>
+      <x:c r="J19" s="39"/>
       <x:c r="K19" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -1736,7 +1727,7 @@
       <x:c r="I20" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J20" s="39" t="str"/>
+      <x:c r="J20" s="39"/>
       <x:c r="K20" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -1772,7 +1763,7 @@
       <x:c r="I21" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J21" s="39" t="str"/>
+      <x:c r="J21" s="39"/>
       <x:c r="K21" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -1808,7 +1799,7 @@
       <x:c r="I22" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J22" s="39" t="str"/>
+      <x:c r="J22" s="39"/>
       <x:c r="K22" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -1844,7 +1835,7 @@
       <x:c r="I23" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J23" s="39" t="str"/>
+      <x:c r="J23" s="39"/>
       <x:c r="K23" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -1880,7 +1871,7 @@
       <x:c r="I24" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J24" s="39" t="str"/>
+      <x:c r="J24" s="39"/>
       <x:c r="K24" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -1916,7 +1907,7 @@
       <x:c r="I25" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J25" s="39" t="str"/>
+      <x:c r="J25" s="39"/>
       <x:c r="K25" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -1952,7 +1943,7 @@
       <x:c r="I26" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J26" s="39" t="str"/>
+      <x:c r="J26" s="39"/>
       <x:c r="K26" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -1988,7 +1979,7 @@
       <x:c r="I27" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J27" s="39" t="str"/>
+      <x:c r="J27" s="39"/>
       <x:c r="K27" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -2024,7 +2015,7 @@
       <x:c r="I28" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J28" s="39" t="str"/>
+      <x:c r="J28" s="39"/>
       <x:c r="K28" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -2060,7 +2051,7 @@
       <x:c r="I29" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J29" s="39" t="str"/>
+      <x:c r="J29" s="39"/>
       <x:c r="K29" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -2096,7 +2087,7 @@
       <x:c r="I30" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J30" s="39" t="str"/>
+      <x:c r="J30" s="39"/>
       <x:c r="K30" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -2132,7 +2123,7 @@
       <x:c r="I31" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J31" s="39" t="str"/>
+      <x:c r="J31" s="39"/>
       <x:c r="K31" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -2168,7 +2159,7 @@
       <x:c r="I32" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J32" s="39" t="str"/>
+      <x:c r="J32" s="39"/>
       <x:c r="K32" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -2204,7 +2195,7 @@
       <x:c r="I33" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J33" s="39" t="str"/>
+      <x:c r="J33" s="39"/>
       <x:c r="K33" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -2240,7 +2231,7 @@
       <x:c r="I34" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J34" s="39" t="str"/>
+      <x:c r="J34" s="39"/>
       <x:c r="K34" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -2276,7 +2267,7 @@
       <x:c r="I35" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J35" s="39" t="str"/>
+      <x:c r="J35" s="39"/>
       <x:c r="K35" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
@@ -2289,10 +2280,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B36" s="33" t="str">
-        <x:v>2002202-2</x:v>
+        <x:v>2002228-2</x:v>
       </x:c>
       <x:c r="C36" s="39" t="str">
-        <x:v>القرآن الكريم (2)</x:v>
+        <x:v>القرآن الكريم (٥)</x:v>
       </x:c>
       <x:c r="D36" s="39" t="str">
         <x:v>الدراسات الإسلامية</x:v>
@@ -2304,7 +2295,7 @@
         <x:v>الدراسات الإسلامية: جديدة 47</x:v>
       </x:c>
       <x:c r="G36" s="39" t="str">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H36" s="39" t="n">
         <x:v>1</x:v>
@@ -2312,12 +2303,12 @@
       <x:c r="I36" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J36" s="39" t="str"/>
+      <x:c r="J36" s="39"/>
       <x:c r="K36" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L36" s="39" t="str">
-        <x:v>2002202-2||القرانالكريم2</x:v>
+        <x:v>2002228-2||القرانالكريم٥</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="42" customHeight="1">
@@ -2325,10 +2316,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B37" s="33" t="str">
-        <x:v>2002228-2</x:v>
+        <x:v>2002229-2</x:v>
       </x:c>
       <x:c r="C37" s="39" t="str">
-        <x:v>القرآن الكريم (٥)</x:v>
+        <x:v>القرآن الكريم (٦)</x:v>
       </x:c>
       <x:c r="D37" s="39" t="str">
         <x:v>الدراسات الإسلامية</x:v>
@@ -2340,7 +2331,7 @@
         <x:v>الدراسات الإسلامية: جديدة 47</x:v>
       </x:c>
       <x:c r="G37" s="39" t="str">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H37" s="39" t="n">
         <x:v>1</x:v>
@@ -2348,12 +2339,12 @@
       <x:c r="I37" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J37" s="39" t="str"/>
+      <x:c r="J37" s="39"/>
       <x:c r="K37" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L37" s="39" t="str">
-        <x:v>2002228-2||القرانالكريم٥</x:v>
+        <x:v>2002229-2||القرانالكريم٦</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="42" customHeight="1">
@@ -2361,10 +2352,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B38" s="33" t="str">
-        <x:v>2002229-2</x:v>
+        <x:v>2002236-2</x:v>
       </x:c>
       <x:c r="C38" s="39" t="str">
-        <x:v>القرآن الكريم (٦)</x:v>
+        <x:v>القرآن الكريم (٨)</x:v>
       </x:c>
       <x:c r="D38" s="39" t="str">
         <x:v>الدراسات الإسلامية</x:v>
@@ -2376,7 +2367,7 @@
         <x:v>الدراسات الإسلامية: جديدة 47</x:v>
       </x:c>
       <x:c r="G38" s="39" t="str">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H38" s="39" t="n">
         <x:v>1</x:v>
@@ -2384,12 +2375,12 @@
       <x:c r="I38" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J38" s="39" t="str"/>
+      <x:c r="J38" s="39"/>
       <x:c r="K38" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L38" s="39" t="str">
-        <x:v>2002229-2||القرانالكريم٦</x:v>
+        <x:v>2002236-2||القرانالكريم٨</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="42" customHeight="1">
@@ -2397,10 +2388,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B39" s="33" t="str">
-        <x:v>2002236-2</x:v>
+        <x:v>2002310-3</x:v>
       </x:c>
       <x:c r="C39" s="39" t="str">
-        <x:v>القرآن الكريم (٨)</x:v>
+        <x:v>التفسير التحليلي (٣)</x:v>
       </x:c>
       <x:c r="D39" s="39" t="str">
         <x:v>الدراسات الإسلامية</x:v>
@@ -2412,7 +2403,7 @@
         <x:v>الدراسات الإسلامية: جديدة 47</x:v>
       </x:c>
       <x:c r="G39" s="39" t="str">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H39" s="39" t="n">
         <x:v>1</x:v>
@@ -2420,12 +2411,12 @@
       <x:c r="I39" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J39" s="39" t="str"/>
+      <x:c r="J39" s="39"/>
       <x:c r="K39" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L39" s="39" t="str">
-        <x:v>2002236-2||القرانالكريم٨</x:v>
+        <x:v>2002310-3||التفسيرالتحليلي٣</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="42" customHeight="1">
@@ -2433,35 +2424,37 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B40" s="33" t="str">
-        <x:v>2002310-3</x:v>
+        <x:v>2003220-2</x:v>
       </x:c>
       <x:c r="C40" s="39" t="str">
-        <x:v>التفسير التحليلي (٣)</x:v>
+        <x:v>المدخل لدراسة الأنظمة</x:v>
       </x:c>
       <x:c r="D40" s="39" t="str">
-        <x:v>الدراسات الإسلامية</x:v>
+        <x:v>الدراسات الإسلامية، القرآن وعلومه</x:v>
       </x:c>
       <x:c r="E40" s="39" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F40" s="39" t="str">
-        <x:v>الدراسات الإسلامية: جديدة 47</x:v>
+        <x:v>الدراسات الإسلامية: قديمة 39
+القرآن وعلومه: جديدة 47
+القرآن وعلومه: قديمة 39</x:v>
       </x:c>
       <x:c r="G40" s="39" t="str">
-        <x:v>6</x:v>
+        <x:v>3، 4</x:v>
       </x:c>
       <x:c r="H40" s="39" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I40" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J40" s="39" t="str"/>
+      <x:c r="J40" s="39"/>
       <x:c r="K40" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L40" s="39" t="str">
-        <x:v>2002310-3||التفسيرالتحليلي٣</x:v>
+        <x:v>2003220-2||المدخللدراسةالانظمة</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="42" customHeight="1">
@@ -2469,37 +2462,35 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B41" s="33" t="str">
-        <x:v>2003220-2</x:v>
+        <x:v>2004211-4</x:v>
       </x:c>
       <x:c r="C41" s="39" t="str">
-        <x:v>المدخل لدراسة الأنظمة</x:v>
+        <x:v>العقيدة (1)</x:v>
       </x:c>
       <x:c r="D41" s="39" t="str">
-        <x:v>الدراسات الإسلامية، القرآن وعلومه</x:v>
+        <x:v>الدراسات الإسلامية</x:v>
       </x:c>
       <x:c r="E41" s="39" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F41" s="39" t="str">
-        <x:v>الدراسات الإسلامية: قديمة 39
-القرآن وعلومه: جديدة 47
-القرآن وعلومه: قديمة 39</x:v>
+        <x:v>الدراسات الإسلامية: جديدة 47</x:v>
       </x:c>
       <x:c r="G41" s="39" t="str">
-        <x:v>3، 4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H41" s="39" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I41" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J41" s="39" t="str"/>
+      <x:c r="J41" s="39"/>
       <x:c r="K41" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L41" s="39" t="str">
-        <x:v>2003220-2||المدخللدراسةالانظمة</x:v>
+        <x:v>2004211-4||العقيدة1</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="42" customHeight="1">
@@ -2507,10 +2498,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B42" s="33" t="str">
-        <x:v>2004211-4</x:v>
+        <x:v>2004252-4</x:v>
       </x:c>
       <x:c r="C42" s="39" t="str">
-        <x:v>العقيدة (1)</x:v>
+        <x:v>الحديث التحليلي (1)</x:v>
       </x:c>
       <x:c r="D42" s="39" t="str">
         <x:v>الدراسات الإسلامية</x:v>
@@ -2522,7 +2513,7 @@
         <x:v>الدراسات الإسلامية: جديدة 47</x:v>
       </x:c>
       <x:c r="G42" s="39" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H42" s="39" t="n">
         <x:v>1</x:v>
@@ -2530,12 +2521,12 @@
       <x:c r="I42" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J42" s="39" t="str"/>
+      <x:c r="J42" s="39"/>
       <x:c r="K42" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L42" s="39" t="str">
-        <x:v>2004211-4||العقيدة1</x:v>
+        <x:v>2004252-4||الحديثالتحليلي1</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="42" customHeight="1">
@@ -2543,10 +2534,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B43" s="33" t="str">
-        <x:v>2004252-4</x:v>
+        <x:v>2004256-2</x:v>
       </x:c>
       <x:c r="C43" s="39" t="str">
-        <x:v>الحديث التحليلي (1)</x:v>
+        <x:v>الحديث التحليلي (٢)</x:v>
       </x:c>
       <x:c r="D43" s="39" t="str">
         <x:v>الدراسات الإسلامية</x:v>
@@ -2558,7 +2549,7 @@
         <x:v>الدراسات الإسلامية: جديدة 47</x:v>
       </x:c>
       <x:c r="G43" s="39" t="str">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H43" s="39" t="n">
         <x:v>1</x:v>
@@ -2566,12 +2557,12 @@
       <x:c r="I43" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J43" s="39" t="str"/>
+      <x:c r="J43" s="39"/>
       <x:c r="K43" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L43" s="39" t="str">
-        <x:v>2004252-4||الحديثالتحليلي1</x:v>
+        <x:v>2004256-2||الحديثالتحليلي٢</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="42" customHeight="1">
@@ -2579,10 +2570,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B44" s="33" t="str">
-        <x:v>2004256-2</x:v>
+        <x:v>2004262-2</x:v>
       </x:c>
       <x:c r="C44" s="39" t="str">
-        <x:v>الحديث التحليلي (٢)</x:v>
+        <x:v>الدعوة والحسبة</x:v>
       </x:c>
       <x:c r="D44" s="39" t="str">
         <x:v>الدراسات الإسلامية</x:v>
@@ -2594,7 +2585,7 @@
         <x:v>الدراسات الإسلامية: جديدة 47</x:v>
       </x:c>
       <x:c r="G44" s="39" t="str">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H44" s="39" t="n">
         <x:v>1</x:v>
@@ -2602,12 +2593,12 @@
       <x:c r="I44" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J44" s="39" t="str"/>
+      <x:c r="J44" s="39"/>
       <x:c r="K44" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L44" s="39" t="str">
-        <x:v>2004256-2||الحديثالتحليلي٢</x:v>
+        <x:v>2004262-2||الدعوةوالحسبة</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="42" customHeight="1">
@@ -2615,10 +2606,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B45" s="33" t="str">
-        <x:v>2004262-2</x:v>
+        <x:v>2004269-4</x:v>
       </x:c>
       <x:c r="C45" s="39" t="str">
-        <x:v>الدعوة والحسبة</x:v>
+        <x:v>التخريج ودراسة الأسانيد</x:v>
       </x:c>
       <x:c r="D45" s="39" t="str">
         <x:v>الدراسات الإسلامية</x:v>
@@ -2630,7 +2621,7 @@
         <x:v>الدراسات الإسلامية: جديدة 47</x:v>
       </x:c>
       <x:c r="G45" s="39" t="str">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H45" s="39" t="n">
         <x:v>1</x:v>
@@ -2638,12 +2629,12 @@
       <x:c r="I45" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J45" s="39" t="str"/>
+      <x:c r="J45" s="39"/>
       <x:c r="K45" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L45" s="39" t="str">
-        <x:v>2004262-2||الدعوةوالحسبة</x:v>
+        <x:v>2004269-4||التخريجودراسةالاسانيد</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="42" customHeight="1">
@@ -2651,10 +2642,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B46" s="33" t="str">
-        <x:v>2004269-4</x:v>
+        <x:v>2004272-2</x:v>
       </x:c>
       <x:c r="C46" s="39" t="str">
-        <x:v>التخريج ودراسة الأسانيد</x:v>
+        <x:v>العمل الخيري</x:v>
       </x:c>
       <x:c r="D46" s="39" t="str">
         <x:v>الدراسات الإسلامية</x:v>
@@ -2674,12 +2665,12 @@
       <x:c r="I46" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J46" s="39" t="str"/>
+      <x:c r="J46" s="39"/>
       <x:c r="K46" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L46" s="39" t="str">
-        <x:v>2004269-4||التخريجودراسةالاسانيد</x:v>
+        <x:v>2004272-2||العملالخيري</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="42" customHeight="1">
@@ -2687,10 +2678,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B47" s="33" t="str">
-        <x:v>2004272-2</x:v>
+        <x:v>2004305-4</x:v>
       </x:c>
       <x:c r="C47" s="39" t="str">
-        <x:v>العمل الخيري</x:v>
+        <x:v>أحاديث الأحكام (١)</x:v>
       </x:c>
       <x:c r="D47" s="39" t="str">
         <x:v>الدراسات الإسلامية</x:v>
@@ -2702,7 +2693,7 @@
         <x:v>الدراسات الإسلامية: جديدة 47</x:v>
       </x:c>
       <x:c r="G47" s="39" t="str">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H47" s="39" t="n">
         <x:v>1</x:v>
@@ -2710,12 +2701,12 @@
       <x:c r="I47" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J47" s="39" t="str"/>
+      <x:c r="J47" s="39"/>
       <x:c r="K47" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L47" s="39" t="str">
-        <x:v>2004272-2||العملالخيري</x:v>
+        <x:v>2004305-4||احاديثالاحكام١</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="42" customHeight="1">
@@ -2723,10 +2714,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B48" s="33" t="str">
-        <x:v>2004305-4</x:v>
+        <x:v>20013101-3</x:v>
       </x:c>
       <x:c r="C48" s="39" t="str">
-        <x:v>أحاديث الأحكام (١)</x:v>
+        <x:v>الفقه (٤)</x:v>
       </x:c>
       <x:c r="D48" s="39" t="str">
         <x:v>الدراسات الإسلامية</x:v>
@@ -2738,7 +2729,7 @@
         <x:v>الدراسات الإسلامية: جديدة 47</x:v>
       </x:c>
       <x:c r="G48" s="39" t="str">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H48" s="39" t="n">
         <x:v>1</x:v>
@@ -2746,12 +2737,12 @@
       <x:c r="I48" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J48" s="39" t="str"/>
+      <x:c r="J48" s="39"/>
       <x:c r="K48" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L48" s="39" t="str">
-        <x:v>2004305-4||احاديثالاحكام١</x:v>
+        <x:v>20013101-3||الفقه٤</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="42" customHeight="1">
@@ -2759,10 +2750,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B49" s="33" t="str">
-        <x:v>20013101-3</x:v>
+        <x:v>20013201-4</x:v>
       </x:c>
       <x:c r="C49" s="39" t="str">
-        <x:v>الفقه (٤)</x:v>
+        <x:v>الفقه (٥)</x:v>
       </x:c>
       <x:c r="D49" s="39" t="str">
         <x:v>الدراسات الإسلامية</x:v>
@@ -2774,7 +2765,7 @@
         <x:v>الدراسات الإسلامية: جديدة 47</x:v>
       </x:c>
       <x:c r="G49" s="39" t="str">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H49" s="39" t="n">
         <x:v>1</x:v>
@@ -2782,12 +2773,12 @@
       <x:c r="I49" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J49" s="39" t="str"/>
+      <x:c r="J49" s="39"/>
       <x:c r="K49" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L49" s="39" t="str">
-        <x:v>20013101-3||الفقه٤</x:v>
+        <x:v>20013201-4||الفقه٥</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="42" customHeight="1">
@@ -2795,10 +2786,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B50" s="33" t="str">
-        <x:v>20013201-4</x:v>
+        <x:v>20041201-2</x:v>
       </x:c>
       <x:c r="C50" s="39" t="str">
-        <x:v>الفقه (٥)</x:v>
+        <x:v>التجويد</x:v>
       </x:c>
       <x:c r="D50" s="39" t="str">
         <x:v>الدراسات الإسلامية</x:v>
@@ -2807,10 +2798,10 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F50" s="39" t="str">
-        <x:v>الدراسات الإسلامية: جديدة 47</x:v>
+        <x:v>الدراسات الإسلامية: قديمة 39</x:v>
       </x:c>
       <x:c r="G50" s="39" t="str">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H50" s="39" t="n">
         <x:v>1</x:v>
@@ -2818,12 +2809,12 @@
       <x:c r="I50" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J50" s="39" t="str"/>
+      <x:c r="J50" s="39"/>
       <x:c r="K50" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L50" s="39" t="str">
-        <x:v>20013201-4||الفقه٥</x:v>
+        <x:v>20041201-2||التجويد</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="42" customHeight="1">
@@ -2831,10 +2822,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B51" s="33" t="str">
-        <x:v>20041201-2</x:v>
+        <x:v>20042111-2</x:v>
       </x:c>
       <x:c r="C51" s="39" t="str">
-        <x:v>التجويد</x:v>
+        <x:v>العقيدة (٢)</x:v>
       </x:c>
       <x:c r="D51" s="39" t="str">
         <x:v>الدراسات الإسلامية</x:v>
@@ -2843,10 +2834,10 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F51" s="39" t="str">
-        <x:v>الدراسات الإسلامية: قديمة 39</x:v>
+        <x:v>الدراسات الإسلامية: جديدة 47</x:v>
       </x:c>
       <x:c r="G51" s="39" t="str">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H51" s="39" t="n">
         <x:v>1</x:v>
@@ -2854,12 +2845,12 @@
       <x:c r="I51" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J51" s="39" t="str"/>
+      <x:c r="J51" s="39"/>
       <x:c r="K51" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L51" s="39" t="str">
-        <x:v>20041201-2||التجويد</x:v>
+        <x:v>20042111-2||العقيدة٢</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="42" customHeight="1">
@@ -2867,10 +2858,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B52" s="33" t="str">
-        <x:v>20042111-2</x:v>
+        <x:v>20043105-2</x:v>
       </x:c>
       <x:c r="C52" s="39" t="str">
-        <x:v>العقيدة (٢)</x:v>
+        <x:v>الفقه المقارن</x:v>
       </x:c>
       <x:c r="D52" s="39" t="str">
         <x:v>الدراسات الإسلامية</x:v>
@@ -2879,10 +2870,10 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F52" s="39" t="str">
-        <x:v>الدراسات الإسلامية: جديدة 47</x:v>
+        <x:v>الدراسات الإسلامية: قديمة 39</x:v>
       </x:c>
       <x:c r="G52" s="39" t="str">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H52" s="39" t="n">
         <x:v>1</x:v>
@@ -2890,12 +2881,12 @@
       <x:c r="I52" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J52" s="39" t="str"/>
+      <x:c r="J52" s="39"/>
       <x:c r="K52" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L52" s="39" t="str">
-        <x:v>20042111-2||العقيدة٢</x:v>
+        <x:v>20043105-2||الفقهالمقارن</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="42" customHeight="1">
@@ -2903,10 +2894,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B53" s="33" t="str">
-        <x:v>20043105-2</x:v>
+        <x:v>20043108-2</x:v>
       </x:c>
       <x:c r="C53" s="39" t="str">
-        <x:v>الفقه المقارن</x:v>
+        <x:v>علم المواريث (1)</x:v>
       </x:c>
       <x:c r="D53" s="39" t="str">
         <x:v>الدراسات الإسلامية</x:v>
@@ -2926,12 +2917,12 @@
       <x:c r="I53" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J53" s="39" t="str"/>
+      <x:c r="J53" s="39"/>
       <x:c r="K53" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L53" s="39" t="str">
-        <x:v>20043105-2||الفقهالمقارن</x:v>
+        <x:v>20043108-2||علمالمواريث1</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="42" customHeight="1">
@@ -2939,10 +2930,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B54" s="33" t="str">
-        <x:v>20043108-2</x:v>
+        <x:v>20043109-2</x:v>
       </x:c>
       <x:c r="C54" s="39" t="str">
-        <x:v>علم المواريث (1)</x:v>
+        <x:v>دراسات في سير السلف</x:v>
       </x:c>
       <x:c r="D54" s="39" t="str">
         <x:v>الدراسات الإسلامية</x:v>
@@ -2951,7 +2942,7 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F54" s="39" t="str">
-        <x:v>الدراسات الإسلامية: قديمة 39</x:v>
+        <x:v>الدراسات الإسلامية: جديدة 47</x:v>
       </x:c>
       <x:c r="G54" s="39" t="str">
         <x:v>5</x:v>
@@ -2962,12 +2953,12 @@
       <x:c r="I54" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J54" s="39" t="str"/>
+      <x:c r="J54" s="39"/>
       <x:c r="K54" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L54" s="39" t="str">
-        <x:v>20043108-2||علمالمواريث1</x:v>
+        <x:v>20043109-2||دراساتفيسيرالسلف</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="42" customHeight="1">
@@ -2975,10 +2966,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B55" s="33" t="str">
-        <x:v>20043109-2</x:v>
+        <x:v>20043110-2</x:v>
       </x:c>
       <x:c r="C55" s="39" t="str">
-        <x:v>دراسات في سير السلف</x:v>
+        <x:v>محاسن الإسلام</x:v>
       </x:c>
       <x:c r="D55" s="39" t="str">
         <x:v>الدراسات الإسلامية</x:v>
@@ -2998,12 +2989,12 @@
       <x:c r="I55" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J55" s="39" t="str"/>
+      <x:c r="J55" s="39"/>
       <x:c r="K55" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L55" s="39" t="str">
-        <x:v>20043109-2||دراساتفيسيرالسلف</x:v>
+        <x:v>20043110-2||محاسنالاسلام</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="42" customHeight="1">
@@ -3011,10 +3002,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B56" s="33" t="str">
-        <x:v>20043110-2</x:v>
+        <x:v>20043111-2</x:v>
       </x:c>
       <x:c r="C56" s="39" t="str">
-        <x:v>محاسن الإسلام</x:v>
+        <x:v>الأمن الفكري</x:v>
       </x:c>
       <x:c r="D56" s="39" t="str">
         <x:v>الدراسات الإسلامية</x:v>
@@ -3026,7 +3017,7 @@
         <x:v>الدراسات الإسلامية: جديدة 47</x:v>
       </x:c>
       <x:c r="G56" s="39" t="str">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H56" s="39" t="n">
         <x:v>1</x:v>
@@ -3034,12 +3025,12 @@
       <x:c r="I56" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J56" s="39" t="str"/>
+      <x:c r="J56" s="39"/>
       <x:c r="K56" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L56" s="39" t="str">
-        <x:v>20043110-2||محاسنالاسلام</x:v>
+        <x:v>20043111-2||الامنالفكري</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="42" customHeight="1">
@@ -3047,10 +3038,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B57" s="33" t="str">
-        <x:v>20043111-2</x:v>
+        <x:v>20043202-2</x:v>
       </x:c>
       <x:c r="C57" s="39" t="str">
-        <x:v>الأمن الفكري</x:v>
+        <x:v>القواعد الفقهية</x:v>
       </x:c>
       <x:c r="D57" s="39" t="str">
         <x:v>الدراسات الإسلامية</x:v>
@@ -3059,10 +3050,10 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F57" s="39" t="str">
-        <x:v>الدراسات الإسلامية: جديدة 47</x:v>
+        <x:v>الدراسات الإسلامية: قديمة 39</x:v>
       </x:c>
       <x:c r="G57" s="39" t="str">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H57" s="39" t="n">
         <x:v>1</x:v>
@@ -3070,12 +3061,12 @@
       <x:c r="I57" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J57" s="39" t="str"/>
+      <x:c r="J57" s="39"/>
       <x:c r="K57" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L57" s="39" t="str">
-        <x:v>20043111-2||الامنالفكري</x:v>
+        <x:v>20043202-2||القواعدالفقهية</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="42" customHeight="1">
@@ -3083,10 +3074,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B58" s="33" t="str">
-        <x:v>20043202-2</x:v>
+        <x:v>20044101-2</x:v>
       </x:c>
       <x:c r="C58" s="39" t="str">
-        <x:v>القواعد الفقهية</x:v>
+        <x:v>أصول فقه (3)</x:v>
       </x:c>
       <x:c r="D58" s="39" t="str">
         <x:v>الدراسات الإسلامية</x:v>
@@ -3098,7 +3089,7 @@
         <x:v>الدراسات الإسلامية: قديمة 39</x:v>
       </x:c>
       <x:c r="G58" s="39" t="str">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H58" s="39" t="n">
         <x:v>1</x:v>
@@ -3106,12 +3097,12 @@
       <x:c r="I58" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J58" s="39" t="str"/>
+      <x:c r="J58" s="39"/>
       <x:c r="K58" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L58" s="39" t="str">
-        <x:v>20043202-2||القواعدالفقهية</x:v>
+        <x:v>20044101-2||اصولفقه3</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="42" customHeight="1">
@@ -3119,10 +3110,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B59" s="33" t="str">
-        <x:v>20044101-2</x:v>
+        <x:v>20044206-2</x:v>
       </x:c>
       <x:c r="C59" s="39" t="str">
-        <x:v>أصول فقه (3)</x:v>
+        <x:v>علم المواريث (2)</x:v>
       </x:c>
       <x:c r="D59" s="39" t="str">
         <x:v>الدراسات الإسلامية</x:v>
@@ -3134,7 +3125,7 @@
         <x:v>الدراسات الإسلامية: قديمة 39</x:v>
       </x:c>
       <x:c r="G59" s="39" t="str">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H59" s="39" t="n">
         <x:v>1</x:v>
@@ -3142,12 +3133,12 @@
       <x:c r="I59" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J59" s="39" t="str"/>
+      <x:c r="J59" s="39"/>
       <x:c r="K59" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L59" s="39" t="str">
-        <x:v>20044101-2||اصولفقه3</x:v>
+        <x:v>20044206-2||علمالمواريث2</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="42" customHeight="1">
@@ -3155,10 +3146,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B60" s="33" t="str">
-        <x:v>20044206-2</x:v>
+        <x:v>20044220-4</x:v>
       </x:c>
       <x:c r="C60" s="39" t="str">
-        <x:v>علم المواريث (2)</x:v>
+        <x:v>التدريب التعاوني</x:v>
       </x:c>
       <x:c r="D60" s="39" t="str">
         <x:v>الدراسات الإسلامية</x:v>
@@ -3167,7 +3158,7 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F60" s="39" t="str">
-        <x:v>الدراسات الإسلامية: قديمة 39</x:v>
+        <x:v>الدراسات الإسلامية: جديدة 47</x:v>
       </x:c>
       <x:c r="G60" s="39" t="str">
         <x:v>8</x:v>
@@ -3178,12 +3169,12 @@
       <x:c r="I60" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J60" s="39" t="str"/>
+      <x:c r="J60" s="39"/>
       <x:c r="K60" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L60" s="39" t="str">
-        <x:v>20044206-2||علمالمواريث2</x:v>
+        <x:v>20044220-4||التدريبالتعاوني</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="42" customHeight="1">
@@ -3191,35 +3182,36 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B61" s="33" t="str">
-        <x:v>20044220-4</x:v>
+        <x:v>2001192-2</x:v>
       </x:c>
       <x:c r="C61" s="39" t="str">
-        <x:v>التدريب التعاوني</x:v>
+        <x:v>علوم الحديث (2)</x:v>
       </x:c>
       <x:c r="D61" s="39" t="str">
-        <x:v>الدراسات الإسلامية</x:v>
+        <x:v>الشريعة</x:v>
       </x:c>
       <x:c r="E61" s="39" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F61" s="39" t="str">
-        <x:v>الدراسات الإسلامية: جديدة 47</x:v>
+        <x:v>الشريعة: قديمة 38
+الشريعة: قديمة 39</x:v>
       </x:c>
       <x:c r="G61" s="39" t="str">
-        <x:v>8</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H61" s="39" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I61" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J61" s="39" t="str"/>
+      <x:c r="J61" s="39"/>
       <x:c r="K61" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L61" s="39" t="str">
-        <x:v>20044220-4||التدريبالتعاوني</x:v>
+        <x:v>2001192-2||علومالحديث2</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="42" customHeight="1">
@@ -3227,10 +3219,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B62" s="33" t="str">
-        <x:v>2001192-2</x:v>
+        <x:v>2001193-2</x:v>
       </x:c>
       <x:c r="C62" s="39" t="str">
-        <x:v>علوم الحديث (2)</x:v>
+        <x:v>علوم الحديث (1)</x:v>
       </x:c>
       <x:c r="D62" s="39" t="str">
         <x:v>الشريعة</x:v>
@@ -3243,7 +3235,7 @@
 الشريعة: قديمة 39</x:v>
       </x:c>
       <x:c r="G62" s="39" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H62" s="39" t="n">
         <x:v>2</x:v>
@@ -3251,12 +3243,12 @@
       <x:c r="I62" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J62" s="39" t="str"/>
+      <x:c r="J62" s="39"/>
       <x:c r="K62" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L62" s="39" t="str">
-        <x:v>2001192-2||علومالحديث2</x:v>
+        <x:v>2001193-2||علومالحديث1</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="42" customHeight="1">
@@ -3264,10 +3256,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B63" s="33" t="str">
-        <x:v>2001193-2</x:v>
+        <x:v>2001217-4</x:v>
       </x:c>
       <x:c r="C63" s="39" t="str">
-        <x:v>علوم الحديث (1)</x:v>
+        <x:v>أدلة الأحكام الشرعية (2)</x:v>
       </x:c>
       <x:c r="D63" s="39" t="str">
         <x:v>الشريعة</x:v>
@@ -3280,7 +3272,7 @@
 الشريعة: قديمة 39</x:v>
       </x:c>
       <x:c r="G63" s="39" t="str">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H63" s="39" t="n">
         <x:v>2</x:v>
@@ -3288,12 +3280,12 @@
       <x:c r="I63" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J63" s="39" t="str"/>
+      <x:c r="J63" s="39"/>
       <x:c r="K63" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L63" s="39" t="str">
-        <x:v>2001193-2||علومالحديث1</x:v>
+        <x:v>2001217-4||ادلةالاحكامالشرعية2</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="42" customHeight="1">
@@ -3301,10 +3293,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B64" s="33" t="str">
-        <x:v>2001217-4</x:v>
+        <x:v>2001218-2</x:v>
       </x:c>
       <x:c r="C64" s="39" t="str">
-        <x:v>أدلة الأحكام الشرعية (2)</x:v>
+        <x:v>قاعة بحث (تطبيقي)</x:v>
       </x:c>
       <x:c r="D64" s="39" t="str">
         <x:v>الشريعة</x:v>
@@ -3313,24 +3305,23 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F64" s="39" t="str">
-        <x:v>الشريعة: قديمة 38
-الشريعة: قديمة 39</x:v>
+        <x:v>الشريعة: قديمة 38</x:v>
       </x:c>
       <x:c r="G64" s="39" t="str">
         <x:v>4</x:v>
       </x:c>
       <x:c r="H64" s="39" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I64" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J64" s="39" t="str"/>
+      <x:c r="J64" s="39"/>
       <x:c r="K64" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L64" s="39" t="str">
-        <x:v>2001217-4||ادلةالاحكامالشرعية2</x:v>
+        <x:v>2001218-2||قاعةبحثتطبيقي</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="42" customHeight="1">
@@ -3338,10 +3329,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B65" s="33" t="str">
-        <x:v>2001218-2</x:v>
+        <x:v>2001219-3</x:v>
       </x:c>
       <x:c r="C65" s="39" t="str">
-        <x:v>قاعة بحث (تطبيقي)</x:v>
+        <x:v>أدلة الأحكام الشرعية (1)</x:v>
       </x:c>
       <x:c r="D65" s="39" t="str">
         <x:v>الشريعة</x:v>
@@ -3350,23 +3341,24 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F65" s="39" t="str">
-        <x:v>الشريعة: قديمة 38</x:v>
+        <x:v>الشريعة: قديمة 38
+الشريعة: قديمة 39</x:v>
       </x:c>
       <x:c r="G65" s="39" t="str">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H65" s="39" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I65" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J65" s="39" t="str"/>
+      <x:c r="J65" s="39"/>
       <x:c r="K65" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L65" s="39" t="str">
-        <x:v>2001218-2||قاعةبحثتطبيقي</x:v>
+        <x:v>2001219-3||ادلةالاحكامالشرعية1</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="42" customHeight="1">
@@ -3374,10 +3366,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B66" s="33" t="str">
-        <x:v>2001219-3</x:v>
+        <x:v>2001231-2</x:v>
       </x:c>
       <x:c r="C66" s="39" t="str">
-        <x:v>أدلة الأحكام الشرعية (1)</x:v>
+        <x:v>أحاديث الأحكام (1)</x:v>
       </x:c>
       <x:c r="D66" s="39" t="str">
         <x:v>الشريعة</x:v>
@@ -3398,12 +3390,12 @@
       <x:c r="I66" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J66" s="39" t="str"/>
+      <x:c r="J66" s="39"/>
       <x:c r="K66" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L66" s="39" t="str">
-        <x:v>2001219-3||ادلةالاحكامالشرعية1</x:v>
+        <x:v>2001231-2||احاديثالاحكام1</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="42" customHeight="1">
@@ -3411,10 +3403,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B67" s="33" t="str">
-        <x:v>2001231-2</x:v>
+        <x:v>2001280-2</x:v>
       </x:c>
       <x:c r="C67" s="39" t="str">
-        <x:v>أحاديث الأحكام (1)</x:v>
+        <x:v>أصول الدعوة والحسبة</x:v>
       </x:c>
       <x:c r="D67" s="39" t="str">
         <x:v>الشريعة</x:v>
@@ -3427,7 +3419,7 @@
 الشريعة: قديمة 39</x:v>
       </x:c>
       <x:c r="G67" s="39" t="str">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H67" s="39" t="n">
         <x:v>2</x:v>
@@ -3435,12 +3427,12 @@
       <x:c r="I67" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J67" s="39" t="str"/>
+      <x:c r="J67" s="39"/>
       <x:c r="K67" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L67" s="39" t="str">
-        <x:v>2001231-2||احاديثالاحكام1</x:v>
+        <x:v>2001280-2||اصولالدعوةوالحسبة</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="42" customHeight="1">
@@ -3448,10 +3440,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B68" s="33" t="str">
-        <x:v>2001280-2</x:v>
+        <x:v>2001301-2</x:v>
       </x:c>
       <x:c r="C68" s="39" t="str">
-        <x:v>أصول الدعوة والحسبة</x:v>
+        <x:v>تدوين السنة</x:v>
       </x:c>
       <x:c r="D68" s="39" t="str">
         <x:v>الشريعة</x:v>
@@ -3472,12 +3464,12 @@
       <x:c r="I68" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J68" s="39" t="str"/>
+      <x:c r="J68" s="39"/>
       <x:c r="K68" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L68" s="39" t="str">
-        <x:v>2001280-2||اصولالدعوةوالحسبة</x:v>
+        <x:v>2001301-2||تدوينالسنة</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="42" customHeight="1">
@@ -3485,10 +3477,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B69" s="33" t="str">
-        <x:v>2001301-2</x:v>
+        <x:v>2001332-2</x:v>
       </x:c>
       <x:c r="C69" s="39" t="str">
-        <x:v>تدوين السنة</x:v>
+        <x:v>أحاديث الأحكام (2)</x:v>
       </x:c>
       <x:c r="D69" s="39" t="str">
         <x:v>الشريعة</x:v>
@@ -3501,7 +3493,7 @@
 الشريعة: قديمة 39</x:v>
       </x:c>
       <x:c r="G69" s="39" t="str">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H69" s="39" t="n">
         <x:v>2</x:v>
@@ -3509,12 +3501,12 @@
       <x:c r="I69" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J69" s="39" t="str"/>
+      <x:c r="J69" s="39"/>
       <x:c r="K69" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L69" s="39" t="str">
-        <x:v>2001301-2||تدوينالسنة</x:v>
+        <x:v>2001332-2||احاديثالاحكام2</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="42" customHeight="1">
@@ -3522,10 +3514,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B70" s="33" t="str">
-        <x:v>2001332-2</x:v>
+        <x:v>2001493-2</x:v>
       </x:c>
       <x:c r="C70" s="39" t="str">
-        <x:v>أحاديث الأحكام (2)</x:v>
+        <x:v>تخريج ودراسة الأسانيد</x:v>
       </x:c>
       <x:c r="D70" s="39" t="str">
         <x:v>الشريعة</x:v>
@@ -3538,7 +3530,7 @@
 الشريعة: قديمة 39</x:v>
       </x:c>
       <x:c r="G70" s="39" t="str">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H70" s="39" t="n">
         <x:v>2</x:v>
@@ -3546,12 +3538,12 @@
       <x:c r="I70" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J70" s="39" t="str"/>
+      <x:c r="J70" s="39"/>
       <x:c r="K70" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L70" s="39" t="str">
-        <x:v>2001332-2||احاديثالاحكام2</x:v>
+        <x:v>2001493-2||تخريجودراسةالاسانيد</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="42" customHeight="1">
@@ -3559,10 +3551,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B71" s="33" t="str">
-        <x:v>2001493-2</x:v>
+        <x:v>2003243-2</x:v>
       </x:c>
       <x:c r="C71" s="39" t="str">
-        <x:v>تخريج ودراسة الأسانيد</x:v>
+        <x:v>مبادئ القانون الإداري</x:v>
       </x:c>
       <x:c r="D71" s="39" t="str">
         <x:v>الشريعة</x:v>
@@ -3571,24 +3563,23 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F71" s="39" t="str">
-        <x:v>الشريعة: قديمة 38
-الشريعة: قديمة 39</x:v>
+        <x:v>الشريعة: قديمة 38</x:v>
       </x:c>
       <x:c r="G71" s="39" t="str">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H71" s="39" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I71" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J71" s="39" t="str"/>
+      <x:c r="J71" s="39"/>
       <x:c r="K71" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L71" s="39" t="str">
-        <x:v>2001493-2||تخريجودراسةالاسانيد</x:v>
+        <x:v>2003243-2||مباديالقانونالاداري</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="42" customHeight="1">
@@ -3596,10 +3587,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B72" s="33" t="str">
-        <x:v>2002230-2</x:v>
+        <x:v>2003325-1</x:v>
       </x:c>
       <x:c r="C72" s="39" t="str">
-        <x:v>علوم قرآن</x:v>
+        <x:v>نظام المرافعات الشرعية</x:v>
       </x:c>
       <x:c r="D72" s="39" t="str">
         <x:v>الشريعة</x:v>
@@ -3612,7 +3603,7 @@
 الشريعة: قديمة 39</x:v>
       </x:c>
       <x:c r="G72" s="39" t="str">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H72" s="39" t="n">
         <x:v>2</x:v>
@@ -3620,12 +3611,12 @@
       <x:c r="I72" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J72" s="39" t="str"/>
+      <x:c r="J72" s="39"/>
       <x:c r="K72" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L72" s="39" t="str">
-        <x:v>2002230-2||علومقران</x:v>
+        <x:v>2003325-1||نظامالمرافعاتالشرعية</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="42" customHeight="1">
@@ -3633,10 +3624,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B73" s="33" t="str">
-        <x:v>2002241-2</x:v>
+        <x:v>2003328-1</x:v>
       </x:c>
       <x:c r="C73" s="39" t="str">
-        <x:v>تفسير آيات الأحكام (1)</x:v>
+        <x:v>نظام الإجراءات الجزائية</x:v>
       </x:c>
       <x:c r="D73" s="39" t="str">
         <x:v>الشريعة</x:v>
@@ -3649,7 +3640,7 @@
 الشريعة: قديمة 39</x:v>
       </x:c>
       <x:c r="G73" s="39" t="str">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H73" s="39" t="n">
         <x:v>2</x:v>
@@ -3657,12 +3648,12 @@
       <x:c r="I73" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J73" s="39" t="str"/>
+      <x:c r="J73" s="39"/>
       <x:c r="K73" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L73" s="39" t="str">
-        <x:v>2002241-2||تفسيراياتالاحكام1</x:v>
+        <x:v>2003328-1||نظامالاجراءاتالجزايية</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="42" customHeight="1">
@@ -3670,10 +3661,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B74" s="33" t="str">
-        <x:v>2002242-2</x:v>
+        <x:v>2004301-2</x:v>
       </x:c>
       <x:c r="C74" s="39" t="str">
-        <x:v>تفسير آيات الأحكام (2)</x:v>
+        <x:v>تدوين السنة</x:v>
       </x:c>
       <x:c r="D74" s="39" t="str">
         <x:v>الشريعة</x:v>
@@ -3682,24 +3673,23 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F74" s="39" t="str">
-        <x:v>الشريعة: قديمة 38
-الشريعة: قديمة 39</x:v>
+        <x:v>الشريعة: جديدة 47</x:v>
       </x:c>
       <x:c r="G74" s="39" t="str">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H74" s="39" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I74" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J74" s="39" t="str"/>
+      <x:c r="J74" s="39"/>
       <x:c r="K74" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L74" s="39" t="str">
-        <x:v>2002242-2||تفسيراياتالاحكام2</x:v>
+        <x:v>2004301-2||تدوينالسنة</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="42" customHeight="1">
@@ -3707,10 +3697,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B75" s="33" t="str">
-        <x:v>2002343-2</x:v>
+        <x:v>2004476-2</x:v>
       </x:c>
       <x:c r="C75" s="39" t="str">
-        <x:v>تفسير آيات الأحكام (3)</x:v>
+        <x:v>الأديان والفرق</x:v>
       </x:c>
       <x:c r="D75" s="39" t="str">
         <x:v>الشريعة</x:v>
@@ -3719,24 +3709,23 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F75" s="39" t="str">
-        <x:v>الشريعة: قديمة 38
-الشريعة: قديمة 39</x:v>
+        <x:v>الشريعة: جديدة 47</x:v>
       </x:c>
       <x:c r="G75" s="39" t="str">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H75" s="39" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I75" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J75" s="39" t="str"/>
+      <x:c r="J75" s="39"/>
       <x:c r="K75" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L75" s="39" t="str">
-        <x:v>2002343-2||تفسيراياتالاحكام3</x:v>
+        <x:v>2004476-2||الاديانوالفرق</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="42" customHeight="1">
@@ -3744,10 +3733,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B76" s="33" t="str">
-        <x:v>2003243-2</x:v>
+        <x:v>20014201-2</x:v>
       </x:c>
       <x:c r="C76" s="39" t="str">
-        <x:v>مبادئ القانون الإداري</x:v>
+        <x:v>التدريبات العملية</x:v>
       </x:c>
       <x:c r="D76" s="39" t="str">
         <x:v>الشريعة</x:v>
@@ -3756,10 +3745,10 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F76" s="39" t="str">
-        <x:v>الشريعة: قديمة 38</x:v>
+        <x:v>الشريعة: قديمة 39</x:v>
       </x:c>
       <x:c r="G76" s="39" t="str">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H76" s="39" t="n">
         <x:v>1</x:v>
@@ -3767,12 +3756,12 @@
       <x:c r="I76" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J76" s="39" t="str"/>
+      <x:c r="J76" s="39"/>
       <x:c r="K76" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L76" s="39" t="str">
-        <x:v>2003243-2||مباديالقانونالاداري</x:v>
+        <x:v>20014201-2||التدريباتالعملية</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="42" customHeight="1">
@@ -3780,10 +3769,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B77" s="33" t="str">
-        <x:v>2003325-1</x:v>
+        <x:v>20032202-2</x:v>
       </x:c>
       <x:c r="C77" s="39" t="str">
-        <x:v>نظام المرافعات الشرعية</x:v>
+        <x:v>المدخل إلى دراسة الأنظمة</x:v>
       </x:c>
       <x:c r="D77" s="39" t="str">
         <x:v>الشريعة</x:v>
@@ -3792,24 +3781,23 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F77" s="39" t="str">
-        <x:v>الشريعة: قديمة 38
-الشريعة: قديمة 39</x:v>
+        <x:v>الشريعة: قديمة 39</x:v>
       </x:c>
       <x:c r="G77" s="39" t="str">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H77" s="39" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I77" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J77" s="39" t="str"/>
+      <x:c r="J77" s="39"/>
       <x:c r="K77" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L77" s="39" t="str">
-        <x:v>2003325-1||نظامالمرافعاتالشرعية</x:v>
+        <x:v>20032202-2||المدخلاليدراسةالانظمة</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="42" customHeight="1">
@@ -3817,36 +3805,35 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B78" s="33" t="str">
-        <x:v>2003328-1</x:v>
+        <x:v>2003880-2</x:v>
       </x:c>
       <x:c r="C78" s="39" t="str">
-        <x:v>نظام الإجراءات الجزائية</x:v>
+        <x:v>الأنظمة العدلية في السعودية</x:v>
       </x:c>
       <x:c r="D78" s="39" t="str">
-        <x:v>الشريعة</x:v>
+        <x:v>الفقه</x:v>
       </x:c>
       <x:c r="E78" s="39" t="str">
-        <x:v>بكالوريوس</x:v>
+        <x:v>ماجستير</x:v>
       </x:c>
       <x:c r="F78" s="39" t="str">
-        <x:v>الشريعة: قديمة 38
-الشريعة: قديمة 39</x:v>
+        <x:v>الفقه: جديدة 1</x:v>
       </x:c>
       <x:c r="G78" s="39" t="str">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H78" s="39" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I78" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J78" s="39" t="str"/>
+      <x:c r="J78" s="39"/>
       <x:c r="K78" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L78" s="39" t="str">
-        <x:v>2003328-1||نظامالاجراءاتالجزايية</x:v>
+        <x:v>2003880-2||الانظمةالعدليةفيالسعودية</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="42" customHeight="1">
@@ -3854,35 +3841,36 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B79" s="33" t="str">
-        <x:v>2004301-2</x:v>
+        <x:v>2001205-2</x:v>
       </x:c>
       <x:c r="C79" s="39" t="str">
-        <x:v>تدوين السنة</x:v>
+        <x:v>الحديث (1)</x:v>
       </x:c>
       <x:c r="D79" s="39" t="str">
-        <x:v>الشريعة</x:v>
+        <x:v>القراءات، القرآن وعلومه</x:v>
       </x:c>
       <x:c r="E79" s="39" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F79" s="39" t="str">
-        <x:v>الشريعة: جديدة 47</x:v>
+        <x:v>القراءات: قديمة 38
+القرآن وعلومه: قديمة 39</x:v>
       </x:c>
       <x:c r="G79" s="39" t="str">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H79" s="39" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I79" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J79" s="39" t="str"/>
+      <x:c r="J79" s="39"/>
       <x:c r="K79" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L79" s="39" t="str">
-        <x:v>2004301-2||تدوينالسنة</x:v>
+        <x:v>2001205-2||الحديث1</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="42" customHeight="1">
@@ -3890,35 +3878,36 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B80" s="33" t="str">
-        <x:v>2004476-2</x:v>
+        <x:v>2001209-2</x:v>
       </x:c>
       <x:c r="C80" s="39" t="str">
-        <x:v>الأديان والفرق</x:v>
+        <x:v>الحديث (2)</x:v>
       </x:c>
       <x:c r="D80" s="39" t="str">
-        <x:v>الشريعة</x:v>
+        <x:v>القراءات، القرآن وعلومه</x:v>
       </x:c>
       <x:c r="E80" s="39" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F80" s="39" t="str">
-        <x:v>الشريعة: جديدة 47</x:v>
+        <x:v>القراءات: قديمة 38
+القرآن وعلومه: قديمة 39</x:v>
       </x:c>
       <x:c r="G80" s="39" t="str">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H80" s="39" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I80" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J80" s="39" t="str"/>
+      <x:c r="J80" s="39"/>
       <x:c r="K80" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L80" s="39" t="str">
-        <x:v>2004476-2||الاديانوالفرق</x:v>
+        <x:v>2001209-2||الحديث2</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="42" customHeight="1">
@@ -3926,35 +3915,37 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B81" s="33" t="str">
-        <x:v>20014201-2</x:v>
+        <x:v>2001221-2</x:v>
       </x:c>
       <x:c r="C81" s="39" t="str">
-        <x:v>التدريبات العملية</x:v>
+        <x:v>الفقه (1)</x:v>
       </x:c>
       <x:c r="D81" s="39" t="str">
-        <x:v>الشريعة</x:v>
+        <x:v>القراءات، القرآن وعلومه</x:v>
       </x:c>
       <x:c r="E81" s="39" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F81" s="39" t="str">
-        <x:v>الشريعة: قديمة 39</x:v>
+        <x:v>القراءات: جديدة 47
+القراءات: قديمة 38
+القرآن وعلومه: جديدة 47</x:v>
       </x:c>
       <x:c r="G81" s="39" t="str">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H81" s="39" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I81" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J81" s="39" t="str"/>
+      <x:c r="J81" s="39"/>
       <x:c r="K81" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L81" s="39" t="str">
-        <x:v>20014201-2||التدريباتالعملية</x:v>
+        <x:v>2001221-2||الفقه1</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="42" customHeight="1">
@@ -3962,22 +3953,22 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B82" s="33" t="str">
-        <x:v>20032202-2</x:v>
+        <x:v>2001273-2</x:v>
       </x:c>
       <x:c r="C82" s="39" t="str">
-        <x:v>المدخل إلى دراسة الأنظمة</x:v>
+        <x:v>العقيدة (1)</x:v>
       </x:c>
       <x:c r="D82" s="39" t="str">
-        <x:v>الشريعة</x:v>
+        <x:v>القراءات</x:v>
       </x:c>
       <x:c r="E82" s="39" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F82" s="39" t="str">
-        <x:v>الشريعة: قديمة 39</x:v>
+        <x:v>القراءات: قديمة 38</x:v>
       </x:c>
       <x:c r="G82" s="39" t="str">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H82" s="39" t="n">
         <x:v>1</x:v>
@@ -3985,12 +3976,12 @@
       <x:c r="I82" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J82" s="39" t="str"/>
+      <x:c r="J82" s="39"/>
       <x:c r="K82" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L82" s="39" t="str">
-        <x:v>20032202-2||المدخلاليدراسةالانظمة</x:v>
+        <x:v>2001273-2||العقيدة1</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="42" customHeight="1">
@@ -3998,35 +3989,36 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B83" s="33" t="str">
-        <x:v>2003880-2</x:v>
+        <x:v>2001320-2</x:v>
       </x:c>
       <x:c r="C83" s="39" t="str">
-        <x:v>الأنظمة العدلية في السعودية</x:v>
+        <x:v>الحديث (3)</x:v>
       </x:c>
       <x:c r="D83" s="39" t="str">
-        <x:v>الفقه</x:v>
+        <x:v>القراءات، القرآن وعلومه</x:v>
       </x:c>
       <x:c r="E83" s="39" t="str">
-        <x:v>ماجستير</x:v>
+        <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F83" s="39" t="str">
-        <x:v>الفقه: جديدة 1</x:v>
+        <x:v>القراءات: قديمة 38
+القرآن وعلومه: قديمة 39</x:v>
       </x:c>
       <x:c r="G83" s="39" t="str">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H83" s="39" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I83" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J83" s="39" t="str"/>
+      <x:c r="J83" s="39"/>
       <x:c r="K83" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L83" s="39" t="str">
-        <x:v>2003880-2||الانظمةالعدليةفيالسعودية</x:v>
+        <x:v>2001320-2||الحديث3</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="42" customHeight="1">
@@ -4034,10 +4026,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B84" s="33" t="str">
-        <x:v>2001205-2</x:v>
+        <x:v>2001322-2</x:v>
       </x:c>
       <x:c r="C84" s="39" t="str">
-        <x:v>الحديث (1)</x:v>
+        <x:v>الفقه (2)</x:v>
       </x:c>
       <x:c r="D84" s="39" t="str">
         <x:v>القراءات، القرآن وعلومه</x:v>
@@ -4047,23 +4039,24 @@
       </x:c>
       <x:c r="F84" s="39" t="str">
         <x:v>القراءات: قديمة 38
+القرآن وعلومه: جديدة 47
 القرآن وعلومه: قديمة 39</x:v>
       </x:c>
       <x:c r="G84" s="39" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H84" s="39" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H84" s="39" t="n">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="I84" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J84" s="39" t="str"/>
+      <x:c r="J84" s="39"/>
       <x:c r="K84" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L84" s="39" t="str">
-        <x:v>2001205-2||الحديث1</x:v>
+        <x:v>2001322-2||الفقه2</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="42" customHeight="1">
@@ -4071,36 +4064,35 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B85" s="33" t="str">
-        <x:v>2001209-2</x:v>
+        <x:v>2002111-3</x:v>
       </x:c>
       <x:c r="C85" s="39" t="str">
-        <x:v>الحديث (2)</x:v>
+        <x:v>عرض القراءات السبع (١)</x:v>
       </x:c>
       <x:c r="D85" s="39" t="str">
-        <x:v>القراءات، القرآن وعلومه</x:v>
+        <x:v>القراءات</x:v>
       </x:c>
       <x:c r="E85" s="39" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F85" s="39" t="str">
-        <x:v>القراءات: قديمة 38
-القرآن وعلومه: قديمة 39</x:v>
+        <x:v>القراءات: جديدة 47</x:v>
       </x:c>
       <x:c r="G85" s="39" t="str">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H85" s="39" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I85" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J85" s="39" t="str"/>
+      <x:c r="J85" s="39"/>
       <x:c r="K85" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L85" s="39" t="str">
-        <x:v>2001209-2||الحديث2</x:v>
+        <x:v>2002111-3||عرضالقراءاتالسبع١</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="42" customHeight="1">
@@ -4108,37 +4100,35 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B86" s="33" t="str">
-        <x:v>2001221-2</x:v>
+        <x:v>2002112-3</x:v>
       </x:c>
       <x:c r="C86" s="39" t="str">
-        <x:v>الفقه (1)</x:v>
+        <x:v>عرض القراءات السبع (٢)</x:v>
       </x:c>
       <x:c r="D86" s="39" t="str">
-        <x:v>القراءات، القرآن وعلومه</x:v>
+        <x:v>القراءات</x:v>
       </x:c>
       <x:c r="E86" s="39" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F86" s="39" t="str">
-        <x:v>القراءات: جديدة 47
-القراءات: قديمة 38
-القرآن وعلومه: جديدة 47</x:v>
+        <x:v>القراءات: جديدة 47</x:v>
       </x:c>
       <x:c r="G86" s="39" t="str">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H86" s="39" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I86" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J86" s="39" t="str"/>
+      <x:c r="J86" s="39"/>
       <x:c r="K86" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L86" s="39" t="str">
-        <x:v>2001221-2||الفقه1</x:v>
+        <x:v>2002112-3||عرضالقراءاتالسبع٢</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="42" customHeight="1">
@@ -4146,10 +4136,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B87" s="33" t="str">
-        <x:v>2001273-2</x:v>
+        <x:v>2002113-3</x:v>
       </x:c>
       <x:c r="C87" s="39" t="str">
-        <x:v>العقيدة (1)</x:v>
+        <x:v>عرض القراءات السبع (٣)</x:v>
       </x:c>
       <x:c r="D87" s="39" t="str">
         <x:v>القراءات</x:v>
@@ -4158,10 +4148,10 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F87" s="39" t="str">
-        <x:v>القراءات: قديمة 38</x:v>
+        <x:v>القراءات: جديدة 47</x:v>
       </x:c>
       <x:c r="G87" s="39" t="str">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H87" s="39" t="n">
         <x:v>1</x:v>
@@ -4169,12 +4159,12 @@
       <x:c r="I87" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J87" s="39" t="str"/>
+      <x:c r="J87" s="39"/>
       <x:c r="K87" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L87" s="39" t="str">
-        <x:v>2001273-2||العقيدة1</x:v>
+        <x:v>2002113-3||عرضالقراءاتالسبع٣</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="42" customHeight="1">
@@ -4182,36 +4172,35 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B88" s="33" t="str">
-        <x:v>2001320-2</x:v>
+        <x:v>2002114-3</x:v>
       </x:c>
       <x:c r="C88" s="39" t="str">
-        <x:v>الحديث (3)</x:v>
+        <x:v>عرض القراءات السبع (٤)</x:v>
       </x:c>
       <x:c r="D88" s="39" t="str">
-        <x:v>القراءات، القرآن وعلومه</x:v>
+        <x:v>القراءات</x:v>
       </x:c>
       <x:c r="E88" s="39" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F88" s="39" t="str">
-        <x:v>القراءات: قديمة 38
-القرآن وعلومه: قديمة 39</x:v>
+        <x:v>القراءات: جديدة 47</x:v>
       </x:c>
       <x:c r="G88" s="39" t="str">
         <x:v>6</x:v>
       </x:c>
       <x:c r="H88" s="39" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I88" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J88" s="39" t="str"/>
+      <x:c r="J88" s="39"/>
       <x:c r="K88" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L88" s="39" t="str">
-        <x:v>2001320-2||الحديث3</x:v>
+        <x:v>2002114-3||عرضالقراءاتالسبع٤</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="42" customHeight="1">
@@ -4219,37 +4208,35 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B89" s="33" t="str">
-        <x:v>2001322-2</x:v>
+        <x:v>2002238-2</x:v>
       </x:c>
       <x:c r="C89" s="39" t="str">
-        <x:v>الفقه (2)</x:v>
+        <x:v>الوقف والابتداء</x:v>
       </x:c>
       <x:c r="D89" s="39" t="str">
-        <x:v>القراءات، القرآن وعلومه</x:v>
+        <x:v>القراءات</x:v>
       </x:c>
       <x:c r="E89" s="39" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F89" s="39" t="str">
-        <x:v>القراءات: قديمة 38
-القرآن وعلومه: جديدة 47
-القرآن وعلومه: قديمة 39</x:v>
+        <x:v>القراءات: جديدة 47</x:v>
       </x:c>
       <x:c r="G89" s="39" t="str">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H89" s="39" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I89" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J89" s="39" t="str"/>
+      <x:c r="J89" s="39"/>
       <x:c r="K89" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L89" s="39" t="str">
-        <x:v>2001322-2||الفقه2</x:v>
+        <x:v>2002238-2||الوقفوالابتداء</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="42" customHeight="1">
@@ -4257,10 +4244,10 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B90" s="33" t="str">
-        <x:v>2002111-3</x:v>
+        <x:v>2002239-2</x:v>
       </x:c>
       <x:c r="C90" s="39" t="str">
-        <x:v>عرض القراءات السبع (١)</x:v>
+        <x:v>مصادر ومناهج المؤلفين في القراءات</x:v>
       </x:c>
       <x:c r="D90" s="39" t="str">
         <x:v>القراءات</x:v>
@@ -4272,7 +4259,7 @@
         <x:v>القراءات: جديدة 47</x:v>
       </x:c>
       <x:c r="G90" s="39" t="str">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H90" s="39" t="n">
         <x:v>1</x:v>
@@ -4280,12 +4267,12 @@
       <x:c r="I90" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J90" s="39" t="str"/>
+      <x:c r="J90" s="39"/>
       <x:c r="K90" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L90" s="39" t="str">
-        <x:v>2002111-3||عرضالقراءاتالسبع١</x:v>
+        <x:v>2002239-2||مصادرومناهجالمولفينفيالقراءات</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="42" customHeight="1">
@@ -4293,10 +4280,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B91" s="33" t="str">
-        <x:v>2002112-3</x:v>
+        <x:v>2002266-6</x:v>
       </x:c>
       <x:c r="C91" s="39" t="str">
-        <x:v>عرض القراءات السبع (٢)</x:v>
+        <x:v>التدريب التعاوني</x:v>
       </x:c>
       <x:c r="D91" s="39" t="str">
         <x:v>القراءات</x:v>
@@ -4308,7 +4295,7 @@
         <x:v>القراءات: جديدة 47</x:v>
       </x:c>
       <x:c r="G91" s="39" t="str">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H91" s="39" t="n">
         <x:v>1</x:v>
@@ -4316,12 +4303,12 @@
       <x:c r="I91" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J91" s="39" t="str"/>
+      <x:c r="J91" s="39"/>
       <x:c r="K91" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L91" s="39" t="str">
-        <x:v>2002112-3||عرضالقراءاتالسبع٢</x:v>
+        <x:v>2002266-6||التدريبالتعاوني</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="42" customHeight="1">
@@ -4329,10 +4316,10 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B92" s="33" t="str">
-        <x:v>2002113-3</x:v>
+        <x:v>2002280-2</x:v>
       </x:c>
       <x:c r="C92" s="39" t="str">
-        <x:v>عرض القراءات السبع (٣)</x:v>
+        <x:v>تدريبات على الجمع والكيفيات</x:v>
       </x:c>
       <x:c r="D92" s="39" t="str">
         <x:v>القراءات</x:v>
@@ -4344,7 +4331,7 @@
         <x:v>القراءات: جديدة 47</x:v>
       </x:c>
       <x:c r="G92" s="39" t="str">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H92" s="39" t="n">
         <x:v>1</x:v>
@@ -4352,12 +4339,12 @@
       <x:c r="I92" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J92" s="39" t="str"/>
+      <x:c r="J92" s="39"/>
       <x:c r="K92" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L92" s="39" t="str">
-        <x:v>2002113-3||عرضالقراءاتالسبع٣</x:v>
+        <x:v>2002280-2||تدريباتعليالجمعوالكيفيات</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="42" customHeight="1">
@@ -4365,10 +4352,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B93" s="33" t="str">
-        <x:v>2002114-3</x:v>
+        <x:v>2002352-2</x:v>
       </x:c>
       <x:c r="C93" s="39" t="str">
-        <x:v>عرض القراءات السبع (٤)</x:v>
+        <x:v>التفسير التحليلي (2)</x:v>
       </x:c>
       <x:c r="D93" s="39" t="str">
         <x:v>القراءات</x:v>
@@ -4380,7 +4367,7 @@
         <x:v>القراءات: جديدة 47</x:v>
       </x:c>
       <x:c r="G93" s="39" t="str">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H93" s="39" t="n">
         <x:v>1</x:v>
@@ -4388,12 +4375,12 @@
       <x:c r="I93" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J93" s="39" t="str"/>
+      <x:c r="J93" s="39"/>
       <x:c r="K93" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L93" s="39" t="str">
-        <x:v>2002114-3||عرضالقراءاتالسبع٤</x:v>
+        <x:v>2002352-2||التفسيرالتحليلي2</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="42" customHeight="1">
@@ -4401,10 +4388,10 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="B94" s="33" t="str">
-        <x:v>2002238-2</x:v>
+        <x:v>2002460-2</x:v>
       </x:c>
       <x:c r="C94" s="39" t="str">
-        <x:v>الوقف والابتداء</x:v>
+        <x:v>عرض القراءات الثلاث (١)</x:v>
       </x:c>
       <x:c r="D94" s="39" t="str">
         <x:v>القراءات</x:v>
@@ -4416,7 +4403,7 @@
         <x:v>القراءات: جديدة 47</x:v>
       </x:c>
       <x:c r="G94" s="39" t="str">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H94" s="39" t="n">
         <x:v>1</x:v>
@@ -4424,12 +4411,12 @@
       <x:c r="I94" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J94" s="39" t="str"/>
+      <x:c r="J94" s="39"/>
       <x:c r="K94" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L94" s="39" t="str">
-        <x:v>2002238-2||الوقفوالابتداء</x:v>
+        <x:v>2002460-2||عرضالقراءاتالثلاث١</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="42" customHeight="1">
@@ -4437,10 +4424,10 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="B95" s="33" t="str">
-        <x:v>2002239-2</x:v>
+        <x:v>2002461-2</x:v>
       </x:c>
       <x:c r="C95" s="39" t="str">
-        <x:v>مصادر ومناهج المؤلفين في القراءات</x:v>
+        <x:v>عرض القراءات الثلاث (٢)</x:v>
       </x:c>
       <x:c r="D95" s="39" t="str">
         <x:v>القراءات</x:v>
@@ -4452,7 +4439,7 @@
         <x:v>القراءات: جديدة 47</x:v>
       </x:c>
       <x:c r="G95" s="39" t="str">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H95" s="39" t="n">
         <x:v>1</x:v>
@@ -4460,12 +4447,12 @@
       <x:c r="I95" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J95" s="39" t="str"/>
+      <x:c r="J95" s="39"/>
       <x:c r="K95" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L95" s="39" t="str">
-        <x:v>2002239-2||مصادرومناهجالمولفينفيالقراءات</x:v>
+        <x:v>2002461-2||عرضالقراءاتالثلاث٢</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="42" customHeight="1">
@@ -4473,35 +4460,36 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B96" s="33" t="str">
-        <x:v>2002266-6</x:v>
+        <x:v>2004102-2</x:v>
       </x:c>
       <x:c r="C96" s="39" t="str">
-        <x:v>التدريب التعاوني</x:v>
+        <x:v>مصطلح الحديث</x:v>
       </x:c>
       <x:c r="D96" s="39" t="str">
-        <x:v>القراءات</x:v>
+        <x:v>القراءات، القرآن وعلومه</x:v>
       </x:c>
       <x:c r="E96" s="39" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F96" s="39" t="str">
-        <x:v>القراءات: جديدة 47</x:v>
+        <x:v>القراءات: جديدة 47
+القرآن وعلومه: جديدة 47</x:v>
       </x:c>
       <x:c r="G96" s="39" t="str">
-        <x:v>8</x:v>
+        <x:v>2، 3</x:v>
       </x:c>
       <x:c r="H96" s="39" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I96" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J96" s="39" t="str"/>
+      <x:c r="J96" s="39"/>
       <x:c r="K96" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L96" s="39" t="str">
-        <x:v>2002266-6||التدريبالتعاوني</x:v>
+        <x:v>2004102-2||مصطلحالحديث</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="42" customHeight="1">
@@ -4509,35 +4497,36 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B97" s="33" t="str">
-        <x:v>2002280-2</x:v>
+        <x:v>2004205-2</x:v>
       </x:c>
       <x:c r="C97" s="39" t="str">
-        <x:v>تدريبات على الجمع والكيفيات</x:v>
+        <x:v>الحديث (1)</x:v>
       </x:c>
       <x:c r="D97" s="39" t="str">
-        <x:v>القراءات</x:v>
+        <x:v>القراءات، القرآن وعلومه</x:v>
       </x:c>
       <x:c r="E97" s="39" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F97" s="39" t="str">
-        <x:v>القراءات: جديدة 47</x:v>
+        <x:v>القراءات: جديدة 47
+القرآن وعلومه: جديدة 47</x:v>
       </x:c>
       <x:c r="G97" s="39" t="str">
-        <x:v>3</x:v>
+        <x:v>3، 4</x:v>
       </x:c>
       <x:c r="H97" s="39" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I97" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J97" s="39" t="str"/>
+      <x:c r="J97" s="39"/>
       <x:c r="K97" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L97" s="39" t="str">
-        <x:v>2002280-2||تدريباتعليالجمعوالكيفيات</x:v>
+        <x:v>2004205-2||الحديث1</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="42" customHeight="1">
@@ -4545,35 +4534,36 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B98" s="33" t="str">
-        <x:v>2002352-2</x:v>
+        <x:v>2004209-2</x:v>
       </x:c>
       <x:c r="C98" s="39" t="str">
-        <x:v>التفسير التحليلي (2)</x:v>
+        <x:v>الحديث (2)</x:v>
       </x:c>
       <x:c r="D98" s="39" t="str">
-        <x:v>القراءات</x:v>
+        <x:v>القراءات، القرآن وعلومه</x:v>
       </x:c>
       <x:c r="E98" s="39" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F98" s="39" t="str">
-        <x:v>القراءات: جديدة 47</x:v>
+        <x:v>القراءات: جديدة 47
+القرآن وعلومه: جديدة 47</x:v>
       </x:c>
       <x:c r="G98" s="39" t="str">
-        <x:v>4</x:v>
+        <x:v>4، 5</x:v>
       </x:c>
       <x:c r="H98" s="39" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I98" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J98" s="39" t="str"/>
+      <x:c r="J98" s="39"/>
       <x:c r="K98" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L98" s="39" t="str">
-        <x:v>2002352-2||التفسيرالتحليلي2</x:v>
+        <x:v>2004209-2||الحديث2</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="42" customHeight="1">
@@ -4581,35 +4571,36 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B99" s="33" t="str">
-        <x:v>2002460-2</x:v>
+        <x:v>2004320-2</x:v>
       </x:c>
       <x:c r="C99" s="39" t="str">
-        <x:v>عرض القراءات الثلاث (١)</x:v>
+        <x:v>الحديث (3)</x:v>
       </x:c>
       <x:c r="D99" s="39" t="str">
-        <x:v>القراءات</x:v>
+        <x:v>القراءات، القرآن وعلومه</x:v>
       </x:c>
       <x:c r="E99" s="39" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F99" s="39" t="str">
-        <x:v>القراءات: جديدة 47</x:v>
+        <x:v>القراءات: جديدة 47
+القرآن وعلومه: جديدة 47</x:v>
       </x:c>
       <x:c r="G99" s="39" t="str">
-        <x:v>7</x:v>
+        <x:v>5، 6</x:v>
       </x:c>
       <x:c r="H99" s="39" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I99" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J99" s="39" t="str"/>
+      <x:c r="J99" s="39"/>
       <x:c r="K99" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L99" s="39" t="str">
-        <x:v>2002460-2||عرضالقراءاتالثلاث١</x:v>
+        <x:v>2004320-2||الحديث3</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="42" customHeight="1">
@@ -4617,35 +4608,36 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="B100" s="33" t="str">
-        <x:v>2002461-2</x:v>
+        <x:v>2004403-2</x:v>
       </x:c>
       <x:c r="C100" s="39" t="str">
-        <x:v>عرض القراءات الثلاث (٢)</x:v>
+        <x:v>الأديان والفرق والمذاهب المعاصرة</x:v>
       </x:c>
       <x:c r="D100" s="39" t="str">
-        <x:v>القراءات</x:v>
+        <x:v>القراءات، القرآن وعلومه</x:v>
       </x:c>
       <x:c r="E100" s="39" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F100" s="39" t="str">
-        <x:v>القراءات: جديدة 47</x:v>
+        <x:v>القراءات: جديدة 47
+القرآن وعلومه: جديدة 47</x:v>
       </x:c>
       <x:c r="G100" s="39" t="str">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H100" s="39" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I100" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J100" s="39" t="str"/>
+      <x:c r="J100" s="39"/>
       <x:c r="K100" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L100" s="39" t="str">
-        <x:v>2002461-2||عرضالقراءاتالثلاث٢</x:v>
+        <x:v>2004403-2||الاديانوالفرقوالمذاهبالمعاصرة</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="42" customHeight="1">
@@ -4653,36 +4645,35 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B101" s="33" t="str">
-        <x:v>2004102-2</x:v>
+        <x:v>101221-2</x:v>
       </x:c>
       <x:c r="C101" s="39" t="str">
-        <x:v>مصطلح الحديث</x:v>
+        <x:v>الفقه (1)</x:v>
       </x:c>
       <x:c r="D101" s="39" t="str">
-        <x:v>القراءات، القرآن وعلومه</x:v>
+        <x:v>القرآن وعلومه</x:v>
       </x:c>
       <x:c r="E101" s="39" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F101" s="39" t="str">
-        <x:v>القراءات: جديدة 47
-القرآن وعلومه: جديدة 47</x:v>
+        <x:v>القرآن وعلومه: قديمة 39</x:v>
       </x:c>
       <x:c r="G101" s="39" t="str">
-        <x:v>2، 3</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H101" s="39" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I101" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J101" s="39" t="str"/>
+      <x:c r="J101" s="39"/>
       <x:c r="K101" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L101" s="39" t="str">
-        <x:v>2004102-2||مصطلحالحديث</x:v>
+        <x:v>101221-2||الفقه1</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="42" customHeight="1">
@@ -4690,36 +4681,35 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B102" s="33" t="str">
-        <x:v>2004205-2</x:v>
+        <x:v>2001160-2</x:v>
       </x:c>
       <x:c r="C102" s="39" t="str">
-        <x:v>الحديث (1)</x:v>
+        <x:v>المدخل لدراسة الشريعة</x:v>
       </x:c>
       <x:c r="D102" s="39" t="str">
-        <x:v>القراءات، القرآن وعلومه</x:v>
+        <x:v>القرآن وعلومه</x:v>
       </x:c>
       <x:c r="E102" s="39" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F102" s="39" t="str">
-        <x:v>القراءات: جديدة 47
-القرآن وعلومه: جديدة 47</x:v>
+        <x:v>القرآن وعلومه: قديمة 39</x:v>
       </x:c>
       <x:c r="G102" s="39" t="str">
-        <x:v>3، 4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H102" s="39" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I102" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J102" s="39" t="str"/>
+      <x:c r="J102" s="39"/>
       <x:c r="K102" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L102" s="39" t="str">
-        <x:v>2004205-2||الحديث1</x:v>
+        <x:v>2001160-2||المدخللدراسةالشريعة</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="42" customHeight="1">
@@ -4727,23 +4717,23 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="B103" s="33" t="str">
-        <x:v>2004209-2</x:v>
+        <x:v>2001317-2</x:v>
       </x:c>
       <x:c r="C103" s="39" t="str">
-        <x:v>الحديث (2)</x:v>
+        <x:v>الفقه (3)</x:v>
       </x:c>
       <x:c r="D103" s="39" t="str">
-        <x:v>القراءات، القرآن وعلومه</x:v>
+        <x:v>القرآن وعلومه</x:v>
       </x:c>
       <x:c r="E103" s="39" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F103" s="39" t="str">
-        <x:v>القراءات: جديدة 47
-القرآن وعلومه: جديدة 47</x:v>
+        <x:v>القرآن وعلومه: جديدة 47
+القرآن وعلومه: قديمة 39</x:v>
       </x:c>
       <x:c r="G103" s="39" t="str">
-        <x:v>4، 5</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H103" s="39" t="n">
         <x:v>2</x:v>
@@ -4751,12 +4741,12 @@
       <x:c r="I103" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J103" s="39" t="str"/>
+      <x:c r="J103" s="39"/>
       <x:c r="K103" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L103" s="39" t="str">
-        <x:v>2004209-2||الحديث2</x:v>
+        <x:v>2001317-2||الفقه3</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="42" customHeight="1">
@@ -4764,36 +4754,35 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B104" s="33" t="str">
-        <x:v>2004320-2</x:v>
+        <x:v>2001424-2</x:v>
       </x:c>
       <x:c r="C104" s="39" t="str">
-        <x:v>الحديث (3)</x:v>
+        <x:v>الفقه (4)</x:v>
       </x:c>
       <x:c r="D104" s="39" t="str">
-        <x:v>القراءات، القرآن وعلومه</x:v>
+        <x:v>القرآن وعلومه</x:v>
       </x:c>
       <x:c r="E104" s="39" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F104" s="39" t="str">
-        <x:v>القراءات: جديدة 47
-القرآن وعلومه: جديدة 47</x:v>
+        <x:v>القرآن وعلومه: قديمة 39</x:v>
       </x:c>
       <x:c r="G104" s="39" t="str">
-        <x:v>5، 6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H104" s="39" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I104" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J104" s="39" t="str"/>
+      <x:c r="J104" s="39"/>
       <x:c r="K104" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L104" s="39" t="str">
-        <x:v>2004320-2||الحديث3</x:v>
+        <x:v>2001424-2||الفقه4</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="42" customHeight="1">
@@ -4801,36 +4790,35 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B105" s="33" t="str">
-        <x:v>2004403-2</x:v>
+        <x:v>2002266-5</x:v>
       </x:c>
       <x:c r="C105" s="39" t="str">
-        <x:v>الأديان والفرق والمذاهب المعاصرة</x:v>
+        <x:v>التدريب التعاوني</x:v>
       </x:c>
       <x:c r="D105" s="39" t="str">
-        <x:v>القراءات، القرآن وعلومه</x:v>
+        <x:v>القرآن وعلومه</x:v>
       </x:c>
       <x:c r="E105" s="39" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F105" s="39" t="str">
-        <x:v>القراءات: جديدة 47
-القرآن وعلومه: جديدة 47</x:v>
+        <x:v>القرآن وعلومه: جديدة 47</x:v>
       </x:c>
       <x:c r="G105" s="39" t="str">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H105" s="39" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I105" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J105" s="39" t="str"/>
+      <x:c r="J105" s="39"/>
       <x:c r="K105" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L105" s="39" t="str">
-        <x:v>2004403-2||الاديانوالفرقوالمذاهبالمعاصرة</x:v>
+        <x:v>2002266-5||التدريبالتعاوني</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="42" customHeight="1">
@@ -4838,10 +4826,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B106" s="33" t="str">
-        <x:v>101221-2</x:v>
+        <x:v>20024101-2</x:v>
       </x:c>
       <x:c r="C106" s="39" t="str">
-        <x:v>الفقه (1)</x:v>
+        <x:v>قاعة بحث</x:v>
       </x:c>
       <x:c r="D106" s="39" t="str">
         <x:v>القرآن وعلومه</x:v>
@@ -4850,10 +4838,10 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="F106" s="39" t="str">
-        <x:v>القرآن وعلومه: قديمة 39</x:v>
+        <x:v>القرآن وعلومه: جديدة 47</x:v>
       </x:c>
       <x:c r="G106" s="39" t="str">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H106" s="39" t="n">
         <x:v>1</x:v>
@@ -4861,194 +4849,83 @@
       <x:c r="I106" s="39" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="J106" s="39" t="str"/>
+      <x:c r="J106" s="39"/>
       <x:c r="K106" s="39" t="str">
         <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
       </x:c>
       <x:c r="L106" s="39" t="str">
-        <x:v>101221-2||الفقه1</x:v>
+        <x:v>20024101-2||قاعةبحث</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="42" customHeight="1">
-      <x:c r="A107" s="33" t="n">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="B107" s="33" t="str">
-        <x:v>2001160-2</x:v>
-      </x:c>
-      <x:c r="C107" s="39" t="str">
-        <x:v>المدخل لدراسة الشريعة</x:v>
-      </x:c>
-      <x:c r="D107" s="39" t="str">
-        <x:v>القرآن وعلومه</x:v>
-      </x:c>
-      <x:c r="E107" s="39" t="str">
-        <x:v>بكالوريوس</x:v>
-      </x:c>
-      <x:c r="F107" s="39" t="str">
-        <x:v>القرآن وعلومه: قديمة 39</x:v>
-      </x:c>
-      <x:c r="G107" s="39" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H107" s="39" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I107" s="39" t="str">
-        <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
-      </x:c>
-      <x:c r="J107" s="39" t="str"/>
-      <x:c r="K107" s="39" t="str">
-        <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
-      </x:c>
-      <x:c r="L107" s="39" t="str">
-        <x:v>2001160-2||المدخللدراسةالشريعة</x:v>
-      </x:c>
+      <x:c r="A107" s="33"/>
+      <x:c r="B107" s="33"/>
+      <x:c r="C107" s="39"/>
+      <x:c r="D107" s="39"/>
+      <x:c r="E107" s="39"/>
+      <x:c r="F107" s="39"/>
+      <x:c r="G107" s="39"/>
+      <x:c r="H107" s="39"/>
+      <x:c r="I107" s="39"/>
+      <x:c r="J107" s="39"/>
+      <x:c r="K107" s="39"/>
+      <x:c r="L107" s="39"/>
     </x:row>
     <x:row r="108" ht="42" customHeight="1">
-      <x:c r="A108" s="33" t="n">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="B108" s="33" t="str">
-        <x:v>2001317-2</x:v>
-      </x:c>
-      <x:c r="C108" s="39" t="str">
-        <x:v>الفقه (3)</x:v>
-      </x:c>
-      <x:c r="D108" s="39" t="str">
-        <x:v>القرآن وعلومه</x:v>
-      </x:c>
-      <x:c r="E108" s="39" t="str">
-        <x:v>بكالوريوس</x:v>
-      </x:c>
-      <x:c r="F108" s="39" t="str">
-        <x:v>القرآن وعلومه: جديدة 47
-القرآن وعلومه: قديمة 39</x:v>
-      </x:c>
-      <x:c r="G108" s="39" t="str">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H108" s="39" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I108" s="39" t="str">
-        <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
-      </x:c>
-      <x:c r="J108" s="39" t="str"/>
-      <x:c r="K108" s="39" t="str">
-        <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
-      </x:c>
-      <x:c r="L108" s="39" t="str">
-        <x:v>2001317-2||الفقه3</x:v>
-      </x:c>
+      <x:c r="A108" s="33"/>
+      <x:c r="B108" s="33"/>
+      <x:c r="C108" s="39"/>
+      <x:c r="D108" s="39"/>
+      <x:c r="E108" s="39"/>
+      <x:c r="F108" s="39"/>
+      <x:c r="G108" s="39"/>
+      <x:c r="H108" s="39"/>
+      <x:c r="I108" s="39"/>
+      <x:c r="J108" s="39"/>
+      <x:c r="K108" s="39"/>
+      <x:c r="L108" s="39"/>
     </x:row>
     <x:row r="109" ht="42" customHeight="1">
-      <x:c r="A109" s="33" t="n">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="B109" s="33" t="str">
-        <x:v>2001424-2</x:v>
-      </x:c>
-      <x:c r="C109" s="39" t="str">
-        <x:v>الفقه (4)</x:v>
-      </x:c>
-      <x:c r="D109" s="39" t="str">
-        <x:v>القرآن وعلومه</x:v>
-      </x:c>
-      <x:c r="E109" s="39" t="str">
-        <x:v>بكالوريوس</x:v>
-      </x:c>
-      <x:c r="F109" s="39" t="str">
-        <x:v>القرآن وعلومه: قديمة 39</x:v>
-      </x:c>
-      <x:c r="G109" s="39" t="str">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H109" s="39" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I109" s="39" t="str">
-        <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
-      </x:c>
-      <x:c r="J109" s="39" t="str"/>
-      <x:c r="K109" s="39" t="str">
-        <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
-      </x:c>
-      <x:c r="L109" s="39" t="str">
-        <x:v>2001424-2||الفقه4</x:v>
-      </x:c>
+      <x:c r="A109" s="33"/>
+      <x:c r="B109" s="33"/>
+      <x:c r="C109" s="39"/>
+      <x:c r="D109" s="39"/>
+      <x:c r="E109" s="39"/>
+      <x:c r="F109" s="39"/>
+      <x:c r="G109" s="39"/>
+      <x:c r="H109" s="39"/>
+      <x:c r="I109" s="39"/>
+      <x:c r="J109" s="39"/>
+      <x:c r="K109" s="39"/>
+      <x:c r="L109" s="39"/>
     </x:row>
     <x:row r="110" ht="42" customHeight="1">
-      <x:c r="A110" s="33" t="n">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="B110" s="33" t="str">
-        <x:v>2002266-5</x:v>
-      </x:c>
-      <x:c r="C110" s="39" t="str">
-        <x:v>التدريب التعاوني</x:v>
-      </x:c>
-      <x:c r="D110" s="39" t="str">
-        <x:v>القرآن وعلومه</x:v>
-      </x:c>
-      <x:c r="E110" s="39" t="str">
-        <x:v>بكالوريوس</x:v>
-      </x:c>
-      <x:c r="F110" s="39" t="str">
-        <x:v>القرآن وعلومه: جديدة 47</x:v>
-      </x:c>
-      <x:c r="G110" s="39" t="str">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H110" s="39" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I110" s="39" t="str">
-        <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
-      </x:c>
-      <x:c r="J110" s="39" t="str"/>
-      <x:c r="K110" s="39" t="str">
-        <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
-      </x:c>
-      <x:c r="L110" s="39" t="str">
-        <x:v>2002266-5||التدريبالتعاوني</x:v>
-      </x:c>
+      <x:c r="A110" s="33"/>
+      <x:c r="B110" s="33"/>
+      <x:c r="C110" s="39"/>
+      <x:c r="D110" s="39"/>
+      <x:c r="E110" s="39"/>
+      <x:c r="F110" s="39"/>
+      <x:c r="G110" s="39"/>
+      <x:c r="H110" s="39"/>
+      <x:c r="I110" s="39"/>
+      <x:c r="J110" s="39"/>
+      <x:c r="K110" s="39"/>
+      <x:c r="L110" s="39"/>
     </x:row>
     <x:row r="111" ht="42" customHeight="1">
-      <x:c r="A111" s="33" t="n">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="B111" s="33" t="str">
-        <x:v>20024101-2</x:v>
-      </x:c>
-      <x:c r="C111" s="39" t="str">
-        <x:v>قاعة بحث</x:v>
-      </x:c>
-      <x:c r="D111" s="39" t="str">
-        <x:v>القرآن وعلومه</x:v>
-      </x:c>
-      <x:c r="E111" s="39" t="str">
-        <x:v>بكالوريوس</x:v>
-      </x:c>
-      <x:c r="F111" s="39" t="str">
-        <x:v>القرآن وعلومه: جديدة 47</x:v>
-      </x:c>
-      <x:c r="G111" s="39" t="str">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H111" s="39" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I111" s="39" t="str">
-        <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
-      </x:c>
-      <x:c r="J111" s="39" t="str"/>
-      <x:c r="K111" s="39" t="str">
-        <x:v>الحصول على توصيف صالح، ثم التحقق من الهوية وربط مخرجات كل برنامج على حدة</x:v>
-      </x:c>
-      <x:c r="L111" s="39" t="str">
-        <x:v>20024101-2||قاعةبحث</x:v>
-      </x:c>
+      <x:c r="A111" s="33"/>
+      <x:c r="B111" s="33"/>
+      <x:c r="C111" s="39"/>
+      <x:c r="D111" s="39"/>
+      <x:c r="E111" s="39"/>
+      <x:c r="F111" s="39"/>
+      <x:c r="G111" s="39"/>
+      <x:c r="H111" s="39"/>
+      <x:c r="I111" s="39"/>
+      <x:c r="J111" s="39"/>
+      <x:c r="K111" s="39"/>
+      <x:c r="L111" s="39"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5057,7 +4934,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08a623ea69fc4e93"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47649aa9885d4953"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5093,7 +4970,7 @@
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
       <x:c r="A3" s="6" t="str">
-        <x:v>عدد المواضع: 140. كل صف يمثل ظهور مقرر في برنامج وخطة وإصدار محدد.</x:v>
+        <x:v>عدد المواضع: 131. كل صف يمثل ظهور مقرر في برنامج وخطة وإصدار محدد.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -5200,7 +5077,7 @@
       <x:c r="M6" s="40" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N6" s="40" t="str"/>
+      <x:c r="N6" s="40"/>
       <x:c r="O6" s="40" t="str">
         <x:v>2003114-3||القانونالدستوري</x:v>
       </x:c>
@@ -5245,7 +5122,7 @@
       <x:c r="M7" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N7" s="42" t="str"/>
+      <x:c r="N7" s="42"/>
       <x:c r="O7" s="42" t="str">
         <x:v>2003228-3||القانونالمالي</x:v>
       </x:c>
@@ -5290,7 +5167,7 @@
       <x:c r="M8" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N8" s="42" t="str"/>
+      <x:c r="N8" s="42"/>
       <x:c r="O8" s="42" t="str">
         <x:v>2003229-3||تحليلالنصوصالقانونية</x:v>
       </x:c>
@@ -5335,7 +5212,7 @@
       <x:c r="M9" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N9" s="42" t="str"/>
+      <x:c r="N9" s="42"/>
       <x:c r="O9" s="42" t="str">
         <x:v>2003383-3||المحاماةواخلاقياتالمهنة</x:v>
       </x:c>
@@ -5380,7 +5257,7 @@
       <x:c r="M10" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N10" s="42" t="str"/>
+      <x:c r="N10" s="42"/>
       <x:c r="O10" s="42" t="str">
         <x:v>2003204-3||الكاديميةالقانونيةالكتابة</x:v>
       </x:c>
@@ -5425,7 +5302,7 @@
       <x:c r="M11" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N11" s="42" t="str"/>
+      <x:c r="N11" s="42"/>
       <x:c r="O11" s="42" t="str">
         <x:v>2003205-3||العقودالتجاريةالدولية</x:v>
       </x:c>
@@ -5470,7 +5347,7 @@
       <x:c r="M12" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N12" s="42" t="str"/>
+      <x:c r="N12" s="42"/>
       <x:c r="O12" s="42" t="str">
         <x:v>20033201-2||القانونالدبلوماسيوالقنصلي</x:v>
       </x:c>
@@ -5515,7 +5392,7 @@
       <x:c r="M13" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N13" s="42" t="str"/>
+      <x:c r="N13" s="42"/>
       <x:c r="O13" s="42" t="str">
         <x:v>2003102-3||قانونالعملوالتاميناتالاجتماعية</x:v>
       </x:c>
@@ -5560,7 +5437,7 @@
       <x:c r="M14" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N14" s="42" t="str"/>
+      <x:c r="N14" s="42"/>
       <x:c r="O14" s="42" t="str">
         <x:v>2003103-3||الكتابةالمهنيةالقانونية</x:v>
       </x:c>
@@ -5605,7 +5482,7 @@
       <x:c r="M15" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N15" s="42" t="str"/>
+      <x:c r="N15" s="42"/>
       <x:c r="O15" s="42" t="str">
         <x:v>2003106-3||تدريباتقانونية١</x:v>
       </x:c>
@@ -5650,7 +5527,7 @@
       <x:c r="M16" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N16" s="42" t="str"/>
+      <x:c r="N16" s="42"/>
       <x:c r="O16" s="42" t="str">
         <x:v>2003107-3||تدريباتقانونية٢</x:v>
       </x:c>
@@ -5695,7 +5572,7 @@
       <x:c r="M17" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N17" s="42" t="str"/>
+      <x:c r="N17" s="42"/>
       <x:c r="O17" s="42" t="str">
         <x:v>2003108-2||قانونالتحكيم</x:v>
       </x:c>
@@ -5740,7 +5617,7 @@
       <x:c r="M18" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N18" s="42" t="str"/>
+      <x:c r="N18" s="42"/>
       <x:c r="O18" s="42" t="str">
         <x:v>20034202-2||القانونالصحي</x:v>
       </x:c>
@@ -5785,7 +5662,7 @@
       <x:c r="M19" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N19" s="42" t="str"/>
+      <x:c r="N19" s="42"/>
       <x:c r="O19" s="42" t="str">
         <x:v>2001105-2||المدخللدراسةالفقهالاسلامي</x:v>
       </x:c>
@@ -5830,7 +5707,7 @@
       <x:c r="M20" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N20" s="42" t="str"/>
+      <x:c r="N20" s="42"/>
       <x:c r="O20" s="42" t="str">
         <x:v>2001113-2||اصولالفقه1</x:v>
       </x:c>
@@ -5875,7 +5752,7 @@
       <x:c r="M21" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N21" s="42" t="str"/>
+      <x:c r="N21" s="42"/>
       <x:c r="O21" s="42" t="str">
         <x:v>2001328-2||القواعدالفقهية</x:v>
       </x:c>
@@ -5920,7 +5797,7 @@
       <x:c r="M22" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N22" s="42" t="str"/>
+      <x:c r="N22" s="42"/>
       <x:c r="O22" s="42" t="str">
         <x:v>2001330-2||اصولالفقه2</x:v>
       </x:c>
@@ -5965,7 +5842,7 @@
       <x:c r="M23" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N23" s="42" t="str"/>
+      <x:c r="N23" s="42"/>
       <x:c r="O23" s="42" t="str">
         <x:v>2001318-3||فقهالجنايات</x:v>
       </x:c>
@@ -6010,7 +5887,7 @@
       <x:c r="M24" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N24" s="42" t="str"/>
+      <x:c r="N24" s="42"/>
       <x:c r="O24" s="42" t="str">
         <x:v>2001327-3||فقهالاحوالالشخصية</x:v>
       </x:c>
@@ -6055,7 +5932,7 @@
       <x:c r="M25" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N25" s="42" t="str"/>
+      <x:c r="N25" s="42"/>
       <x:c r="O25" s="42" t="str">
         <x:v>2001220-3||فقهالمعاملات</x:v>
       </x:c>
@@ -6100,7 +5977,7 @@
       <x:c r="M26" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N26" s="42" t="str"/>
+      <x:c r="N26" s="42"/>
       <x:c r="O26" s="42" t="str">
         <x:v>2003255-3||الملكيةالفكرية</x:v>
       </x:c>
@@ -6145,7 +6022,7 @@
       <x:c r="M27" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N27" s="42" t="str"/>
+      <x:c r="N27" s="42"/>
       <x:c r="O27" s="42" t="str">
         <x:v>2001401-2||المواريثوالوصايا</x:v>
       </x:c>
@@ -6190,7 +6067,7 @@
       <x:c r="M28" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N28" s="42" t="str"/>
+      <x:c r="N28" s="42"/>
       <x:c r="O28" s="42" t="str">
         <x:v>2003402-2||مادةاختياريةللقسم</x:v>
       </x:c>
@@ -6235,7 +6112,7 @@
       <x:c r="M29" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N29" s="42" t="str"/>
+      <x:c r="N29" s="42"/>
       <x:c r="O29" s="42" t="str">
         <x:v>2004252-4||الحديثالتحليلي1</x:v>
       </x:c>
@@ -6280,7 +6157,7 @@
       <x:c r="M30" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N30" s="42" t="str"/>
+      <x:c r="N30" s="42"/>
       <x:c r="O30" s="42" t="str">
         <x:v>2001301-3||الفقه1</x:v>
       </x:c>
@@ -6305,13 +6182,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G31" s="43" t="str">
-        <x:v>2002202-2</x:v>
+        <x:v>2004211-4</x:v>
       </x:c>
       <x:c r="H31" s="42" t="str">
-        <x:v>القرآن الكريم (2)</x:v>
+        <x:v>العقيدة (1)</x:v>
       </x:c>
       <x:c r="I31" s="43" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J31" s="42" t="str">
         <x:v>نظري</x:v>
@@ -6325,9 +6202,9 @@
       <x:c r="M31" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N31" s="42" t="str"/>
+      <x:c r="N31" s="42"/>
       <x:c r="O31" s="42" t="str">
-        <x:v>2002202-2||القرانالكريم2</x:v>
+        <x:v>2004211-4||العقيدة1</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="34" customHeight="1">
@@ -6347,16 +6224,16 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="F32" s="43" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G32" s="43" t="str">
-        <x:v>2004211-4</x:v>
+        <x:v>2001302-3</x:v>
       </x:c>
       <x:c r="H32" s="42" t="str">
-        <x:v>العقيدة (1)</x:v>
+        <x:v>الفقه (٢)</x:v>
       </x:c>
       <x:c r="I32" s="43" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J32" s="42" t="str">
         <x:v>نظري</x:v>
@@ -6370,9 +6247,9 @@
       <x:c r="M32" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N32" s="42" t="str"/>
+      <x:c r="N32" s="42"/>
       <x:c r="O32" s="42" t="str">
-        <x:v>2004211-4||العقيدة1</x:v>
+        <x:v>2001302-3||الفقه٢</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="34" customHeight="1">
@@ -6395,13 +6272,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G33" s="43" t="str">
-        <x:v>2001302-3</x:v>
+        <x:v>2004256-2</x:v>
       </x:c>
       <x:c r="H33" s="42" t="str">
-        <x:v>الفقه (٢)</x:v>
+        <x:v>الحديث التحليلي (٢)</x:v>
       </x:c>
       <x:c r="I33" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J33" s="42" t="str">
         <x:v>نظري</x:v>
@@ -6415,9 +6292,9 @@
       <x:c r="M33" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N33" s="42" t="str"/>
+      <x:c r="N33" s="42"/>
       <x:c r="O33" s="42" t="str">
-        <x:v>2001302-3||الفقه٢</x:v>
+        <x:v>2004256-2||الحديثالتحليلي٢</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="34" customHeight="1">
@@ -6440,10 +6317,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G34" s="43" t="str">
-        <x:v>2004256-2</x:v>
+        <x:v>20042111-2</x:v>
       </x:c>
       <x:c r="H34" s="42" t="str">
-        <x:v>الحديث التحليلي (٢)</x:v>
+        <x:v>العقيدة (٢)</x:v>
       </x:c>
       <x:c r="I34" s="43" t="n">
         <x:v>2</x:v>
@@ -6460,9 +6337,9 @@
       <x:c r="M34" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N34" s="42" t="str"/>
+      <x:c r="N34" s="42"/>
       <x:c r="O34" s="42" t="str">
-        <x:v>2004256-2||الحديثالتحليلي٢</x:v>
+        <x:v>20042111-2||العقيدة٢</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="34" customHeight="1">
@@ -6482,16 +6359,16 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="F35" s="43" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G35" s="43" t="str">
+        <x:v>2001265-3</x:v>
+      </x:c>
+      <x:c r="H35" s="42" t="str">
+        <x:v>الفقه (٣)</x:v>
+      </x:c>
+      <x:c r="I35" s="43" t="n">
         <x:v>3</x:v>
-      </x:c>
-      <x:c r="G35" s="43" t="str">
-        <x:v>20042111-2</x:v>
-      </x:c>
-      <x:c r="H35" s="42" t="str">
-        <x:v>العقيدة (٢)</x:v>
-      </x:c>
-      <x:c r="I35" s="43" t="n">
-        <x:v>2</x:v>
       </x:c>
       <x:c r="J35" s="42" t="str">
         <x:v>نظري</x:v>
@@ -6505,9 +6382,9 @@
       <x:c r="M35" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N35" s="42" t="str"/>
+      <x:c r="N35" s="42"/>
       <x:c r="O35" s="42" t="str">
-        <x:v>20042111-2||العقيدة٢</x:v>
+        <x:v>2001265-3||الفقه٣</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="34" customHeight="1">
@@ -6530,13 +6407,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="G36" s="43" t="str">
-        <x:v>2001265-3</x:v>
+        <x:v>2004305-4</x:v>
       </x:c>
       <x:c r="H36" s="42" t="str">
-        <x:v>الفقه (٣)</x:v>
+        <x:v>أحاديث الأحكام (١)</x:v>
       </x:c>
       <x:c r="I36" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J36" s="42" t="str">
         <x:v>نظري</x:v>
@@ -6550,9 +6427,9 @@
       <x:c r="M36" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N36" s="42" t="str"/>
+      <x:c r="N36" s="42"/>
       <x:c r="O36" s="42" t="str">
-        <x:v>2001265-3||الفقه٣</x:v>
+        <x:v>2004305-4||احاديثالاحكام١</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="34" customHeight="1">
@@ -6572,16 +6449,16 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="F37" s="43" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G37" s="43" t="str">
-        <x:v>2004305-4</x:v>
+        <x:v>2002228-2</x:v>
       </x:c>
       <x:c r="H37" s="42" t="str">
-        <x:v>أحاديث الأحكام (١)</x:v>
+        <x:v>القرآن الكريم (٥)</x:v>
       </x:c>
       <x:c r="I37" s="43" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J37" s="42" t="str">
         <x:v>نظري</x:v>
@@ -6595,9 +6472,9 @@
       <x:c r="M37" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N37" s="42" t="str"/>
+      <x:c r="N37" s="42"/>
       <x:c r="O37" s="42" t="str">
-        <x:v>2004305-4||احاديثالاحكام١</x:v>
+        <x:v>2002228-2||القرانالكريم٥</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="34" customHeight="1">
@@ -6620,10 +6497,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G38" s="43" t="str">
-        <x:v>2002228-2</x:v>
+        <x:v>2004262-2</x:v>
       </x:c>
       <x:c r="H38" s="42" t="str">
-        <x:v>القرآن الكريم (٥)</x:v>
+        <x:v>الدعوة والحسبة</x:v>
       </x:c>
       <x:c r="I38" s="43" t="n">
         <x:v>2</x:v>
@@ -6640,9 +6517,9 @@
       <x:c r="M38" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N38" s="42" t="str"/>
+      <x:c r="N38" s="42"/>
       <x:c r="O38" s="42" t="str">
-        <x:v>2002228-2||القرانالكريم٥</x:v>
+        <x:v>2004262-2||الدعوةوالحسبة</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="34" customHeight="1">
@@ -6665,13 +6542,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G39" s="43" t="str">
-        <x:v>2004262-2</x:v>
+        <x:v>20013101-3</x:v>
       </x:c>
       <x:c r="H39" s="42" t="str">
-        <x:v>الدعوة والحسبة</x:v>
+        <x:v>الفقه (٤)</x:v>
       </x:c>
       <x:c r="I39" s="43" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J39" s="42" t="str">
         <x:v>نظري</x:v>
@@ -6685,9 +6562,9 @@
       <x:c r="M39" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N39" s="42" t="str"/>
+      <x:c r="N39" s="42"/>
       <x:c r="O39" s="42" t="str">
-        <x:v>2004262-2||الدعوةوالحسبة</x:v>
+        <x:v>20013101-3||الفقه٤</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="34" customHeight="1">
@@ -6710,19 +6587,19 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G40" s="43" t="str">
-        <x:v>20013101-3</x:v>
+        <x:v>20043109-2</x:v>
       </x:c>
       <x:c r="H40" s="42" t="str">
-        <x:v>الفقه (٤)</x:v>
+        <x:v>دراسات في سير السلف</x:v>
       </x:c>
       <x:c r="I40" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J40" s="42" t="str">
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K40" s="42" t="str">
-        <x:v>إجبارية القسم</x:v>
+        <x:v>اختيارية القسم</x:v>
       </x:c>
       <x:c r="L40" s="42" t="str">
         <x:v>الإسلامية 47.pdf</x:v>
@@ -6730,9 +6607,9 @@
       <x:c r="M40" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N40" s="42" t="str"/>
+      <x:c r="N40" s="42"/>
       <x:c r="O40" s="42" t="str">
-        <x:v>20013101-3||الفقه٤</x:v>
+        <x:v>20043109-2||دراساتفيسيرالسلف</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="34" customHeight="1">
@@ -6755,10 +6632,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G41" s="43" t="str">
-        <x:v>20043109-2</x:v>
+        <x:v>20043110-2</x:v>
       </x:c>
       <x:c r="H41" s="42" t="str">
-        <x:v>دراسات في سير السلف</x:v>
+        <x:v>محاسن الإسلام</x:v>
       </x:c>
       <x:c r="I41" s="43" t="n">
         <x:v>2</x:v>
@@ -6775,9 +6652,9 @@
       <x:c r="M41" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N41" s="42" t="str"/>
+      <x:c r="N41" s="42"/>
       <x:c r="O41" s="42" t="str">
-        <x:v>20043109-2||دراساتفيسيرالسلف</x:v>
+        <x:v>20043110-2||محاسنالاسلام</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="34" customHeight="1">
@@ -6797,13 +6674,13 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="F42" s="43" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G42" s="43" t="str">
-        <x:v>20043110-2</x:v>
+        <x:v>2002229-2</x:v>
       </x:c>
       <x:c r="H42" s="42" t="str">
-        <x:v>محاسن الإسلام</x:v>
+        <x:v>القرآن الكريم (٦)</x:v>
       </x:c>
       <x:c r="I42" s="43" t="n">
         <x:v>2</x:v>
@@ -6812,7 +6689,7 @@
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K42" s="42" t="str">
-        <x:v>اختيارية القسم</x:v>
+        <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L42" s="42" t="str">
         <x:v>الإسلامية 47.pdf</x:v>
@@ -6820,9 +6697,9 @@
       <x:c r="M42" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N42" s="42" t="str"/>
+      <x:c r="N42" s="42"/>
       <x:c r="O42" s="42" t="str">
-        <x:v>20043110-2||محاسنالاسلام</x:v>
+        <x:v>2002229-2||القرانالكريم٦</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="34" customHeight="1">
@@ -6845,13 +6722,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G43" s="43" t="str">
-        <x:v>2002229-2</x:v>
+        <x:v>2002310-3</x:v>
       </x:c>
       <x:c r="H43" s="42" t="str">
-        <x:v>القرآن الكريم (٦)</x:v>
+        <x:v>التفسير التحليلي (٣)</x:v>
       </x:c>
       <x:c r="I43" s="43" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J43" s="42" t="str">
         <x:v>نظري</x:v>
@@ -6865,9 +6742,9 @@
       <x:c r="M43" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N43" s="42" t="str"/>
+      <x:c r="N43" s="42"/>
       <x:c r="O43" s="42" t="str">
-        <x:v>2002229-2||القرانالكريم٦</x:v>
+        <x:v>2002310-3||التفسيرالتحليلي٣</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="34" customHeight="1">
@@ -6890,13 +6767,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G44" s="43" t="str">
-        <x:v>2002310-3</x:v>
+        <x:v>20013201-4</x:v>
       </x:c>
       <x:c r="H44" s="42" t="str">
-        <x:v>التفسير التحليلي (٣)</x:v>
+        <x:v>الفقه (٥)</x:v>
       </x:c>
       <x:c r="I44" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J44" s="42" t="str">
         <x:v>نظري</x:v>
@@ -6910,9 +6787,9 @@
       <x:c r="M44" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N44" s="42" t="str"/>
+      <x:c r="N44" s="42"/>
       <x:c r="O44" s="42" t="str">
-        <x:v>2002310-3||التفسيرالتحليلي٣</x:v>
+        <x:v>20013201-4||الفقه٥</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="34" customHeight="1">
@@ -6932,13 +6809,13 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="F45" s="43" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G45" s="43" t="str">
-        <x:v>20013201-4</x:v>
+        <x:v>2004269-4</x:v>
       </x:c>
       <x:c r="H45" s="42" t="str">
-        <x:v>الفقه (٥)</x:v>
+        <x:v>التخريج ودراسة الأسانيد</x:v>
       </x:c>
       <x:c r="I45" s="43" t="n">
         <x:v>4</x:v>
@@ -6955,9 +6832,9 @@
       <x:c r="M45" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N45" s="42" t="str"/>
+      <x:c r="N45" s="42"/>
       <x:c r="O45" s="42" t="str">
-        <x:v>20013201-4||الفقه٥</x:v>
+        <x:v>2004269-4||التخريجودراسةالاسانيد</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="34" customHeight="1">
@@ -6980,13 +6857,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G46" s="43" t="str">
-        <x:v>2004269-4</x:v>
+        <x:v>2004272-2</x:v>
       </x:c>
       <x:c r="H46" s="42" t="str">
-        <x:v>التخريج ودراسة الأسانيد</x:v>
+        <x:v>العمل الخيري</x:v>
       </x:c>
       <x:c r="I46" s="43" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J46" s="42" t="str">
         <x:v>نظري</x:v>
@@ -7000,9 +6877,9 @@
       <x:c r="M46" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N46" s="42" t="str"/>
+      <x:c r="N46" s="42"/>
       <x:c r="O46" s="42" t="str">
-        <x:v>2004269-4||التخريجودراسةالاسانيد</x:v>
+        <x:v>2004272-2||العملالخيري</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="34" customHeight="1">
@@ -7025,10 +6902,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G47" s="43" t="str">
-        <x:v>2004272-2</x:v>
+        <x:v>20043111-2</x:v>
       </x:c>
       <x:c r="H47" s="42" t="str">
-        <x:v>العمل الخيري</x:v>
+        <x:v>الأمن الفكري</x:v>
       </x:c>
       <x:c r="I47" s="43" t="n">
         <x:v>2</x:v>
@@ -7037,7 +6914,7 @@
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K47" s="42" t="str">
-        <x:v>إجبارية القسم</x:v>
+        <x:v>اختيارية القسم</x:v>
       </x:c>
       <x:c r="L47" s="42" t="str">
         <x:v>الإسلامية 47.pdf</x:v>
@@ -7045,9 +6922,9 @@
       <x:c r="M47" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N47" s="42" t="str"/>
+      <x:c r="N47" s="42"/>
       <x:c r="O47" s="42" t="str">
-        <x:v>2004272-2||العملالخيري</x:v>
+        <x:v>20043111-2||الامنالفكري</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="34" customHeight="1">
@@ -7067,13 +6944,13 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="F48" s="43" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G48" s="43" t="str">
-        <x:v>20043111-2</x:v>
+        <x:v>2001270-2</x:v>
       </x:c>
       <x:c r="H48" s="42" t="str">
-        <x:v>الأمن الفكري</x:v>
+        <x:v>فقه النوازل</x:v>
       </x:c>
       <x:c r="I48" s="43" t="n">
         <x:v>2</x:v>
@@ -7082,7 +6959,7 @@
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K48" s="42" t="str">
-        <x:v>اختيارية القسم</x:v>
+        <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L48" s="42" t="str">
         <x:v>الإسلامية 47.pdf</x:v>
@@ -7090,9 +6967,9 @@
       <x:c r="M48" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N48" s="42" t="str"/>
+      <x:c r="N48" s="42"/>
       <x:c r="O48" s="42" t="str">
-        <x:v>20043111-2||الامنالفكري</x:v>
+        <x:v>2001270-2||فقهالنوازل</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="34" customHeight="1">
@@ -7115,10 +6992,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="G49" s="43" t="str">
-        <x:v>2001270-2</x:v>
+        <x:v>2002236-2</x:v>
       </x:c>
       <x:c r="H49" s="42" t="str">
-        <x:v>فقه النوازل</x:v>
+        <x:v>القرآن الكريم (٨)</x:v>
       </x:c>
       <x:c r="I49" s="43" t="n">
         <x:v>2</x:v>
@@ -7135,9 +7012,9 @@
       <x:c r="M49" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N49" s="42" t="str"/>
+      <x:c r="N49" s="42"/>
       <x:c r="O49" s="42" t="str">
-        <x:v>2001270-2||فقهالنوازل</x:v>
+        <x:v>2002236-2||القرانالكريم٨</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="34" customHeight="1">
@@ -7160,16 +7037,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="G50" s="43" t="str">
-        <x:v>2002236-2</x:v>
+        <x:v>20044220-4</x:v>
       </x:c>
       <x:c r="H50" s="42" t="str">
-        <x:v>القرآن الكريم (٨)</x:v>
+        <x:v>التدريب التعاوني</x:v>
       </x:c>
       <x:c r="I50" s="43" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J50" s="42" t="str">
-        <x:v>نظري</x:v>
+        <x:v>تدريب</x:v>
       </x:c>
       <x:c r="K50" s="42" t="str">
         <x:v>إجبارية القسم</x:v>
@@ -7180,9 +7057,9 @@
       <x:c r="M50" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N50" s="42" t="str"/>
+      <x:c r="N50" s="42"/>
       <x:c r="O50" s="42" t="str">
-        <x:v>2002236-2||القرانالكريم٨</x:v>
+        <x:v>20044220-4||التدريبالتعاوني</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="34" customHeight="1">
@@ -7196,38 +7073,38 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D51" s="42" t="str">
-        <x:v>جديدة</x:v>
+        <x:v>قديمة</x:v>
       </x:c>
       <x:c r="E51" s="43" t="n">
-        <x:v>47</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F51" s="43" t="n">
-        <x:v>8</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G51" s="43" t="str">
-        <x:v>20044220-4</x:v>
+        <x:v>20041201-2</x:v>
       </x:c>
       <x:c r="H51" s="42" t="str">
-        <x:v>التدريب التعاوني</x:v>
+        <x:v>التجويد</x:v>
       </x:c>
       <x:c r="I51" s="43" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J51" s="42" t="str">
-        <x:v>تدريب</x:v>
+        <x:v>نظري</x:v>
       </x:c>
       <x:c r="K51" s="42" t="str">
         <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L51" s="42" t="str">
-        <x:v>الإسلامية 47.pdf</x:v>
+        <x:v>الدراسات الإسلامية 39.pdf</x:v>
       </x:c>
       <x:c r="M51" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N51" s="42" t="str"/>
+      <x:c r="N51" s="42"/>
       <x:c r="O51" s="42" t="str">
-        <x:v>20044220-4||التدريبالتعاوني</x:v>
+        <x:v>20041201-2||التجويد</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="34" customHeight="1">
@@ -7247,13 +7124,13 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="F52" s="43" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G52" s="43" t="str">
-        <x:v>20041201-2</x:v>
+        <x:v>2003220-2</x:v>
       </x:c>
       <x:c r="H52" s="42" t="str">
-        <x:v>التجويد</x:v>
+        <x:v>المدخل لدراسة الأنظمة</x:v>
       </x:c>
       <x:c r="I52" s="43" t="n">
         <x:v>2</x:v>
@@ -7270,9 +7147,9 @@
       <x:c r="M52" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N52" s="42" t="str"/>
+      <x:c r="N52" s="42"/>
       <x:c r="O52" s="42" t="str">
-        <x:v>20041201-2||التجويد</x:v>
+        <x:v>2003220-2||المدخللدراسةالانظمة</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="34" customHeight="1">
@@ -7292,13 +7169,13 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="F53" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G53" s="43" t="str">
-        <x:v>2003220-2</x:v>
+        <x:v>20043105-2</x:v>
       </x:c>
       <x:c r="H53" s="42" t="str">
-        <x:v>المدخل لدراسة الأنظمة</x:v>
+        <x:v>الفقه المقارن</x:v>
       </x:c>
       <x:c r="I53" s="43" t="n">
         <x:v>2</x:v>
@@ -7315,9 +7192,9 @@
       <x:c r="M53" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N53" s="42" t="str"/>
+      <x:c r="N53" s="42"/>
       <x:c r="O53" s="42" t="str">
-        <x:v>2003220-2||المدخللدراسةالانظمة</x:v>
+        <x:v>20043105-2||الفقهالمقارن</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="34" customHeight="1">
@@ -7340,10 +7217,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G54" s="43" t="str">
-        <x:v>20043105-2</x:v>
+        <x:v>20043108-2</x:v>
       </x:c>
       <x:c r="H54" s="42" t="str">
-        <x:v>الفقه المقارن</x:v>
+        <x:v>علم المواريث (1)</x:v>
       </x:c>
       <x:c r="I54" s="43" t="n">
         <x:v>2</x:v>
@@ -7360,9 +7237,9 @@
       <x:c r="M54" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N54" s="42" t="str"/>
+      <x:c r="N54" s="42"/>
       <x:c r="O54" s="42" t="str">
-        <x:v>20043105-2||الفقهالمقارن</x:v>
+        <x:v>20043108-2||علمالمواريث1</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="34" customHeight="1">
@@ -7382,13 +7259,13 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="F55" s="43" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G55" s="43" t="str">
-        <x:v>20043108-2</x:v>
+        <x:v>20043202-2</x:v>
       </x:c>
       <x:c r="H55" s="42" t="str">
-        <x:v>علم المواريث (1)</x:v>
+        <x:v>القواعد الفقهية</x:v>
       </x:c>
       <x:c r="I55" s="43" t="n">
         <x:v>2</x:v>
@@ -7405,9 +7282,9 @@
       <x:c r="M55" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N55" s="42" t="str"/>
+      <x:c r="N55" s="42"/>
       <x:c r="O55" s="42" t="str">
-        <x:v>20043108-2||علمالمواريث1</x:v>
+        <x:v>20043202-2||القواعدالفقهية</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="34" customHeight="1">
@@ -7427,13 +7304,13 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="F56" s="43" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G56" s="43" t="str">
-        <x:v>20043202-2</x:v>
+        <x:v>20044101-2</x:v>
       </x:c>
       <x:c r="H56" s="42" t="str">
-        <x:v>القواعد الفقهية</x:v>
+        <x:v>أصول فقه (3)</x:v>
       </x:c>
       <x:c r="I56" s="43" t="n">
         <x:v>2</x:v>
@@ -7450,9 +7327,9 @@
       <x:c r="M56" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N56" s="42" t="str"/>
+      <x:c r="N56" s="42"/>
       <x:c r="O56" s="42" t="str">
-        <x:v>20043202-2||القواعدالفقهية</x:v>
+        <x:v>20044101-2||اصولفقه3</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="34" customHeight="1">
@@ -7472,13 +7349,13 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="F57" s="43" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G57" s="43" t="str">
-        <x:v>20044101-2</x:v>
+        <x:v>20044206-2</x:v>
       </x:c>
       <x:c r="H57" s="42" t="str">
-        <x:v>أصول فقه (3)</x:v>
+        <x:v>علم المواريث (2)</x:v>
       </x:c>
       <x:c r="I57" s="43" t="n">
         <x:v>2</x:v>
@@ -7495,9 +7372,9 @@
       <x:c r="M57" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N57" s="42" t="str"/>
+      <x:c r="N57" s="42"/>
       <x:c r="O57" s="42" t="str">
-        <x:v>20044101-2||اصولفقه3</x:v>
+        <x:v>20044206-2||علمالمواريث2</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="34" customHeight="1">
@@ -7505,25 +7382,25 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B58" s="42" t="str">
-        <x:v>الدراسات الإسلامية</x:v>
+        <x:v>الشريعة</x:v>
       </x:c>
       <x:c r="C58" s="42" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D58" s="42" t="str">
-        <x:v>قديمة</x:v>
+        <x:v>جديدة</x:v>
       </x:c>
       <x:c r="E58" s="43" t="n">
-        <x:v>39</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F58" s="43" t="n">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G58" s="43" t="str">
-        <x:v>20044206-2</x:v>
+        <x:v>2004301-2</x:v>
       </x:c>
       <x:c r="H58" s="42" t="str">
-        <x:v>علم المواريث (2)</x:v>
+        <x:v>تدوين السنة</x:v>
       </x:c>
       <x:c r="I58" s="43" t="n">
         <x:v>2</x:v>
@@ -7532,17 +7409,17 @@
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K58" s="42" t="str">
-        <x:v>إجبارية القسم</x:v>
+        <x:v>متطلبات الكلية</x:v>
       </x:c>
       <x:c r="L58" s="42" t="str">
-        <x:v>الدراسات الإسلامية 39.pdf</x:v>
+        <x:v>الشريعة 47.pdf</x:v>
       </x:c>
       <x:c r="M58" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N58" s="42" t="str"/>
+      <x:c r="N58" s="42"/>
       <x:c r="O58" s="42" t="str">
-        <x:v>20044206-2||علمالمواريث2</x:v>
+        <x:v>2004301-2||تدوينالسنة</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="34" customHeight="1">
@@ -7562,13 +7439,13 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="F59" s="43" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G59" s="43" t="str">
-        <x:v>2004301-2</x:v>
+        <x:v>2004476-2</x:v>
       </x:c>
       <x:c r="H59" s="42" t="str">
-        <x:v>تدوين السنة</x:v>
+        <x:v>الأديان والفرق</x:v>
       </x:c>
       <x:c r="I59" s="43" t="n">
         <x:v>2</x:v>
@@ -7585,9 +7462,9 @@
       <x:c r="M59" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N59" s="42" t="str"/>
+      <x:c r="N59" s="42"/>
       <x:c r="O59" s="42" t="str">
-        <x:v>2004301-2||تدوينالسنة</x:v>
+        <x:v>2004476-2||الاديانوالفرق</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="34" customHeight="1">
@@ -7601,19 +7478,19 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D60" s="42" t="str">
-        <x:v>جديدة</x:v>
+        <x:v>قديمة</x:v>
       </x:c>
       <x:c r="E60" s="43" t="n">
-        <x:v>47</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F60" s="43" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G60" s="43" t="str">
-        <x:v>2004476-2</x:v>
+        <x:v>2001193-2</x:v>
       </x:c>
       <x:c r="H60" s="42" t="str">
-        <x:v>الأديان والفرق</x:v>
+        <x:v>علوم الحديث (1)</x:v>
       </x:c>
       <x:c r="I60" s="43" t="n">
         <x:v>2</x:v>
@@ -7622,17 +7499,17 @@
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K60" s="42" t="str">
-        <x:v>متطلبات الكلية</x:v>
+        <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L60" s="42" t="str">
-        <x:v>الشريعة 47.pdf</x:v>
+        <x:v>خطط الإصدارات السابقة.pdf</x:v>
       </x:c>
       <x:c r="M60" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N60" s="42" t="str"/>
+      <x:c r="N60" s="42"/>
       <x:c r="O60" s="42" t="str">
-        <x:v>2004476-2||الاديانوالفرق</x:v>
+        <x:v>2001193-2||علومالحديث1</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="34" customHeight="1">
@@ -7652,13 +7529,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F61" s="43" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G61" s="43" t="str">
-        <x:v>2001193-2</x:v>
+        <x:v>2001192-2</x:v>
       </x:c>
       <x:c r="H61" s="42" t="str">
-        <x:v>علوم الحديث (1)</x:v>
+        <x:v>علوم الحديث (2)</x:v>
       </x:c>
       <x:c r="I61" s="43" t="n">
         <x:v>2</x:v>
@@ -7675,9 +7552,9 @@
       <x:c r="M61" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N61" s="42" t="str"/>
+      <x:c r="N61" s="42"/>
       <x:c r="O61" s="42" t="str">
-        <x:v>2001193-2||علومالحديث1</x:v>
+        <x:v>2001192-2||علومالحديث2</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="34" customHeight="1">
@@ -7697,16 +7574,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F62" s="43" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G62" s="43" t="str">
-        <x:v>2002230-2</x:v>
+        <x:v>2001219-3</x:v>
       </x:c>
       <x:c r="H62" s="42" t="str">
-        <x:v>علوم قرآن</x:v>
+        <x:v>أدلة الأحكام الشرعية (1)</x:v>
       </x:c>
       <x:c r="I62" s="43" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J62" s="42" t="str">
         <x:v>نظري</x:v>
@@ -7720,9 +7597,9 @@
       <x:c r="M62" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N62" s="42" t="str"/>
+      <x:c r="N62" s="42"/>
       <x:c r="O62" s="42" t="str">
-        <x:v>2002230-2||علومقران</x:v>
+        <x:v>2001219-3||ادلةالاحكامالشرعية1</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="34" customHeight="1">
@@ -7742,13 +7619,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F63" s="43" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G63" s="43" t="str">
-        <x:v>2001192-2</x:v>
+        <x:v>2001231-2</x:v>
       </x:c>
       <x:c r="H63" s="42" t="str">
-        <x:v>علوم الحديث (2)</x:v>
+        <x:v>أحاديث الأحكام (1)</x:v>
       </x:c>
       <x:c r="I63" s="43" t="n">
         <x:v>2</x:v>
@@ -7765,9 +7642,9 @@
       <x:c r="M63" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N63" s="42" t="str"/>
+      <x:c r="N63" s="42"/>
       <x:c r="O63" s="42" t="str">
-        <x:v>2001192-2||علومالحديث2</x:v>
+        <x:v>2001231-2||احاديثالاحكام1</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="34" customHeight="1">
@@ -7787,16 +7664,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F64" s="43" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G64" s="43" t="str">
-        <x:v>2002241-2</x:v>
+        <x:v>2001217-4</x:v>
       </x:c>
       <x:c r="H64" s="42" t="str">
-        <x:v>تفسير آيات الأحكام (1)</x:v>
+        <x:v>أدلة الأحكام الشرعية (2)</x:v>
       </x:c>
       <x:c r="I64" s="43" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J64" s="42" t="str">
         <x:v>نظري</x:v>
@@ -7810,9 +7687,9 @@
       <x:c r="M64" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N64" s="42" t="str"/>
+      <x:c r="N64" s="42"/>
       <x:c r="O64" s="42" t="str">
-        <x:v>2002241-2||تفسيراياتالاحكام1</x:v>
+        <x:v>2001217-4||ادلةالاحكامالشرعية2</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="34" customHeight="1">
@@ -7832,16 +7709,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F65" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G65" s="43" t="str">
-        <x:v>2001219-3</x:v>
+        <x:v>2001218-2</x:v>
       </x:c>
       <x:c r="H65" s="42" t="str">
-        <x:v>أدلة الأحكام الشرعية (1)</x:v>
+        <x:v>قاعة بحث (تطبيقي)</x:v>
       </x:c>
       <x:c r="I65" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J65" s="42" t="str">
         <x:v>نظري</x:v>
@@ -7855,9 +7732,9 @@
       <x:c r="M65" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N65" s="42" t="str"/>
+      <x:c r="N65" s="42"/>
       <x:c r="O65" s="42" t="str">
-        <x:v>2001219-3||ادلةالاحكامالشرعية1</x:v>
+        <x:v>2001218-2||قاعةبحثتطبيقي</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="34" customHeight="1">
@@ -7877,13 +7754,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F66" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G66" s="43" t="str">
-        <x:v>2001231-2</x:v>
+        <x:v>2001332-2</x:v>
       </x:c>
       <x:c r="H66" s="42" t="str">
-        <x:v>أحاديث الأحكام (1)</x:v>
+        <x:v>أحاديث الأحكام (2)</x:v>
       </x:c>
       <x:c r="I66" s="43" t="n">
         <x:v>2</x:v>
@@ -7900,9 +7777,9 @@
       <x:c r="M66" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N66" s="42" t="str"/>
+      <x:c r="N66" s="42"/>
       <x:c r="O66" s="42" t="str">
-        <x:v>2001231-2||احاديثالاحكام1</x:v>
+        <x:v>2001332-2||احاديثالاحكام2</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="34" customHeight="1">
@@ -7922,13 +7799,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F67" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G67" s="43" t="str">
-        <x:v>2002242-2</x:v>
+        <x:v>2001280-2</x:v>
       </x:c>
       <x:c r="H67" s="42" t="str">
-        <x:v>تفسير آيات الأحكام (2)</x:v>
+        <x:v>أصول الدعوة والحسبة</x:v>
       </x:c>
       <x:c r="I67" s="43" t="n">
         <x:v>2</x:v>
@@ -7945,9 +7822,9 @@
       <x:c r="M67" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N67" s="42" t="str"/>
+      <x:c r="N67" s="42"/>
       <x:c r="O67" s="42" t="str">
-        <x:v>2002242-2||تفسيراياتالاحكام2</x:v>
+        <x:v>2001280-2||اصولالدعوةوالحسبة</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="34" customHeight="1">
@@ -7967,16 +7844,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F68" s="43" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G68" s="43" t="str">
-        <x:v>2001217-4</x:v>
+        <x:v>2001301-2</x:v>
       </x:c>
       <x:c r="H68" s="42" t="str">
-        <x:v>أدلة الأحكام الشرعية (2)</x:v>
+        <x:v>تدوين السنة</x:v>
       </x:c>
       <x:c r="I68" s="43" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J68" s="42" t="str">
         <x:v>نظري</x:v>
@@ -7990,9 +7867,9 @@
       <x:c r="M68" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N68" s="42" t="str"/>
+      <x:c r="N68" s="42"/>
       <x:c r="O68" s="42" t="str">
-        <x:v>2001217-4||ادلةالاحكامالشرعية2</x:v>
+        <x:v>2001301-2||تدوينالسنة</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="34" customHeight="1">
@@ -8012,13 +7889,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F69" s="43" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G69" s="43" t="str">
-        <x:v>2001218-2</x:v>
+        <x:v>2003243-2</x:v>
       </x:c>
       <x:c r="H69" s="42" t="str">
-        <x:v>قاعة بحث (تطبيقي)</x:v>
+        <x:v>مبادئ القانون الإداري</x:v>
       </x:c>
       <x:c r="I69" s="43" t="n">
         <x:v>2</x:v>
@@ -8035,9 +7912,9 @@
       <x:c r="M69" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N69" s="42" t="str"/>
+      <x:c r="N69" s="42"/>
       <x:c r="O69" s="42" t="str">
-        <x:v>2001218-2||قاعةبحثتطبيقي</x:v>
+        <x:v>2003243-2||مباديالقانونالاداري</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="34" customHeight="1">
@@ -8057,16 +7934,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F70" s="43" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G70" s="43" t="str">
-        <x:v>2001332-2</x:v>
+        <x:v>2003325-1</x:v>
       </x:c>
       <x:c r="H70" s="42" t="str">
-        <x:v>أحاديث الأحكام (2)</x:v>
+        <x:v>نظام المرافعات الشرعية</x:v>
       </x:c>
       <x:c r="I70" s="43" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J70" s="42" t="str">
         <x:v>نظري</x:v>
@@ -8080,9 +7957,9 @@
       <x:c r="M70" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N70" s="42" t="str"/>
+      <x:c r="N70" s="42"/>
       <x:c r="O70" s="42" t="str">
-        <x:v>2001332-2||احاديثالاحكام2</x:v>
+        <x:v>2003325-1||نظامالمرافعاتالشرعية</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="34" customHeight="1">
@@ -8102,16 +7979,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F71" s="43" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G71" s="43" t="str">
-        <x:v>2002343-2</x:v>
+        <x:v>2003328-1</x:v>
       </x:c>
       <x:c r="H71" s="42" t="str">
-        <x:v>تفسير آيات الأحكام (3)</x:v>
+        <x:v>نظام الإجراءات الجزائية</x:v>
       </x:c>
       <x:c r="I71" s="43" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J71" s="42" t="str">
         <x:v>نظري</x:v>
@@ -8125,9 +8002,9 @@
       <x:c r="M71" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N71" s="42" t="str"/>
+      <x:c r="N71" s="42"/>
       <x:c r="O71" s="42" t="str">
-        <x:v>2002343-2||تفسيراياتالاحكام3</x:v>
+        <x:v>2003328-1||نظامالاجراءاتالجزايية</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="34" customHeight="1">
@@ -8147,13 +8024,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F72" s="43" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G72" s="43" t="str">
-        <x:v>2001280-2</x:v>
+        <x:v>2001493-2</x:v>
       </x:c>
       <x:c r="H72" s="42" t="str">
-        <x:v>أصول الدعوة والحسبة</x:v>
+        <x:v>تخريج ودراسة الأسانيد</x:v>
       </x:c>
       <x:c r="I72" s="43" t="n">
         <x:v>2</x:v>
@@ -8170,9 +8047,9 @@
       <x:c r="M72" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N72" s="42" t="str"/>
+      <x:c r="N72" s="42"/>
       <x:c r="O72" s="42" t="str">
-        <x:v>2001280-2||اصولالدعوةوالحسبة</x:v>
+        <x:v>2001493-2||تخريجودراسةالاسانيد</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="34" customHeight="1">
@@ -8189,16 +8066,16 @@
         <x:v>قديمة</x:v>
       </x:c>
       <x:c r="E73" s="43" t="n">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F73" s="43" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G73" s="43" t="str">
-        <x:v>2001301-2</x:v>
+        <x:v>2001193-2</x:v>
       </x:c>
       <x:c r="H73" s="42" t="str">
-        <x:v>تدوين السنة</x:v>
+        <x:v>علوم الحديث (1)</x:v>
       </x:c>
       <x:c r="I73" s="43" t="n">
         <x:v>2</x:v>
@@ -8210,14 +8087,14 @@
         <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L73" s="42" t="str">
-        <x:v>خطط الإصدارات السابقة.pdf</x:v>
+        <x:v>الشريعة 39.pdf</x:v>
       </x:c>
       <x:c r="M73" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N73" s="42" t="str"/>
+      <x:c r="N73" s="42"/>
       <x:c r="O73" s="42" t="str">
-        <x:v>2001301-2||تدوينالسنة</x:v>
+        <x:v>2001193-2||علومالحديث1</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="34" customHeight="1">
@@ -8234,16 +8111,16 @@
         <x:v>قديمة</x:v>
       </x:c>
       <x:c r="E74" s="43" t="n">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F74" s="43" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G74" s="43" t="str">
-        <x:v>2003243-2</x:v>
+        <x:v>2001192-2</x:v>
       </x:c>
       <x:c r="H74" s="42" t="str">
-        <x:v>مبادئ القانون الإداري</x:v>
+        <x:v>علوم الحديث (2)</x:v>
       </x:c>
       <x:c r="I74" s="43" t="n">
         <x:v>2</x:v>
@@ -8255,14 +8132,14 @@
         <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L74" s="42" t="str">
-        <x:v>خطط الإصدارات السابقة.pdf</x:v>
+        <x:v>الشريعة 39.pdf</x:v>
       </x:c>
       <x:c r="M74" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N74" s="42" t="str"/>
+      <x:c r="N74" s="42"/>
       <x:c r="O74" s="42" t="str">
-        <x:v>2003243-2||مباديالقانونالاداري</x:v>
+        <x:v>2001192-2||علومالحديث2</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="34" customHeight="1">
@@ -8279,19 +8156,19 @@
         <x:v>قديمة</x:v>
       </x:c>
       <x:c r="E75" s="43" t="n">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F75" s="43" t="n">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G75" s="43" t="str">
-        <x:v>2003325-1</x:v>
+        <x:v>2001219-3</x:v>
       </x:c>
       <x:c r="H75" s="42" t="str">
-        <x:v>نظام المرافعات الشرعية</x:v>
+        <x:v>أدلة الأحكام الشرعية (1)</x:v>
       </x:c>
       <x:c r="I75" s="43" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J75" s="42" t="str">
         <x:v>نظري</x:v>
@@ -8300,14 +8177,14 @@
         <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L75" s="42" t="str">
-        <x:v>خطط الإصدارات السابقة.pdf</x:v>
+        <x:v>الشريعة 39.pdf</x:v>
       </x:c>
       <x:c r="M75" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N75" s="42" t="str"/>
+      <x:c r="N75" s="42"/>
       <x:c r="O75" s="42" t="str">
-        <x:v>2003325-1||نظامالمرافعاتالشرعية</x:v>
+        <x:v>2001219-3||ادلةالاحكامالشرعية1</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="34" customHeight="1">
@@ -8324,19 +8201,19 @@
         <x:v>قديمة</x:v>
       </x:c>
       <x:c r="E76" s="43" t="n">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F76" s="43" t="n">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G76" s="43" t="str">
-        <x:v>2003328-1</x:v>
+        <x:v>2001231-2</x:v>
       </x:c>
       <x:c r="H76" s="42" t="str">
-        <x:v>نظام الإجراءات الجزائية</x:v>
+        <x:v>أحاديث الأحكام (1)</x:v>
       </x:c>
       <x:c r="I76" s="43" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J76" s="42" t="str">
         <x:v>نظري</x:v>
@@ -8345,14 +8222,14 @@
         <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L76" s="42" t="str">
-        <x:v>خطط الإصدارات السابقة.pdf</x:v>
+        <x:v>الشريعة 39.pdf</x:v>
       </x:c>
       <x:c r="M76" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N76" s="42" t="str"/>
+      <x:c r="N76" s="42"/>
       <x:c r="O76" s="42" t="str">
-        <x:v>2003328-1||نظامالاجراءاتالجزايية</x:v>
+        <x:v>2001231-2||احاديثالاحكام1</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="34" customHeight="1">
@@ -8369,19 +8246,19 @@
         <x:v>قديمة</x:v>
       </x:c>
       <x:c r="E77" s="43" t="n">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F77" s="43" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G77" s="43" t="str">
-        <x:v>2001493-2</x:v>
+        <x:v>2001217-4</x:v>
       </x:c>
       <x:c r="H77" s="42" t="str">
-        <x:v>تخريج ودراسة الأسانيد</x:v>
+        <x:v>أدلة الأحكام الشرعية (2)</x:v>
       </x:c>
       <x:c r="I77" s="43" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J77" s="42" t="str">
         <x:v>نظري</x:v>
@@ -8390,14 +8267,14 @@
         <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L77" s="42" t="str">
-        <x:v>خطط الإصدارات السابقة.pdf</x:v>
+        <x:v>الشريعة 39.pdf</x:v>
       </x:c>
       <x:c r="M77" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N77" s="42" t="str"/>
+      <x:c r="N77" s="42"/>
       <x:c r="O77" s="42" t="str">
-        <x:v>2001493-2||تخريجودراسةالاسانيد</x:v>
+        <x:v>2001217-4||ادلةالاحكامالشرعية2</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="34" customHeight="1">
@@ -8417,13 +8294,13 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="F78" s="43" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G78" s="43" t="str">
-        <x:v>2001193-2</x:v>
+        <x:v>2001332-2</x:v>
       </x:c>
       <x:c r="H78" s="42" t="str">
-        <x:v>علوم الحديث (1)</x:v>
+        <x:v>أحاديث الأحكام (2)</x:v>
       </x:c>
       <x:c r="I78" s="43" t="n">
         <x:v>2</x:v>
@@ -8440,9 +8317,9 @@
       <x:c r="M78" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N78" s="42" t="str"/>
+      <x:c r="N78" s="42"/>
       <x:c r="O78" s="42" t="str">
-        <x:v>2001193-2||علومالحديث1</x:v>
+        <x:v>2001332-2||احاديثالاحكام2</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="34" customHeight="1">
@@ -8462,13 +8339,13 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="F79" s="43" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G79" s="43" t="str">
-        <x:v>2002230-2</x:v>
+        <x:v>20032202-2</x:v>
       </x:c>
       <x:c r="H79" s="42" t="str">
-        <x:v>علوم قرآن</x:v>
+        <x:v>المدخل إلى دراسة الأنظمة</x:v>
       </x:c>
       <x:c r="I79" s="43" t="n">
         <x:v>2</x:v>
@@ -8485,9 +8362,9 @@
       <x:c r="M79" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N79" s="42" t="str"/>
+      <x:c r="N79" s="42"/>
       <x:c r="O79" s="42" t="str">
-        <x:v>2002230-2||علومقران</x:v>
+        <x:v>20032202-2||المدخلاليدراسةالانظمة</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="34" customHeight="1">
@@ -8507,13 +8384,13 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="F80" s="43" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G80" s="43" t="str">
-        <x:v>2001192-2</x:v>
+        <x:v>2001280-2</x:v>
       </x:c>
       <x:c r="H80" s="42" t="str">
-        <x:v>علوم الحديث (2)</x:v>
+        <x:v>أصول الدعوة والحسبة</x:v>
       </x:c>
       <x:c r="I80" s="43" t="n">
         <x:v>2</x:v>
@@ -8530,9 +8407,9 @@
       <x:c r="M80" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N80" s="42" t="str"/>
+      <x:c r="N80" s="42"/>
       <x:c r="O80" s="42" t="str">
-        <x:v>2001192-2||علومالحديث2</x:v>
+        <x:v>2001280-2||اصولالدعوةوالحسبة</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="34" customHeight="1">
@@ -8552,13 +8429,13 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="F81" s="43" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G81" s="43" t="str">
-        <x:v>2002241-2</x:v>
+        <x:v>2001301-2</x:v>
       </x:c>
       <x:c r="H81" s="42" t="str">
-        <x:v>تفسير آيات الأحكام (1)</x:v>
+        <x:v>تدوين السنة</x:v>
       </x:c>
       <x:c r="I81" s="43" t="n">
         <x:v>2</x:v>
@@ -8575,9 +8452,9 @@
       <x:c r="M81" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N81" s="42" t="str"/>
+      <x:c r="N81" s="42"/>
       <x:c r="O81" s="42" t="str">
-        <x:v>2002241-2||تفسيراياتالاحكام1</x:v>
+        <x:v>2001301-2||تدوينالسنة</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="34" customHeight="1">
@@ -8597,16 +8474,16 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="F82" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G82" s="43" t="str">
-        <x:v>2001219-3</x:v>
+        <x:v>2003325-1</x:v>
       </x:c>
       <x:c r="H82" s="42" t="str">
-        <x:v>أدلة الأحكام الشرعية (1)</x:v>
+        <x:v>نظام المرافعات الشرعية</x:v>
       </x:c>
       <x:c r="I82" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J82" s="42" t="str">
         <x:v>نظري</x:v>
@@ -8620,9 +8497,9 @@
       <x:c r="M82" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N82" s="42" t="str"/>
+      <x:c r="N82" s="42"/>
       <x:c r="O82" s="42" t="str">
-        <x:v>2001219-3||ادلةالاحكامالشرعية1</x:v>
+        <x:v>2003325-1||نظامالمرافعاتالشرعية</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="34" customHeight="1">
@@ -8642,16 +8519,16 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="F83" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G83" s="43" t="str">
-        <x:v>2001231-2</x:v>
+        <x:v>2003328-1</x:v>
       </x:c>
       <x:c r="H83" s="42" t="str">
-        <x:v>أحاديث الأحكام (1)</x:v>
+        <x:v>نظام الإجراءات الجزائية</x:v>
       </x:c>
       <x:c r="I83" s="43" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J83" s="42" t="str">
         <x:v>نظري</x:v>
@@ -8665,9 +8542,9 @@
       <x:c r="M83" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N83" s="42" t="str"/>
+      <x:c r="N83" s="42"/>
       <x:c r="O83" s="42" t="str">
-        <x:v>2001231-2||احاديثالاحكام1</x:v>
+        <x:v>2003328-1||نظامالاجراءاتالجزايية</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="34" customHeight="1">
@@ -8687,13 +8564,13 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="F84" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G84" s="43" t="str">
-        <x:v>2002242-2</x:v>
+        <x:v>2001493-2</x:v>
       </x:c>
       <x:c r="H84" s="42" t="str">
-        <x:v>تفسير آيات الأحكام (2)</x:v>
+        <x:v>تخريج ودراسة الأسانيد</x:v>
       </x:c>
       <x:c r="I84" s="43" t="n">
         <x:v>2</x:v>
@@ -8710,9 +8587,9 @@
       <x:c r="M84" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N84" s="42" t="str"/>
+      <x:c r="N84" s="42"/>
       <x:c r="O84" s="42" t="str">
-        <x:v>2002242-2||تفسيراياتالاحكام2</x:v>
+        <x:v>2001493-2||تخريجودراسةالاسانيد</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="34" customHeight="1">
@@ -8732,16 +8609,16 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="F85" s="43" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G85" s="43" t="str">
-        <x:v>2001217-4</x:v>
+        <x:v>20014201-2</x:v>
       </x:c>
       <x:c r="H85" s="42" t="str">
-        <x:v>أدلة الأحكام الشرعية (2)</x:v>
+        <x:v>التدريبات العملية</x:v>
       </x:c>
       <x:c r="I85" s="43" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J85" s="42" t="str">
         <x:v>نظري</x:v>
@@ -8755,9 +8632,9 @@
       <x:c r="M85" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N85" s="42" t="str"/>
+      <x:c r="N85" s="42"/>
       <x:c r="O85" s="42" t="str">
-        <x:v>2001217-4||ادلةالاحكامالشرعية2</x:v>
+        <x:v>20014201-2||التدريباتالعملية</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="34" customHeight="1">
@@ -8765,25 +8642,25 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B86" s="42" t="str">
-        <x:v>الشريعة</x:v>
+        <x:v>القراءات</x:v>
       </x:c>
       <x:c r="C86" s="42" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D86" s="42" t="str">
-        <x:v>قديمة</x:v>
+        <x:v>جديدة</x:v>
       </x:c>
       <x:c r="E86" s="43" t="n">
-        <x:v>39</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F86" s="43" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G86" s="43" t="str">
-        <x:v>2001332-2</x:v>
+        <x:v>2001221-2</x:v>
       </x:c>
       <x:c r="H86" s="42" t="str">
-        <x:v>أحاديث الأحكام (2)</x:v>
+        <x:v>الفقه (1)</x:v>
       </x:c>
       <x:c r="I86" s="43" t="n">
         <x:v>2</x:v>
@@ -8792,17 +8669,17 @@
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K86" s="42" t="str">
-        <x:v>إجبارية القسم</x:v>
+        <x:v>متطلبات الكلية</x:v>
       </x:c>
       <x:c r="L86" s="42" t="str">
-        <x:v>الشريعة 39.pdf</x:v>
+        <x:v>القراءات 47.pdf</x:v>
       </x:c>
       <x:c r="M86" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N86" s="42" t="str"/>
+      <x:c r="N86" s="42"/>
       <x:c r="O86" s="42" t="str">
-        <x:v>2001332-2||احاديثالاحكام2</x:v>
+        <x:v>2001221-2||الفقه1</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="34" customHeight="1">
@@ -8810,44 +8687,44 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B87" s="42" t="str">
-        <x:v>الشريعة</x:v>
+        <x:v>القراءات</x:v>
       </x:c>
       <x:c r="C87" s="42" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D87" s="42" t="str">
-        <x:v>قديمة</x:v>
+        <x:v>جديدة</x:v>
       </x:c>
       <x:c r="E87" s="43" t="n">
-        <x:v>39</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F87" s="43" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G87" s="43" t="str">
-        <x:v>2002343-2</x:v>
+        <x:v>2002111-3</x:v>
       </x:c>
       <x:c r="H87" s="42" t="str">
-        <x:v>تفسير آيات الأحكام (3)</x:v>
+        <x:v>عرض القراءات السبع (١)</x:v>
       </x:c>
       <x:c r="I87" s="43" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J87" s="42" t="str">
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K87" s="42" t="str">
-        <x:v>إجبارية القسم</x:v>
+        <x:v>متطلبات الكلية</x:v>
       </x:c>
       <x:c r="L87" s="42" t="str">
-        <x:v>الشريعة 39.pdf</x:v>
+        <x:v>القراءات 47.pdf</x:v>
       </x:c>
       <x:c r="M87" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N87" s="42" t="str"/>
+      <x:c r="N87" s="42"/>
       <x:c r="O87" s="42" t="str">
-        <x:v>2002343-2||تفسيراياتالاحكام3</x:v>
+        <x:v>2002111-3||عرضالقراءاتالسبع١</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="34" customHeight="1">
@@ -8855,25 +8732,25 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B88" s="42" t="str">
-        <x:v>الشريعة</x:v>
+        <x:v>القراءات</x:v>
       </x:c>
       <x:c r="C88" s="42" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D88" s="42" t="str">
-        <x:v>قديمة</x:v>
+        <x:v>جديدة</x:v>
       </x:c>
       <x:c r="E88" s="43" t="n">
-        <x:v>39</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F88" s="43" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G88" s="43" t="str">
-        <x:v>20032202-2</x:v>
+        <x:v>2002280-2</x:v>
       </x:c>
       <x:c r="H88" s="42" t="str">
-        <x:v>المدخل إلى دراسة الأنظمة</x:v>
+        <x:v>تدريبات على الجمع والكيفيات</x:v>
       </x:c>
       <x:c r="I88" s="43" t="n">
         <x:v>2</x:v>
@@ -8882,17 +8759,17 @@
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K88" s="42" t="str">
-        <x:v>إجبارية القسم</x:v>
+        <x:v>متطلبات الكلية</x:v>
       </x:c>
       <x:c r="L88" s="42" t="str">
-        <x:v>الشريعة 39.pdf</x:v>
+        <x:v>القراءات 47.pdf</x:v>
       </x:c>
       <x:c r="M88" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N88" s="42" t="str"/>
+      <x:c r="N88" s="42"/>
       <x:c r="O88" s="42" t="str">
-        <x:v>20032202-2||المدخلاليدراسةالانظمة</x:v>
+        <x:v>2002280-2||تدريباتعليالجمعوالكيفيات</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="34" customHeight="1">
@@ -8900,25 +8777,25 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B89" s="42" t="str">
-        <x:v>الشريعة</x:v>
+        <x:v>القراءات</x:v>
       </x:c>
       <x:c r="C89" s="42" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D89" s="42" t="str">
-        <x:v>قديمة</x:v>
+        <x:v>جديدة</x:v>
       </x:c>
       <x:c r="E89" s="43" t="n">
-        <x:v>39</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F89" s="43" t="n">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G89" s="43" t="str">
-        <x:v>2001280-2</x:v>
+        <x:v>2004102-2</x:v>
       </x:c>
       <x:c r="H89" s="42" t="str">
-        <x:v>أصول الدعوة والحسبة</x:v>
+        <x:v>مصطلح الحديث</x:v>
       </x:c>
       <x:c r="I89" s="43" t="n">
         <x:v>2</x:v>
@@ -8927,17 +8804,17 @@
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K89" s="42" t="str">
-        <x:v>إجبارية القسم</x:v>
+        <x:v>متطلبات الكلية</x:v>
       </x:c>
       <x:c r="L89" s="42" t="str">
-        <x:v>الشريعة 39.pdf</x:v>
+        <x:v>القراءات 47.pdf</x:v>
       </x:c>
       <x:c r="M89" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N89" s="42" t="str"/>
+      <x:c r="N89" s="42"/>
       <x:c r="O89" s="42" t="str">
-        <x:v>2001280-2||اصولالدعوةوالحسبة</x:v>
+        <x:v>2004102-2||مصطلحالحديث</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="34" customHeight="1">
@@ -8945,44 +8822,44 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B90" s="42" t="str">
-        <x:v>الشريعة</x:v>
+        <x:v>القراءات</x:v>
       </x:c>
       <x:c r="C90" s="42" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D90" s="42" t="str">
-        <x:v>قديمة</x:v>
+        <x:v>جديدة</x:v>
       </x:c>
       <x:c r="E90" s="43" t="n">
-        <x:v>39</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F90" s="43" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G90" s="43" t="str">
-        <x:v>2001301-2</x:v>
+        <x:v>2002112-3</x:v>
       </x:c>
       <x:c r="H90" s="42" t="str">
-        <x:v>تدوين السنة</x:v>
+        <x:v>عرض القراءات السبع (٢)</x:v>
       </x:c>
       <x:c r="I90" s="43" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J90" s="42" t="str">
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K90" s="42" t="str">
-        <x:v>إجبارية القسم</x:v>
+        <x:v>متطلبات الكلية</x:v>
       </x:c>
       <x:c r="L90" s="42" t="str">
-        <x:v>الشريعة 39.pdf</x:v>
+        <x:v>القراءات 47.pdf</x:v>
       </x:c>
       <x:c r="M90" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N90" s="42" t="str"/>
+      <x:c r="N90" s="42"/>
       <x:c r="O90" s="42" t="str">
-        <x:v>2001301-2||تدوينالسنة</x:v>
+        <x:v>2002112-3||عرضالقراءاتالسبع٢</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="34" customHeight="1">
@@ -8990,44 +8867,44 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B91" s="42" t="str">
-        <x:v>الشريعة</x:v>
+        <x:v>القراءات</x:v>
       </x:c>
       <x:c r="C91" s="42" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D91" s="42" t="str">
-        <x:v>قديمة</x:v>
+        <x:v>جديدة</x:v>
       </x:c>
       <x:c r="E91" s="43" t="n">
-        <x:v>39</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F91" s="43" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G91" s="43" t="str">
-        <x:v>2003325-1</x:v>
+        <x:v>2002352-2</x:v>
       </x:c>
       <x:c r="H91" s="42" t="str">
-        <x:v>نظام المرافعات الشرعية</x:v>
+        <x:v>التفسير التحليلي (2)</x:v>
       </x:c>
       <x:c r="I91" s="43" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J91" s="42" t="str">
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K91" s="42" t="str">
-        <x:v>إجبارية القسم</x:v>
+        <x:v>متطلبات الكلية</x:v>
       </x:c>
       <x:c r="L91" s="42" t="str">
-        <x:v>الشريعة 39.pdf</x:v>
+        <x:v>القراءات 47.pdf</x:v>
       </x:c>
       <x:c r="M91" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N91" s="42" t="str"/>
+      <x:c r="N91" s="42"/>
       <x:c r="O91" s="42" t="str">
-        <x:v>2003325-1||نظامالمرافعاتالشرعية</x:v>
+        <x:v>2002352-2||التفسيرالتحليلي2</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="34" customHeight="1">
@@ -9035,44 +8912,44 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B92" s="42" t="str">
-        <x:v>الشريعة</x:v>
+        <x:v>القراءات</x:v>
       </x:c>
       <x:c r="C92" s="42" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D92" s="42" t="str">
-        <x:v>قديمة</x:v>
+        <x:v>جديدة</x:v>
       </x:c>
       <x:c r="E92" s="43" t="n">
-        <x:v>39</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F92" s="43" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G92" s="43" t="str">
-        <x:v>2003328-1</x:v>
+        <x:v>2004205-2</x:v>
       </x:c>
       <x:c r="H92" s="42" t="str">
-        <x:v>نظام الإجراءات الجزائية</x:v>
+        <x:v>الحديث (1)</x:v>
       </x:c>
       <x:c r="I92" s="43" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J92" s="42" t="str">
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K92" s="42" t="str">
-        <x:v>إجبارية القسم</x:v>
+        <x:v>متطلبات الكلية</x:v>
       </x:c>
       <x:c r="L92" s="42" t="str">
-        <x:v>الشريعة 39.pdf</x:v>
+        <x:v>القراءات 47.pdf</x:v>
       </x:c>
       <x:c r="M92" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N92" s="42" t="str"/>
+      <x:c r="N92" s="42"/>
       <x:c r="O92" s="42" t="str">
-        <x:v>2003328-1||نظامالاجراءاتالجزايية</x:v>
+        <x:v>2004205-2||الحديث1</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="34" customHeight="1">
@@ -9080,44 +8957,44 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B93" s="42" t="str">
-        <x:v>الشريعة</x:v>
+        <x:v>القراءات</x:v>
       </x:c>
       <x:c r="C93" s="42" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D93" s="42" t="str">
-        <x:v>قديمة</x:v>
+        <x:v>جديدة</x:v>
       </x:c>
       <x:c r="E93" s="43" t="n">
-        <x:v>39</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F93" s="43" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G93" s="43" t="str">
-        <x:v>2001493-2</x:v>
+        <x:v>2002113-3</x:v>
       </x:c>
       <x:c r="H93" s="42" t="str">
-        <x:v>تخريج ودراسة الأسانيد</x:v>
+        <x:v>عرض القراءات السبع (٣)</x:v>
       </x:c>
       <x:c r="I93" s="43" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J93" s="42" t="str">
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K93" s="42" t="str">
-        <x:v>إجبارية القسم</x:v>
+        <x:v>متطلبات الكلية</x:v>
       </x:c>
       <x:c r="L93" s="42" t="str">
-        <x:v>الشريعة 39.pdf</x:v>
+        <x:v>القراءات 47.pdf</x:v>
       </x:c>
       <x:c r="M93" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N93" s="42" t="str"/>
+      <x:c r="N93" s="42"/>
       <x:c r="O93" s="42" t="str">
-        <x:v>2001493-2||تخريجودراسةالاسانيد</x:v>
+        <x:v>2002113-3||عرضالقراءاتالسبع٣</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="34" customHeight="1">
@@ -9125,25 +9002,25 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="B94" s="42" t="str">
-        <x:v>الشريعة</x:v>
+        <x:v>القراءات</x:v>
       </x:c>
       <x:c r="C94" s="42" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D94" s="42" t="str">
-        <x:v>قديمة</x:v>
+        <x:v>جديدة</x:v>
       </x:c>
       <x:c r="E94" s="43" t="n">
-        <x:v>39</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F94" s="43" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G94" s="43" t="str">
-        <x:v>20014201-2</x:v>
+        <x:v>2002238-2</x:v>
       </x:c>
       <x:c r="H94" s="42" t="str">
-        <x:v>التدريبات العملية</x:v>
+        <x:v>الوقف والابتداء</x:v>
       </x:c>
       <x:c r="I94" s="43" t="n">
         <x:v>2</x:v>
@@ -9152,17 +9029,17 @@
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K94" s="42" t="str">
-        <x:v>إجبارية القسم</x:v>
+        <x:v>متطلبات الكلية</x:v>
       </x:c>
       <x:c r="L94" s="42" t="str">
-        <x:v>الشريعة 39.pdf</x:v>
+        <x:v>القراءات 47.pdf</x:v>
       </x:c>
       <x:c r="M94" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N94" s="42" t="str"/>
+      <x:c r="N94" s="42"/>
       <x:c r="O94" s="42" t="str">
-        <x:v>20014201-2||التدريباتالعملية</x:v>
+        <x:v>2002238-2||الوقفوالابتداء</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="34" customHeight="1">
@@ -9182,13 +9059,13 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="F95" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G95" s="43" t="str">
-        <x:v>2001221-2</x:v>
+        <x:v>2002239-2</x:v>
       </x:c>
       <x:c r="H95" s="42" t="str">
-        <x:v>الفقه (1)</x:v>
+        <x:v>مصادر ومناهج المؤلفين في القراءات</x:v>
       </x:c>
       <x:c r="I95" s="43" t="n">
         <x:v>2</x:v>
@@ -9205,9 +9082,9 @@
       <x:c r="M95" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N95" s="42" t="str"/>
+      <x:c r="N95" s="42"/>
       <x:c r="O95" s="42" t="str">
-        <x:v>2001221-2||الفقه1</x:v>
+        <x:v>2002239-2||مصادرومناهجالمولفينفيالقراءات</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="34" customHeight="1">
@@ -9227,16 +9104,16 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="F96" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G96" s="43" t="str">
-        <x:v>2002111-3</x:v>
+        <x:v>2004209-2</x:v>
       </x:c>
       <x:c r="H96" s="42" t="str">
-        <x:v>عرض القراءات السبع (١)</x:v>
+        <x:v>الحديث (2)</x:v>
       </x:c>
       <x:c r="I96" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J96" s="42" t="str">
         <x:v>نظري</x:v>
@@ -9250,9 +9127,9 @@
       <x:c r="M96" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N96" s="42" t="str"/>
+      <x:c r="N96" s="42"/>
       <x:c r="O96" s="42" t="str">
-        <x:v>2002111-3||عرضالقراءاتالسبع١</x:v>
+        <x:v>2004209-2||الحديث2</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="34" customHeight="1">
@@ -9272,16 +9149,16 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="F97" s="43" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G97" s="43" t="str">
+        <x:v>2002114-3</x:v>
+      </x:c>
+      <x:c r="H97" s="42" t="str">
+        <x:v>عرض القراءات السبع (٤)</x:v>
+      </x:c>
+      <x:c r="I97" s="43" t="n">
         <x:v>3</x:v>
-      </x:c>
-      <x:c r="G97" s="43" t="str">
-        <x:v>2002280-2</x:v>
-      </x:c>
-      <x:c r="H97" s="42" t="str">
-        <x:v>تدريبات على الجمع والكيفيات</x:v>
-      </x:c>
-      <x:c r="I97" s="43" t="n">
-        <x:v>2</x:v>
       </x:c>
       <x:c r="J97" s="42" t="str">
         <x:v>نظري</x:v>
@@ -9295,9 +9172,9 @@
       <x:c r="M97" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N97" s="42" t="str"/>
+      <x:c r="N97" s="42"/>
       <x:c r="O97" s="42" t="str">
-        <x:v>2002280-2||تدريباتعليالجمعوالكيفيات</x:v>
+        <x:v>2002114-3||عرضالقراءاتالسبع٤</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="34" customHeight="1">
@@ -9317,13 +9194,13 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="F98" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G98" s="43" t="str">
-        <x:v>2004102-2</x:v>
+        <x:v>2004320-2</x:v>
       </x:c>
       <x:c r="H98" s="42" t="str">
-        <x:v>مصطلح الحديث</x:v>
+        <x:v>الحديث (3)</x:v>
       </x:c>
       <x:c r="I98" s="43" t="n">
         <x:v>2</x:v>
@@ -9340,9 +9217,9 @@
       <x:c r="M98" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N98" s="42" t="str"/>
+      <x:c r="N98" s="42"/>
       <x:c r="O98" s="42" t="str">
-        <x:v>2004102-2||مصطلحالحديث</x:v>
+        <x:v>2004320-2||الحديث3</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="34" customHeight="1">
@@ -9362,16 +9239,16 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="F99" s="43" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G99" s="43" t="str">
-        <x:v>2002112-3</x:v>
+        <x:v>2002460-2</x:v>
       </x:c>
       <x:c r="H99" s="42" t="str">
-        <x:v>عرض القراءات السبع (٢)</x:v>
+        <x:v>عرض القراءات الثلاث (١)</x:v>
       </x:c>
       <x:c r="I99" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J99" s="42" t="str">
         <x:v>نظري</x:v>
@@ -9385,9 +9262,9 @@
       <x:c r="M99" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N99" s="42" t="str"/>
+      <x:c r="N99" s="42"/>
       <x:c r="O99" s="42" t="str">
-        <x:v>2002112-3||عرضالقراءاتالسبع٢</x:v>
+        <x:v>2002460-2||عرضالقراءاتالثلاث١</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="34" customHeight="1">
@@ -9407,13 +9284,13 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="F100" s="43" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G100" s="43" t="str">
-        <x:v>2002352-2</x:v>
+        <x:v>2004403-2</x:v>
       </x:c>
       <x:c r="H100" s="42" t="str">
-        <x:v>التفسير التحليلي (2)</x:v>
+        <x:v>الأديان والفرق والمذاهب المعاصرة</x:v>
       </x:c>
       <x:c r="I100" s="43" t="n">
         <x:v>2</x:v>
@@ -9430,9 +9307,9 @@
       <x:c r="M100" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N100" s="42" t="str"/>
+      <x:c r="N100" s="42"/>
       <x:c r="O100" s="42" t="str">
-        <x:v>2002352-2||التفسيرالتحليلي2</x:v>
+        <x:v>2004403-2||الاديانوالفرقوالمذاهبالمعاصرة</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="34" customHeight="1">
@@ -9452,19 +9329,19 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="F101" s="43" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G101" s="43" t="str">
-        <x:v>2004205-2</x:v>
+        <x:v>2002266-6</x:v>
       </x:c>
       <x:c r="H101" s="42" t="str">
-        <x:v>الحديث (1)</x:v>
+        <x:v>التدريب التعاوني</x:v>
       </x:c>
       <x:c r="I101" s="43" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J101" s="42" t="str">
-        <x:v>نظري</x:v>
+        <x:v>تدريب</x:v>
       </x:c>
       <x:c r="K101" s="42" t="str">
         <x:v>متطلبات الكلية</x:v>
@@ -9475,9 +9352,9 @@
       <x:c r="M101" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N101" s="42" t="str"/>
+      <x:c r="N101" s="42"/>
       <x:c r="O101" s="42" t="str">
-        <x:v>2004205-2||الحديث1</x:v>
+        <x:v>2002266-6||التدريبالتعاوني</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="34" customHeight="1">
@@ -9497,16 +9374,16 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="F102" s="43" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G102" s="43" t="str">
-        <x:v>2002113-3</x:v>
+        <x:v>2002461-2</x:v>
       </x:c>
       <x:c r="H102" s="42" t="str">
-        <x:v>عرض القراءات السبع (٣)</x:v>
+        <x:v>عرض القراءات الثلاث (٢)</x:v>
       </x:c>
       <x:c r="I102" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J102" s="42" t="str">
         <x:v>نظري</x:v>
@@ -9520,9 +9397,9 @@
       <x:c r="M102" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N102" s="42" t="str"/>
+      <x:c r="N102" s="42"/>
       <x:c r="O102" s="42" t="str">
-        <x:v>2002113-3||عرضالقراءاتالسبع٣</x:v>
+        <x:v>2002461-2||عرضالقراءاتالثلاث٢</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="34" customHeight="1">
@@ -9536,19 +9413,19 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D103" s="42" t="str">
-        <x:v>جديدة</x:v>
+        <x:v>قديمة</x:v>
       </x:c>
       <x:c r="E103" s="43" t="n">
-        <x:v>47</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F103" s="43" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G103" s="43" t="str">
-        <x:v>2002238-2</x:v>
+        <x:v>2001205-2</x:v>
       </x:c>
       <x:c r="H103" s="42" t="str">
-        <x:v>الوقف والابتداء</x:v>
+        <x:v>الحديث (1)</x:v>
       </x:c>
       <x:c r="I103" s="43" t="n">
         <x:v>2</x:v>
@@ -9557,17 +9434,17 @@
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K103" s="42" t="str">
-        <x:v>متطلبات الكلية</x:v>
+        <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L103" s="42" t="str">
-        <x:v>القراءات 47.pdf</x:v>
+        <x:v>القراءات 38.pdf</x:v>
       </x:c>
       <x:c r="M103" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N103" s="42" t="str"/>
+      <x:c r="N103" s="42"/>
       <x:c r="O103" s="42" t="str">
-        <x:v>2002238-2||الوقفوالابتداء</x:v>
+        <x:v>2001205-2||الحديث1</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="34" customHeight="1">
@@ -9581,19 +9458,19 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D104" s="42" t="str">
-        <x:v>جديدة</x:v>
+        <x:v>قديمة</x:v>
       </x:c>
       <x:c r="E104" s="43" t="n">
-        <x:v>47</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F104" s="43" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G104" s="43" t="str">
-        <x:v>2002239-2</x:v>
+        <x:v>2001221-2</x:v>
       </x:c>
       <x:c r="H104" s="42" t="str">
-        <x:v>مصادر ومناهج المؤلفين في القراءات</x:v>
+        <x:v>الفقه (1)</x:v>
       </x:c>
       <x:c r="I104" s="43" t="n">
         <x:v>2</x:v>
@@ -9602,17 +9479,17 @@
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K104" s="42" t="str">
-        <x:v>متطلبات الكلية</x:v>
+        <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L104" s="42" t="str">
-        <x:v>القراءات 47.pdf</x:v>
+        <x:v>القراءات 38.pdf</x:v>
       </x:c>
       <x:c r="M104" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N104" s="42" t="str"/>
+      <x:c r="N104" s="42"/>
       <x:c r="O104" s="42" t="str">
-        <x:v>2002239-2||مصادرومناهجالمولفينفيالقراءات</x:v>
+        <x:v>2001221-2||الفقه1</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="34" customHeight="1">
@@ -9626,19 +9503,19 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D105" s="42" t="str">
-        <x:v>جديدة</x:v>
+        <x:v>قديمة</x:v>
       </x:c>
       <x:c r="E105" s="43" t="n">
-        <x:v>47</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F105" s="43" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G105" s="43" t="str">
-        <x:v>2004209-2</x:v>
+        <x:v>2001273-2</x:v>
       </x:c>
       <x:c r="H105" s="42" t="str">
-        <x:v>الحديث (2)</x:v>
+        <x:v>العقيدة (1)</x:v>
       </x:c>
       <x:c r="I105" s="43" t="n">
         <x:v>2</x:v>
@@ -9647,17 +9524,17 @@
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K105" s="42" t="str">
-        <x:v>متطلبات الكلية</x:v>
+        <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L105" s="42" t="str">
-        <x:v>القراءات 47.pdf</x:v>
+        <x:v>القراءات 38.pdf</x:v>
       </x:c>
       <x:c r="M105" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N105" s="42" t="str"/>
+      <x:c r="N105" s="42"/>
       <x:c r="O105" s="42" t="str">
-        <x:v>2004209-2||الحديث2</x:v>
+        <x:v>2001273-2||العقيدة1</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="34" customHeight="1">
@@ -9671,38 +9548,38 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D106" s="42" t="str">
-        <x:v>جديدة</x:v>
+        <x:v>قديمة</x:v>
       </x:c>
       <x:c r="E106" s="43" t="n">
-        <x:v>47</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F106" s="43" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G106" s="43" t="str">
-        <x:v>2002114-3</x:v>
+        <x:v>2001209-2</x:v>
       </x:c>
       <x:c r="H106" s="42" t="str">
-        <x:v>عرض القراءات السبع (٤)</x:v>
+        <x:v>الحديث (2)</x:v>
       </x:c>
       <x:c r="I106" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J106" s="42" t="str">
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K106" s="42" t="str">
-        <x:v>متطلبات الكلية</x:v>
+        <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L106" s="42" t="str">
-        <x:v>القراءات 47.pdf</x:v>
+        <x:v>القراءات 38.pdf</x:v>
       </x:c>
       <x:c r="M106" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N106" s="42" t="str"/>
+      <x:c r="N106" s="42"/>
       <x:c r="O106" s="42" t="str">
-        <x:v>2002114-3||عرضالقراءاتالسبع٤</x:v>
+        <x:v>2001209-2||الحديث2</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="34" customHeight="1">
@@ -9716,19 +9593,19 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D107" s="42" t="str">
-        <x:v>جديدة</x:v>
+        <x:v>قديمة</x:v>
       </x:c>
       <x:c r="E107" s="43" t="n">
-        <x:v>47</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F107" s="43" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G107" s="43" t="str">
-        <x:v>2004320-2</x:v>
+        <x:v>2001322-2</x:v>
       </x:c>
       <x:c r="H107" s="42" t="str">
-        <x:v>الحديث (3)</x:v>
+        <x:v>الفقه (2)</x:v>
       </x:c>
       <x:c r="I107" s="43" t="n">
         <x:v>2</x:v>
@@ -9737,17 +9614,17 @@
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K107" s="42" t="str">
-        <x:v>متطلبات الكلية</x:v>
+        <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L107" s="42" t="str">
-        <x:v>القراءات 47.pdf</x:v>
+        <x:v>القراءات 38.pdf</x:v>
       </x:c>
       <x:c r="M107" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N107" s="42" t="str"/>
+      <x:c r="N107" s="42"/>
       <x:c r="O107" s="42" t="str">
-        <x:v>2004320-2||الحديث3</x:v>
+        <x:v>2001322-2||الفقه2</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="34" customHeight="1">
@@ -9761,19 +9638,19 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D108" s="42" t="str">
-        <x:v>جديدة</x:v>
+        <x:v>قديمة</x:v>
       </x:c>
       <x:c r="E108" s="43" t="n">
-        <x:v>47</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F108" s="43" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G108" s="43" t="str">
-        <x:v>2002460-2</x:v>
+        <x:v>2001320-2</x:v>
       </x:c>
       <x:c r="H108" s="42" t="str">
-        <x:v>عرض القراءات الثلاث (١)</x:v>
+        <x:v>الحديث (3)</x:v>
       </x:c>
       <x:c r="I108" s="43" t="n">
         <x:v>2</x:v>
@@ -9782,17 +9659,17 @@
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K108" s="42" t="str">
-        <x:v>متطلبات الكلية</x:v>
+        <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L108" s="42" t="str">
-        <x:v>القراءات 47.pdf</x:v>
+        <x:v>القراءات 38.pdf</x:v>
       </x:c>
       <x:c r="M108" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N108" s="42" t="str"/>
+      <x:c r="N108" s="42"/>
       <x:c r="O108" s="42" t="str">
-        <x:v>2002460-2||عرضالقراءاتالثلاث١</x:v>
+        <x:v>2001320-2||الحديث3</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="34" customHeight="1">
@@ -9800,7 +9677,7 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B109" s="42" t="str">
-        <x:v>القراءات</x:v>
+        <x:v>القرآن وعلومه</x:v>
       </x:c>
       <x:c r="C109" s="42" t="str">
         <x:v>بكالوريوس</x:v>
@@ -9812,13 +9689,13 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="F109" s="43" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G109" s="43" t="str">
-        <x:v>2004403-2</x:v>
+        <x:v>2004102-2</x:v>
       </x:c>
       <x:c r="H109" s="42" t="str">
-        <x:v>الأديان والفرق والمذاهب المعاصرة</x:v>
+        <x:v>مصطلح الحديث</x:v>
       </x:c>
       <x:c r="I109" s="43" t="n">
         <x:v>2</x:v>
@@ -9830,14 +9707,14 @@
         <x:v>متطلبات الكلية</x:v>
       </x:c>
       <x:c r="L109" s="42" t="str">
-        <x:v>القراءات 47.pdf</x:v>
+        <x:v>القرآن وعلومه 47.pdf</x:v>
       </x:c>
       <x:c r="M109" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N109" s="42" t="str"/>
+      <x:c r="N109" s="42"/>
       <x:c r="O109" s="42" t="str">
-        <x:v>2004403-2||الاديانوالفرقوالمذاهبالمعاصرة</x:v>
+        <x:v>2004102-2||مصطلحالحديث</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="34" customHeight="1">
@@ -9845,7 +9722,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B110" s="42" t="str">
-        <x:v>القراءات</x:v>
+        <x:v>القرآن وعلومه</x:v>
       </x:c>
       <x:c r="C110" s="42" t="str">
         <x:v>بكالوريوس</x:v>
@@ -9857,32 +9734,32 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="F110" s="43" t="n">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G110" s="43" t="str">
-        <x:v>2002266-6</x:v>
+        <x:v>2001221-2</x:v>
       </x:c>
       <x:c r="H110" s="42" t="str">
-        <x:v>التدريب التعاوني</x:v>
+        <x:v>الفقه (1)</x:v>
       </x:c>
       <x:c r="I110" s="43" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J110" s="42" t="str">
-        <x:v>تدريب</x:v>
+        <x:v>نظري</x:v>
       </x:c>
       <x:c r="K110" s="42" t="str">
-        <x:v>متطلبات الكلية</x:v>
+        <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L110" s="42" t="str">
-        <x:v>القراءات 47.pdf</x:v>
+        <x:v>القرآن وعلومه 47.pdf</x:v>
       </x:c>
       <x:c r="M110" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N110" s="42" t="str"/>
+      <x:c r="N110" s="42"/>
       <x:c r="O110" s="42" t="str">
-        <x:v>2002266-6||التدريبالتعاوني</x:v>
+        <x:v>2001221-2||الفقه1</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="34" customHeight="1">
@@ -9890,7 +9767,7 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="B111" s="42" t="str">
-        <x:v>القراءات</x:v>
+        <x:v>القرآن وعلومه</x:v>
       </x:c>
       <x:c r="C111" s="42" t="str">
         <x:v>بكالوريوس</x:v>
@@ -9902,13 +9779,13 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="F111" s="43" t="n">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G111" s="43" t="str">
-        <x:v>2002461-2</x:v>
+        <x:v>2003220-2</x:v>
       </x:c>
       <x:c r="H111" s="42" t="str">
-        <x:v>عرض القراءات الثلاث (٢)</x:v>
+        <x:v>المدخل لدراسة الأنظمة</x:v>
       </x:c>
       <x:c r="I111" s="43" t="n">
         <x:v>2</x:v>
@@ -9917,17 +9794,17 @@
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K111" s="42" t="str">
-        <x:v>متطلبات الكلية</x:v>
+        <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L111" s="42" t="str">
-        <x:v>القراءات 47.pdf</x:v>
+        <x:v>القرآن وعلومه 47.pdf</x:v>
       </x:c>
       <x:c r="M111" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N111" s="42" t="str"/>
+      <x:c r="N111" s="42"/>
       <x:c r="O111" s="42" t="str">
-        <x:v>2002461-2||عرضالقراءاتالثلاث٢</x:v>
+        <x:v>2003220-2||المدخللدراسةالانظمة</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="34" customHeight="1">
@@ -9935,22 +9812,22 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="B112" s="42" t="str">
-        <x:v>القراءات</x:v>
+        <x:v>القرآن وعلومه</x:v>
       </x:c>
       <x:c r="C112" s="42" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D112" s="42" t="str">
-        <x:v>قديمة</x:v>
+        <x:v>جديدة</x:v>
       </x:c>
       <x:c r="E112" s="43" t="n">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F112" s="43" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G112" s="43" t="str">
-        <x:v>2001205-2</x:v>
+        <x:v>2004205-2</x:v>
       </x:c>
       <x:c r="H112" s="42" t="str">
         <x:v>الحديث (1)</x:v>
@@ -9962,17 +9839,17 @@
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K112" s="42" t="str">
-        <x:v>إجبارية القسم</x:v>
+        <x:v>متطلبات الكلية</x:v>
       </x:c>
       <x:c r="L112" s="42" t="str">
-        <x:v>القراءات 38.pdf</x:v>
+        <x:v>القرآن وعلومه 47.pdf</x:v>
       </x:c>
       <x:c r="M112" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N112" s="42" t="str"/>
+      <x:c r="N112" s="42"/>
       <x:c r="O112" s="42" t="str">
-        <x:v>2001205-2||الحديث1</x:v>
+        <x:v>2004205-2||الحديث1</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="34" customHeight="1">
@@ -9980,25 +9857,25 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="B113" s="42" t="str">
-        <x:v>القراءات</x:v>
+        <x:v>القرآن وعلومه</x:v>
       </x:c>
       <x:c r="C113" s="42" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D113" s="42" t="str">
-        <x:v>قديمة</x:v>
+        <x:v>جديدة</x:v>
       </x:c>
       <x:c r="E113" s="43" t="n">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F113" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G113" s="43" t="str">
-        <x:v>2001221-2</x:v>
+        <x:v>2001322-2</x:v>
       </x:c>
       <x:c r="H113" s="42" t="str">
-        <x:v>الفقه (1)</x:v>
+        <x:v>الفقه (2)</x:v>
       </x:c>
       <x:c r="I113" s="43" t="n">
         <x:v>2</x:v>
@@ -10010,14 +9887,14 @@
         <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L113" s="42" t="str">
-        <x:v>القراءات 38.pdf</x:v>
+        <x:v>القرآن وعلومه 47.pdf</x:v>
       </x:c>
       <x:c r="M113" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N113" s="42" t="str"/>
+      <x:c r="N113" s="42"/>
       <x:c r="O113" s="42" t="str">
-        <x:v>2001221-2||الفقه1</x:v>
+        <x:v>2001322-2||الفقه2</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="34" customHeight="1">
@@ -10025,25 +9902,25 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="B114" s="42" t="str">
-        <x:v>القراءات</x:v>
+        <x:v>القرآن وعلومه</x:v>
       </x:c>
       <x:c r="C114" s="42" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D114" s="42" t="str">
-        <x:v>قديمة</x:v>
+        <x:v>جديدة</x:v>
       </x:c>
       <x:c r="E114" s="43" t="n">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F114" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G114" s="43" t="str">
-        <x:v>2001273-2</x:v>
+        <x:v>2004209-2</x:v>
       </x:c>
       <x:c r="H114" s="42" t="str">
-        <x:v>العقيدة (1)</x:v>
+        <x:v>الحديث (2)</x:v>
       </x:c>
       <x:c r="I114" s="43" t="n">
         <x:v>2</x:v>
@@ -10052,17 +9929,17 @@
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K114" s="42" t="str">
-        <x:v>إجبارية القسم</x:v>
+        <x:v>متطلبات الكلية</x:v>
       </x:c>
       <x:c r="L114" s="42" t="str">
-        <x:v>القراءات 38.pdf</x:v>
+        <x:v>القرآن وعلومه 47.pdf</x:v>
       </x:c>
       <x:c r="M114" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N114" s="42" t="str"/>
+      <x:c r="N114" s="42"/>
       <x:c r="O114" s="42" t="str">
-        <x:v>2001273-2||العقيدة1</x:v>
+        <x:v>2004209-2||الحديث2</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="34" customHeight="1">
@@ -10070,25 +9947,25 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B115" s="42" t="str">
-        <x:v>القراءات</x:v>
+        <x:v>القرآن وعلومه</x:v>
       </x:c>
       <x:c r="C115" s="42" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D115" s="42" t="str">
-        <x:v>قديمة</x:v>
+        <x:v>جديدة</x:v>
       </x:c>
       <x:c r="E115" s="43" t="n">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F115" s="43" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G115" s="43" t="str">
-        <x:v>2001209-2</x:v>
+        <x:v>2001113-2</x:v>
       </x:c>
       <x:c r="H115" s="42" t="str">
-        <x:v>الحديث (2)</x:v>
+        <x:v>أصول الفقه (1)</x:v>
       </x:c>
       <x:c r="I115" s="43" t="n">
         <x:v>2</x:v>
@@ -10100,14 +9977,14 @@
         <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L115" s="42" t="str">
-        <x:v>القراءات 38.pdf</x:v>
+        <x:v>القرآن وعلومه 47.pdf</x:v>
       </x:c>
       <x:c r="M115" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N115" s="42" t="str"/>
+      <x:c r="N115" s="42"/>
       <x:c r="O115" s="42" t="str">
-        <x:v>2001209-2||الحديث2</x:v>
+        <x:v>2001113-2||اصولالفقه1</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="34" customHeight="1">
@@ -10115,25 +9992,25 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="B116" s="42" t="str">
-        <x:v>القراءات</x:v>
+        <x:v>القرآن وعلومه</x:v>
       </x:c>
       <x:c r="C116" s="42" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D116" s="42" t="str">
-        <x:v>قديمة</x:v>
+        <x:v>جديدة</x:v>
       </x:c>
       <x:c r="E116" s="43" t="n">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F116" s="43" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G116" s="43" t="str">
-        <x:v>2001322-2</x:v>
+        <x:v>2001317-2</x:v>
       </x:c>
       <x:c r="H116" s="42" t="str">
-        <x:v>الفقه (2)</x:v>
+        <x:v>الفقه (3)</x:v>
       </x:c>
       <x:c r="I116" s="43" t="n">
         <x:v>2</x:v>
@@ -10145,14 +10022,14 @@
         <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L116" s="42" t="str">
-        <x:v>القراءات 38.pdf</x:v>
+        <x:v>القرآن وعلومه 47.pdf</x:v>
       </x:c>
       <x:c r="M116" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N116" s="42" t="str"/>
+      <x:c r="N116" s="42"/>
       <x:c r="O116" s="42" t="str">
-        <x:v>2001322-2||الفقه2</x:v>
+        <x:v>2001317-2||الفقه3</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="34" customHeight="1">
@@ -10160,22 +10037,22 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="B117" s="42" t="str">
-        <x:v>القراءات</x:v>
+        <x:v>القرآن وعلومه</x:v>
       </x:c>
       <x:c r="C117" s="42" t="str">
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D117" s="42" t="str">
-        <x:v>قديمة</x:v>
+        <x:v>جديدة</x:v>
       </x:c>
       <x:c r="E117" s="43" t="n">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F117" s="43" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G117" s="43" t="str">
-        <x:v>2001320-2</x:v>
+        <x:v>2004320-2</x:v>
       </x:c>
       <x:c r="H117" s="42" t="str">
         <x:v>الحديث (3)</x:v>
@@ -10187,17 +10064,17 @@
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K117" s="42" t="str">
-        <x:v>إجبارية القسم</x:v>
+        <x:v>متطلبات الكلية</x:v>
       </x:c>
       <x:c r="L117" s="42" t="str">
-        <x:v>القراءات 38.pdf</x:v>
+        <x:v>القرآن وعلومه 47.pdf</x:v>
       </x:c>
       <x:c r="M117" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N117" s="42" t="str"/>
+      <x:c r="N117" s="42"/>
       <x:c r="O117" s="42" t="str">
-        <x:v>2001320-2||الحديث3</x:v>
+        <x:v>2004320-2||الحديث3</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="34" customHeight="1">
@@ -10217,13 +10094,13 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="F118" s="43" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G118" s="43" t="str">
-        <x:v>2004102-2</x:v>
+        <x:v>2001330-2</x:v>
       </x:c>
       <x:c r="H118" s="42" t="str">
-        <x:v>مصطلح الحديث</x:v>
+        <x:v>أصول الفقه (2)</x:v>
       </x:c>
       <x:c r="I118" s="43" t="n">
         <x:v>2</x:v>
@@ -10232,7 +10109,7 @@
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K118" s="42" t="str">
-        <x:v>متطلبات الكلية</x:v>
+        <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L118" s="42" t="str">
         <x:v>القرآن وعلومه 47.pdf</x:v>
@@ -10240,9 +10117,9 @@
       <x:c r="M118" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N118" s="42" t="str"/>
+      <x:c r="N118" s="42"/>
       <x:c r="O118" s="42" t="str">
-        <x:v>2004102-2||مصطلحالحديث</x:v>
+        <x:v>2001330-2||اصولالفقه2</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="34" customHeight="1">
@@ -10262,13 +10139,13 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="F119" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G119" s="43" t="str">
-        <x:v>2001221-2</x:v>
+        <x:v>2004403-2</x:v>
       </x:c>
       <x:c r="H119" s="42" t="str">
-        <x:v>الفقه (1)</x:v>
+        <x:v>الأديان والفرق والمذاهب المعاصرة</x:v>
       </x:c>
       <x:c r="I119" s="43" t="n">
         <x:v>2</x:v>
@@ -10277,7 +10154,7 @@
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K119" s="42" t="str">
-        <x:v>إجبارية القسم</x:v>
+        <x:v>متطلبات الكلية</x:v>
       </x:c>
       <x:c r="L119" s="42" t="str">
         <x:v>القرآن وعلومه 47.pdf</x:v>
@@ -10285,9 +10162,9 @@
       <x:c r="M119" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N119" s="42" t="str"/>
+      <x:c r="N119" s="42"/>
       <x:c r="O119" s="42" t="str">
-        <x:v>2001221-2||الفقه1</x:v>
+        <x:v>2004403-2||الاديانوالفرقوالمذاهبالمعاصرة</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="34" customHeight="1">
@@ -10307,13 +10184,13 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="F120" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G120" s="43" t="str">
-        <x:v>2003220-2</x:v>
+        <x:v>20024101-2</x:v>
       </x:c>
       <x:c r="H120" s="42" t="str">
-        <x:v>المدخل لدراسة الأنظمة</x:v>
+        <x:v>قاعة بحث</x:v>
       </x:c>
       <x:c r="I120" s="43" t="n">
         <x:v>2</x:v>
@@ -10330,9 +10207,9 @@
       <x:c r="M120" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N120" s="42" t="str"/>
+      <x:c r="N120" s="42"/>
       <x:c r="O120" s="42" t="str">
-        <x:v>2003220-2||المدخللدراسةالانظمة</x:v>
+        <x:v>20024101-2||قاعةبحث</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="34" customHeight="1">
@@ -10352,22 +10229,22 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="F121" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G121" s="43" t="str">
-        <x:v>2004205-2</x:v>
+        <x:v>2002266-5</x:v>
       </x:c>
       <x:c r="H121" s="42" t="str">
-        <x:v>الحديث (1)</x:v>
+        <x:v>التدريب التعاوني</x:v>
       </x:c>
       <x:c r="I121" s="43" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="J121" s="42" t="str">
-        <x:v>نظري</x:v>
+        <x:v>تدريب</x:v>
       </x:c>
       <x:c r="K121" s="42" t="str">
-        <x:v>متطلبات الكلية</x:v>
+        <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L121" s="42" t="str">
         <x:v>القرآن وعلومه 47.pdf</x:v>
@@ -10375,9 +10252,9 @@
       <x:c r="M121" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N121" s="42" t="str"/>
+      <x:c r="N121" s="42"/>
       <x:c r="O121" s="42" t="str">
-        <x:v>2004205-2||الحديث1</x:v>
+        <x:v>2002266-5||التدريبالتعاوني</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="34" customHeight="1">
@@ -10391,19 +10268,19 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D122" s="42" t="str">
-        <x:v>جديدة</x:v>
+        <x:v>قديمة</x:v>
       </x:c>
       <x:c r="E122" s="43" t="n">
-        <x:v>47</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F122" s="43" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G122" s="43" t="str">
-        <x:v>2001322-2</x:v>
+        <x:v>2001160-2</x:v>
       </x:c>
       <x:c r="H122" s="42" t="str">
-        <x:v>الفقه (2)</x:v>
+        <x:v>المدخل لدراسة الشريعة</x:v>
       </x:c>
       <x:c r="I122" s="43" t="n">
         <x:v>2</x:v>
@@ -10415,14 +10292,14 @@
         <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L122" s="42" t="str">
-        <x:v>القرآن وعلومه 47.pdf</x:v>
+        <x:v>القرآن وعلومه 39.pdf</x:v>
       </x:c>
       <x:c r="M122" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N122" s="42" t="str"/>
+      <x:c r="N122" s="42"/>
       <x:c r="O122" s="42" t="str">
-        <x:v>2001322-2||الفقه2</x:v>
+        <x:v>2001160-2||المدخللدراسةالشريعة</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="34" customHeight="1">
@@ -10436,19 +10313,19 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D123" s="42" t="str">
-        <x:v>جديدة</x:v>
+        <x:v>قديمة</x:v>
       </x:c>
       <x:c r="E123" s="43" t="n">
-        <x:v>47</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F123" s="43" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G123" s="43" t="str">
-        <x:v>2004209-2</x:v>
+        <x:v>101221-2</x:v>
       </x:c>
       <x:c r="H123" s="42" t="str">
-        <x:v>الحديث (2)</x:v>
+        <x:v>الفقه (1)</x:v>
       </x:c>
       <x:c r="I123" s="43" t="n">
         <x:v>2</x:v>
@@ -10457,17 +10334,17 @@
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K123" s="42" t="str">
-        <x:v>متطلبات الكلية</x:v>
+        <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L123" s="42" t="str">
-        <x:v>القرآن وعلومه 47.pdf</x:v>
+        <x:v>القرآن وعلومه 39.pdf</x:v>
       </x:c>
       <x:c r="M123" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N123" s="42" t="str"/>
+      <x:c r="N123" s="42"/>
       <x:c r="O123" s="42" t="str">
-        <x:v>2004209-2||الحديث2</x:v>
+        <x:v>101221-2||الفقه1</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="34" customHeight="1">
@@ -10481,19 +10358,19 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D124" s="42" t="str">
-        <x:v>جديدة</x:v>
+        <x:v>قديمة</x:v>
       </x:c>
       <x:c r="E124" s="43" t="n">
-        <x:v>47</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F124" s="43" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G124" s="43" t="str">
-        <x:v>2001113-2</x:v>
+        <x:v>2001205-2</x:v>
       </x:c>
       <x:c r="H124" s="42" t="str">
-        <x:v>أصول الفقه (1)</x:v>
+        <x:v>الحديث (1)</x:v>
       </x:c>
       <x:c r="I124" s="43" t="n">
         <x:v>2</x:v>
@@ -10505,14 +10382,14 @@
         <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L124" s="42" t="str">
-        <x:v>القرآن وعلومه 47.pdf</x:v>
+        <x:v>القرآن وعلومه 39.pdf</x:v>
       </x:c>
       <x:c r="M124" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N124" s="42" t="str"/>
+      <x:c r="N124" s="42"/>
       <x:c r="O124" s="42" t="str">
-        <x:v>2001113-2||اصولالفقه1</x:v>
+        <x:v>2001205-2||الحديث1</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="34" customHeight="1">
@@ -10526,19 +10403,19 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D125" s="42" t="str">
-        <x:v>جديدة</x:v>
+        <x:v>قديمة</x:v>
       </x:c>
       <x:c r="E125" s="43" t="n">
-        <x:v>47</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F125" s="43" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G125" s="43" t="str">
-        <x:v>2001317-2</x:v>
+        <x:v>2001209-2</x:v>
       </x:c>
       <x:c r="H125" s="42" t="str">
-        <x:v>الفقه (3)</x:v>
+        <x:v>الحديث (2)</x:v>
       </x:c>
       <x:c r="I125" s="43" t="n">
         <x:v>2</x:v>
@@ -10550,14 +10427,14 @@
         <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L125" s="42" t="str">
-        <x:v>القرآن وعلومه 47.pdf</x:v>
+        <x:v>القرآن وعلومه 39.pdf</x:v>
       </x:c>
       <x:c r="M125" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N125" s="42" t="str"/>
+      <x:c r="N125" s="42"/>
       <x:c r="O125" s="42" t="str">
-        <x:v>2001317-2||الفقه3</x:v>
+        <x:v>2001209-2||الحديث2</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="34" customHeight="1">
@@ -10571,19 +10448,19 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D126" s="42" t="str">
-        <x:v>جديدة</x:v>
+        <x:v>قديمة</x:v>
       </x:c>
       <x:c r="E126" s="43" t="n">
-        <x:v>47</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F126" s="43" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G126" s="43" t="str">
-        <x:v>2004320-2</x:v>
+        <x:v>2001322-2</x:v>
       </x:c>
       <x:c r="H126" s="42" t="str">
-        <x:v>الحديث (3)</x:v>
+        <x:v>الفقه (2)</x:v>
       </x:c>
       <x:c r="I126" s="43" t="n">
         <x:v>2</x:v>
@@ -10592,17 +10469,17 @@
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K126" s="42" t="str">
-        <x:v>متطلبات الكلية</x:v>
+        <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L126" s="42" t="str">
-        <x:v>القرآن وعلومه 47.pdf</x:v>
+        <x:v>القرآن وعلومه 39.pdf</x:v>
       </x:c>
       <x:c r="M126" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N126" s="42" t="str"/>
+      <x:c r="N126" s="42"/>
       <x:c r="O126" s="42" t="str">
-        <x:v>2004320-2||الحديث3</x:v>
+        <x:v>2001322-2||الفقه2</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="34" customHeight="1">
@@ -10616,19 +10493,19 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D127" s="42" t="str">
-        <x:v>جديدة</x:v>
+        <x:v>قديمة</x:v>
       </x:c>
       <x:c r="E127" s="43" t="n">
-        <x:v>47</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F127" s="43" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G127" s="43" t="str">
-        <x:v>2001330-2</x:v>
+        <x:v>2003220-2</x:v>
       </x:c>
       <x:c r="H127" s="42" t="str">
-        <x:v>أصول الفقه (2)</x:v>
+        <x:v>المدخل لدراسة الأنظمة</x:v>
       </x:c>
       <x:c r="I127" s="43" t="n">
         <x:v>2</x:v>
@@ -10640,14 +10517,14 @@
         <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L127" s="42" t="str">
-        <x:v>القرآن وعلومه 47.pdf</x:v>
+        <x:v>القرآن وعلومه 39.pdf</x:v>
       </x:c>
       <x:c r="M127" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N127" s="42" t="str"/>
+      <x:c r="N127" s="42"/>
       <x:c r="O127" s="42" t="str">
-        <x:v>2001330-2||اصولالفقه2</x:v>
+        <x:v>2003220-2||المدخللدراسةالانظمة</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="34" customHeight="1">
@@ -10661,19 +10538,19 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D128" s="42" t="str">
-        <x:v>جديدة</x:v>
+        <x:v>قديمة</x:v>
       </x:c>
       <x:c r="E128" s="43" t="n">
-        <x:v>47</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F128" s="43" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G128" s="43" t="str">
-        <x:v>2004403-2</x:v>
+        <x:v>2001113-2</x:v>
       </x:c>
       <x:c r="H128" s="42" t="str">
-        <x:v>الأديان والفرق والمذاهب المعاصرة</x:v>
+        <x:v>أصول الفقه (1)</x:v>
       </x:c>
       <x:c r="I128" s="43" t="n">
         <x:v>2</x:v>
@@ -10682,17 +10559,17 @@
         <x:v>نظري</x:v>
       </x:c>
       <x:c r="K128" s="42" t="str">
-        <x:v>متطلبات الكلية</x:v>
+        <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L128" s="42" t="str">
-        <x:v>القرآن وعلومه 47.pdf</x:v>
+        <x:v>القرآن وعلومه 39.pdf</x:v>
       </x:c>
       <x:c r="M128" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N128" s="42" t="str"/>
+      <x:c r="N128" s="42"/>
       <x:c r="O128" s="42" t="str">
-        <x:v>2004403-2||الاديانوالفرقوالمذاهبالمعاصرة</x:v>
+        <x:v>2001113-2||اصولالفقه1</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="34" customHeight="1">
@@ -10706,19 +10583,19 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D129" s="42" t="str">
-        <x:v>جديدة</x:v>
+        <x:v>قديمة</x:v>
       </x:c>
       <x:c r="E129" s="43" t="n">
-        <x:v>47</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F129" s="43" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G129" s="43" t="str">
-        <x:v>20024101-2</x:v>
+        <x:v>2001317-2</x:v>
       </x:c>
       <x:c r="H129" s="42" t="str">
-        <x:v>قاعة بحث</x:v>
+        <x:v>الفقه (3)</x:v>
       </x:c>
       <x:c r="I129" s="43" t="n">
         <x:v>2</x:v>
@@ -10730,14 +10607,14 @@
         <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L129" s="42" t="str">
-        <x:v>القرآن وعلومه 47.pdf</x:v>
+        <x:v>القرآن وعلومه 39.pdf</x:v>
       </x:c>
       <x:c r="M129" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N129" s="42" t="str"/>
+      <x:c r="N129" s="42"/>
       <x:c r="O129" s="42" t="str">
-        <x:v>20024101-2||قاعةبحث</x:v>
+        <x:v>2001317-2||الفقه3</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="34" customHeight="1">
@@ -10751,38 +10628,38 @@
         <x:v>بكالوريوس</x:v>
       </x:c>
       <x:c r="D130" s="42" t="str">
-        <x:v>جديدة</x:v>
+        <x:v>قديمة</x:v>
       </x:c>
       <x:c r="E130" s="43" t="n">
-        <x:v>47</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F130" s="43" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G130" s="43" t="str">
-        <x:v>2002266-5</x:v>
+        <x:v>2001320-2</x:v>
       </x:c>
       <x:c r="H130" s="42" t="str">
-        <x:v>التدريب التعاوني</x:v>
+        <x:v>الحديث (3)</x:v>
       </x:c>
       <x:c r="I130" s="43" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J130" s="42" t="str">
-        <x:v>تدريب</x:v>
+        <x:v>نظري</x:v>
       </x:c>
       <x:c r="K130" s="42" t="str">
         <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L130" s="42" t="str">
-        <x:v>القرآن وعلومه 47.pdf</x:v>
+        <x:v>القرآن وعلومه 39.pdf</x:v>
       </x:c>
       <x:c r="M130" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N130" s="42" t="str"/>
+      <x:c r="N130" s="42"/>
       <x:c r="O130" s="42" t="str">
-        <x:v>2002266-5||التدريبالتعاوني</x:v>
+        <x:v>2001320-2||الحديث3</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="34" customHeight="1">
@@ -10802,13 +10679,13 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="F131" s="43" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G131" s="43" t="str">
-        <x:v>2001160-2</x:v>
+        <x:v>2001330-2</x:v>
       </x:c>
       <x:c r="H131" s="42" t="str">
-        <x:v>المدخل لدراسة الشريعة</x:v>
+        <x:v>أصول الفقه (2)</x:v>
       </x:c>
       <x:c r="I131" s="43" t="n">
         <x:v>2</x:v>
@@ -10825,9 +10702,9 @@
       <x:c r="M131" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N131" s="42" t="str"/>
+      <x:c r="N131" s="42"/>
       <x:c r="O131" s="42" t="str">
-        <x:v>2001160-2||المدخللدراسةالشريعة</x:v>
+        <x:v>2001330-2||اصولالفقه2</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="34" customHeight="1">
@@ -10847,13 +10724,13 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="F132" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G132" s="43" t="str">
-        <x:v>101221-2</x:v>
+        <x:v>2001424-2</x:v>
       </x:c>
       <x:c r="H132" s="42" t="str">
-        <x:v>الفقه (1)</x:v>
+        <x:v>الفقه (4)</x:v>
       </x:c>
       <x:c r="I132" s="43" t="n">
         <x:v>2</x:v>
@@ -10870,9 +10747,9 @@
       <x:c r="M132" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N132" s="42" t="str"/>
+      <x:c r="N132" s="42"/>
       <x:c r="O132" s="42" t="str">
-        <x:v>101221-2||الفقه1</x:v>
+        <x:v>2001424-2||الفقه4</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="34" customHeight="1">
@@ -10880,25 +10757,25 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="B133" s="42" t="str">
-        <x:v>القرآن وعلومه</x:v>
+        <x:v>أصول الفقه</x:v>
       </x:c>
       <x:c r="C133" s="42" t="str">
-        <x:v>بكالوريوس</x:v>
+        <x:v>دكتوراه</x:v>
       </x:c>
       <x:c r="D133" s="42" t="str">
-        <x:v>قديمة</x:v>
+        <x:v>جديدة</x:v>
       </x:c>
       <x:c r="E133" s="43" t="n">
-        <x:v>39</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F133" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G133" s="43" t="str">
-        <x:v>2001205-2</x:v>
+        <x:v>2001901-2</x:v>
       </x:c>
       <x:c r="H133" s="42" t="str">
-        <x:v>الحديث (1)</x:v>
+        <x:v>دراسات مقاصدية</x:v>
       </x:c>
       <x:c r="I133" s="43" t="n">
         <x:v>2</x:v>
@@ -10910,14 +10787,14 @@
         <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L133" s="42" t="str">
-        <x:v>القرآن وعلومه 39.pdf</x:v>
+        <x:v>الدكتوراه في أصول الفقه.pdf</x:v>
       </x:c>
       <x:c r="M133" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N133" s="42" t="str"/>
+      <x:c r="N133" s="42"/>
       <x:c r="O133" s="42" t="str">
-        <x:v>2001205-2||الحديث1</x:v>
+        <x:v>2001901-2||دراساتمقاصدية</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="34" customHeight="1">
@@ -10925,28 +10802,28 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="B134" s="42" t="str">
-        <x:v>القرآن وعلومه</x:v>
+        <x:v>أصول الفقه</x:v>
       </x:c>
       <x:c r="C134" s="42" t="str">
-        <x:v>بكالوريوس</x:v>
+        <x:v>دكتوراه</x:v>
       </x:c>
       <x:c r="D134" s="42" t="str">
-        <x:v>قديمة</x:v>
+        <x:v>جديدة</x:v>
       </x:c>
       <x:c r="E134" s="43" t="n">
-        <x:v>39</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F134" s="43" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G134" s="43" t="str">
-        <x:v>2001209-2</x:v>
+        <x:v>2001902-3</x:v>
       </x:c>
       <x:c r="H134" s="42" t="str">
-        <x:v>الحديث (2)</x:v>
+        <x:v>دراسة تحليلية أصولية</x:v>
       </x:c>
       <x:c r="I134" s="43" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J134" s="42" t="str">
         <x:v>نظري</x:v>
@@ -10955,14 +10832,14 @@
         <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L134" s="42" t="str">
-        <x:v>القرآن وعلومه 39.pdf</x:v>
+        <x:v>الدكتوراه في أصول الفقه.pdf</x:v>
       </x:c>
       <x:c r="M134" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N134" s="42" t="str"/>
+      <x:c r="N134" s="42"/>
       <x:c r="O134" s="42" t="str">
-        <x:v>2001209-2||الحديث2</x:v>
+        <x:v>2001902-3||دراسةتحليليةاصولية</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="34" customHeight="1">
@@ -10970,28 +10847,28 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="B135" s="42" t="str">
-        <x:v>القرآن وعلومه</x:v>
+        <x:v>أصول الفقه</x:v>
       </x:c>
       <x:c r="C135" s="42" t="str">
-        <x:v>بكالوريوس</x:v>
+        <x:v>دكتوراه</x:v>
       </x:c>
       <x:c r="D135" s="42" t="str">
-        <x:v>قديمة</x:v>
+        <x:v>جديدة</x:v>
       </x:c>
       <x:c r="E135" s="43" t="n">
-        <x:v>39</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F135" s="43" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G135" s="43" t="str">
+        <x:v>2001903-4</x:v>
+      </x:c>
+      <x:c r="H135" s="42" t="str">
+        <x:v>الاجتهاد الاستدلالي والفتوى</x:v>
+      </x:c>
+      <x:c r="I135" s="43" t="n">
         <x:v>4</x:v>
-      </x:c>
-      <x:c r="G135" s="43" t="str">
-        <x:v>2001322-2</x:v>
-      </x:c>
-      <x:c r="H135" s="42" t="str">
-        <x:v>الفقه (2)</x:v>
-      </x:c>
-      <x:c r="I135" s="43" t="n">
-        <x:v>2</x:v>
       </x:c>
       <x:c r="J135" s="42" t="str">
         <x:v>نظري</x:v>
@@ -11000,14 +10877,14 @@
         <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L135" s="42" t="str">
-        <x:v>القرآن وعلومه 39.pdf</x:v>
+        <x:v>الدكتوراه في أصول الفقه.pdf</x:v>
       </x:c>
       <x:c r="M135" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N135" s="42" t="str"/>
+      <x:c r="N135" s="42"/>
       <x:c r="O135" s="42" t="str">
-        <x:v>2001322-2||الفقه2</x:v>
+        <x:v>2001903-4||الاجتهادالاستدلاليوالفتوي</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="34" customHeight="1">
@@ -11015,25 +10892,25 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="B136" s="42" t="str">
-        <x:v>القرآن وعلومه</x:v>
+        <x:v>الفقه</x:v>
       </x:c>
       <x:c r="C136" s="42" t="str">
-        <x:v>بكالوريوس</x:v>
+        <x:v>ماجستير</x:v>
       </x:c>
       <x:c r="D136" s="42" t="str">
-        <x:v>قديمة</x:v>
+        <x:v>جديدة</x:v>
       </x:c>
       <x:c r="E136" s="43" t="n">
-        <x:v>39</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F136" s="43" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G136" s="43" t="str">
-        <x:v>2003220-2</x:v>
+        <x:v>2003880-2</x:v>
       </x:c>
       <x:c r="H136" s="42" t="str">
-        <x:v>المدخل لدراسة الأنظمة</x:v>
+        <x:v>الأنظمة العدلية في السعودية</x:v>
       </x:c>
       <x:c r="I136" s="43" t="n">
         <x:v>2</x:v>
@@ -11045,420 +10922,168 @@
         <x:v>إجبارية القسم</x:v>
       </x:c>
       <x:c r="L136" s="42" t="str">
-        <x:v>القرآن وعلومه 39.pdf</x:v>
+        <x:v>الماجستير في الفقه.pdf</x:v>
       </x:c>
       <x:c r="M136" s="42" t="str">
         <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
       </x:c>
-      <x:c r="N136" s="42" t="str"/>
+      <x:c r="N136" s="42"/>
       <x:c r="O136" s="42" t="str">
-        <x:v>2003220-2||المدخللدراسةالانظمة</x:v>
+        <x:v>2003880-2||الانظمةالعدليةفيالسعودية</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="34" customHeight="1">
-      <x:c r="A137" s="33" t="n">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="B137" s="42" t="str">
-        <x:v>القرآن وعلومه</x:v>
-      </x:c>
-      <x:c r="C137" s="42" t="str">
-        <x:v>بكالوريوس</x:v>
-      </x:c>
-      <x:c r="D137" s="42" t="str">
-        <x:v>قديمة</x:v>
-      </x:c>
-      <x:c r="E137" s="43" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F137" s="43" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G137" s="43" t="str">
-        <x:v>2001113-2</x:v>
-      </x:c>
-      <x:c r="H137" s="42" t="str">
-        <x:v>أصول الفقه (1)</x:v>
-      </x:c>
-      <x:c r="I137" s="43" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J137" s="42" t="str">
-        <x:v>نظري</x:v>
-      </x:c>
-      <x:c r="K137" s="42" t="str">
-        <x:v>إجبارية القسم</x:v>
-      </x:c>
-      <x:c r="L137" s="42" t="str">
-        <x:v>القرآن وعلومه 39.pdf</x:v>
-      </x:c>
-      <x:c r="M137" s="42" t="str">
-        <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
-      </x:c>
-      <x:c r="N137" s="42" t="str"/>
-      <x:c r="O137" s="42" t="str">
-        <x:v>2001113-2||اصولالفقه1</x:v>
-      </x:c>
+      <x:c r="A137" s="33"/>
+      <x:c r="B137" s="42"/>
+      <x:c r="C137" s="42"/>
+      <x:c r="D137" s="42"/>
+      <x:c r="E137" s="43"/>
+      <x:c r="F137" s="43"/>
+      <x:c r="G137" s="43"/>
+      <x:c r="H137" s="42"/>
+      <x:c r="I137" s="43"/>
+      <x:c r="J137" s="42"/>
+      <x:c r="K137" s="42"/>
+      <x:c r="L137" s="42"/>
+      <x:c r="M137" s="42"/>
+      <x:c r="N137" s="42"/>
+      <x:c r="O137" s="42"/>
     </x:row>
     <x:row r="138" ht="34" customHeight="1">
-      <x:c r="A138" s="33" t="n">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="B138" s="42" t="str">
-        <x:v>القرآن وعلومه</x:v>
-      </x:c>
-      <x:c r="C138" s="42" t="str">
-        <x:v>بكالوريوس</x:v>
-      </x:c>
-      <x:c r="D138" s="42" t="str">
-        <x:v>قديمة</x:v>
-      </x:c>
-      <x:c r="E138" s="43" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F138" s="43" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G138" s="43" t="str">
-        <x:v>2001317-2</x:v>
-      </x:c>
-      <x:c r="H138" s="42" t="str">
-        <x:v>الفقه (3)</x:v>
-      </x:c>
-      <x:c r="I138" s="43" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J138" s="42" t="str">
-        <x:v>نظري</x:v>
-      </x:c>
-      <x:c r="K138" s="42" t="str">
-        <x:v>إجبارية القسم</x:v>
-      </x:c>
-      <x:c r="L138" s="42" t="str">
-        <x:v>القرآن وعلومه 39.pdf</x:v>
-      </x:c>
-      <x:c r="M138" s="42" t="str">
-        <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
-      </x:c>
-      <x:c r="N138" s="42" t="str"/>
-      <x:c r="O138" s="42" t="str">
-        <x:v>2001317-2||الفقه3</x:v>
-      </x:c>
+      <x:c r="A138" s="33"/>
+      <x:c r="B138" s="42"/>
+      <x:c r="C138" s="42"/>
+      <x:c r="D138" s="42"/>
+      <x:c r="E138" s="43"/>
+      <x:c r="F138" s="43"/>
+      <x:c r="G138" s="43"/>
+      <x:c r="H138" s="42"/>
+      <x:c r="I138" s="43"/>
+      <x:c r="J138" s="42"/>
+      <x:c r="K138" s="42"/>
+      <x:c r="L138" s="42"/>
+      <x:c r="M138" s="42"/>
+      <x:c r="N138" s="42"/>
+      <x:c r="O138" s="42"/>
     </x:row>
     <x:row r="139" ht="34" customHeight="1">
-      <x:c r="A139" s="33" t="n">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="B139" s="42" t="str">
-        <x:v>القرآن وعلومه</x:v>
-      </x:c>
-      <x:c r="C139" s="42" t="str">
-        <x:v>بكالوريوس</x:v>
-      </x:c>
-      <x:c r="D139" s="42" t="str">
-        <x:v>قديمة</x:v>
-      </x:c>
-      <x:c r="E139" s="43" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F139" s="43" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G139" s="43" t="str">
-        <x:v>2001320-2</x:v>
-      </x:c>
-      <x:c r="H139" s="42" t="str">
-        <x:v>الحديث (3)</x:v>
-      </x:c>
-      <x:c r="I139" s="43" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J139" s="42" t="str">
-        <x:v>نظري</x:v>
-      </x:c>
-      <x:c r="K139" s="42" t="str">
-        <x:v>إجبارية القسم</x:v>
-      </x:c>
-      <x:c r="L139" s="42" t="str">
-        <x:v>القرآن وعلومه 39.pdf</x:v>
-      </x:c>
-      <x:c r="M139" s="42" t="str">
-        <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
-      </x:c>
-      <x:c r="N139" s="42" t="str"/>
-      <x:c r="O139" s="42" t="str">
-        <x:v>2001320-2||الحديث3</x:v>
-      </x:c>
+      <x:c r="A139" s="33"/>
+      <x:c r="B139" s="42"/>
+      <x:c r="C139" s="42"/>
+      <x:c r="D139" s="42"/>
+      <x:c r="E139" s="43"/>
+      <x:c r="F139" s="43"/>
+      <x:c r="G139" s="43"/>
+      <x:c r="H139" s="42"/>
+      <x:c r="I139" s="43"/>
+      <x:c r="J139" s="42"/>
+      <x:c r="K139" s="42"/>
+      <x:c r="L139" s="42"/>
+      <x:c r="M139" s="42"/>
+      <x:c r="N139" s="42"/>
+      <x:c r="O139" s="42"/>
     </x:row>
     <x:row r="140" ht="34" customHeight="1">
-      <x:c r="A140" s="33" t="n">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="B140" s="42" t="str">
-        <x:v>القرآن وعلومه</x:v>
-      </x:c>
-      <x:c r="C140" s="42" t="str">
-        <x:v>بكالوريوس</x:v>
-      </x:c>
-      <x:c r="D140" s="42" t="str">
-        <x:v>قديمة</x:v>
-      </x:c>
-      <x:c r="E140" s="43" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F140" s="43" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G140" s="43" t="str">
-        <x:v>2001330-2</x:v>
-      </x:c>
-      <x:c r="H140" s="42" t="str">
-        <x:v>أصول الفقه (2)</x:v>
-      </x:c>
-      <x:c r="I140" s="43" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J140" s="42" t="str">
-        <x:v>نظري</x:v>
-      </x:c>
-      <x:c r="K140" s="42" t="str">
-        <x:v>إجبارية القسم</x:v>
-      </x:c>
-      <x:c r="L140" s="42" t="str">
-        <x:v>القرآن وعلومه 39.pdf</x:v>
-      </x:c>
-      <x:c r="M140" s="42" t="str">
-        <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
-      </x:c>
-      <x:c r="N140" s="42" t="str"/>
-      <x:c r="O140" s="42" t="str">
-        <x:v>2001330-2||اصولالفقه2</x:v>
-      </x:c>
+      <x:c r="A140" s="33"/>
+      <x:c r="B140" s="42"/>
+      <x:c r="C140" s="42"/>
+      <x:c r="D140" s="42"/>
+      <x:c r="E140" s="43"/>
+      <x:c r="F140" s="43"/>
+      <x:c r="G140" s="43"/>
+      <x:c r="H140" s="42"/>
+      <x:c r="I140" s="43"/>
+      <x:c r="J140" s="42"/>
+      <x:c r="K140" s="42"/>
+      <x:c r="L140" s="42"/>
+      <x:c r="M140" s="42"/>
+      <x:c r="N140" s="42"/>
+      <x:c r="O140" s="42"/>
     </x:row>
     <x:row r="141" ht="34" customHeight="1">
-      <x:c r="A141" s="33" t="n">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="B141" s="42" t="str">
-        <x:v>القرآن وعلومه</x:v>
-      </x:c>
-      <x:c r="C141" s="42" t="str">
-        <x:v>بكالوريوس</x:v>
-      </x:c>
-      <x:c r="D141" s="42" t="str">
-        <x:v>قديمة</x:v>
-      </x:c>
-      <x:c r="E141" s="43" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F141" s="43" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G141" s="43" t="str">
-        <x:v>2001424-2</x:v>
-      </x:c>
-      <x:c r="H141" s="42" t="str">
-        <x:v>الفقه (4)</x:v>
-      </x:c>
-      <x:c r="I141" s="43" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J141" s="42" t="str">
-        <x:v>نظري</x:v>
-      </x:c>
-      <x:c r="K141" s="42" t="str">
-        <x:v>إجبارية القسم</x:v>
-      </x:c>
-      <x:c r="L141" s="42" t="str">
-        <x:v>القرآن وعلومه 39.pdf</x:v>
-      </x:c>
-      <x:c r="M141" s="42" t="str">
-        <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
-      </x:c>
-      <x:c r="N141" s="42" t="str"/>
-      <x:c r="O141" s="42" t="str">
-        <x:v>2001424-2||الفقه4</x:v>
-      </x:c>
+      <x:c r="A141" s="33"/>
+      <x:c r="B141" s="42"/>
+      <x:c r="C141" s="42"/>
+      <x:c r="D141" s="42"/>
+      <x:c r="E141" s="43"/>
+      <x:c r="F141" s="43"/>
+      <x:c r="G141" s="43"/>
+      <x:c r="H141" s="42"/>
+      <x:c r="I141" s="43"/>
+      <x:c r="J141" s="42"/>
+      <x:c r="K141" s="42"/>
+      <x:c r="L141" s="42"/>
+      <x:c r="M141" s="42"/>
+      <x:c r="N141" s="42"/>
+      <x:c r="O141" s="42"/>
     </x:row>
     <x:row r="142" ht="34" customHeight="1">
-      <x:c r="A142" s="33" t="n">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="B142" s="42" t="str">
-        <x:v>أصول الفقه</x:v>
-      </x:c>
-      <x:c r="C142" s="42" t="str">
-        <x:v>دكتوراه</x:v>
-      </x:c>
-      <x:c r="D142" s="42" t="str">
-        <x:v>جديدة</x:v>
-      </x:c>
-      <x:c r="E142" s="43" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F142" s="43" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G142" s="43" t="str">
-        <x:v>2001901-2</x:v>
-      </x:c>
-      <x:c r="H142" s="42" t="str">
-        <x:v>دراسات مقاصدية</x:v>
-      </x:c>
-      <x:c r="I142" s="43" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J142" s="42" t="str">
-        <x:v>نظري</x:v>
-      </x:c>
-      <x:c r="K142" s="42" t="str">
-        <x:v>إجبارية القسم</x:v>
-      </x:c>
-      <x:c r="L142" s="42" t="str">
-        <x:v>الدكتوراه في أصول الفقه.pdf</x:v>
-      </x:c>
-      <x:c r="M142" s="42" t="str">
-        <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
-      </x:c>
-      <x:c r="N142" s="42" t="str"/>
-      <x:c r="O142" s="42" t="str">
-        <x:v>2001901-2||دراساتمقاصدية</x:v>
-      </x:c>
+      <x:c r="A142" s="33"/>
+      <x:c r="B142" s="42"/>
+      <x:c r="C142" s="42"/>
+      <x:c r="D142" s="42"/>
+      <x:c r="E142" s="43"/>
+      <x:c r="F142" s="43"/>
+      <x:c r="G142" s="43"/>
+      <x:c r="H142" s="42"/>
+      <x:c r="I142" s="43"/>
+      <x:c r="J142" s="42"/>
+      <x:c r="K142" s="42"/>
+      <x:c r="L142" s="42"/>
+      <x:c r="M142" s="42"/>
+      <x:c r="N142" s="42"/>
+      <x:c r="O142" s="42"/>
     </x:row>
     <x:row r="143" ht="34" customHeight="1">
-      <x:c r="A143" s="33" t="n">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="B143" s="42" t="str">
-        <x:v>أصول الفقه</x:v>
-      </x:c>
-      <x:c r="C143" s="42" t="str">
-        <x:v>دكتوراه</x:v>
-      </x:c>
-      <x:c r="D143" s="42" t="str">
-        <x:v>جديدة</x:v>
-      </x:c>
-      <x:c r="E143" s="43" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F143" s="43" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G143" s="43" t="str">
-        <x:v>2001902-3</x:v>
-      </x:c>
-      <x:c r="H143" s="42" t="str">
-        <x:v>دراسة تحليلية أصولية</x:v>
-      </x:c>
-      <x:c r="I143" s="43" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="J143" s="42" t="str">
-        <x:v>نظري</x:v>
-      </x:c>
-      <x:c r="K143" s="42" t="str">
-        <x:v>إجبارية القسم</x:v>
-      </x:c>
-      <x:c r="L143" s="42" t="str">
-        <x:v>الدكتوراه في أصول الفقه.pdf</x:v>
-      </x:c>
-      <x:c r="M143" s="42" t="str">
-        <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
-      </x:c>
-      <x:c r="N143" s="42" t="str"/>
-      <x:c r="O143" s="42" t="str">
-        <x:v>2001902-3||دراسةتحليليةاصولية</x:v>
-      </x:c>
+      <x:c r="A143" s="33"/>
+      <x:c r="B143" s="42"/>
+      <x:c r="C143" s="42"/>
+      <x:c r="D143" s="42"/>
+      <x:c r="E143" s="43"/>
+      <x:c r="F143" s="43"/>
+      <x:c r="G143" s="43"/>
+      <x:c r="H143" s="42"/>
+      <x:c r="I143" s="43"/>
+      <x:c r="J143" s="42"/>
+      <x:c r="K143" s="42"/>
+      <x:c r="L143" s="42"/>
+      <x:c r="M143" s="42"/>
+      <x:c r="N143" s="42"/>
+      <x:c r="O143" s="42"/>
     </x:row>
     <x:row r="144" ht="34" customHeight="1">
-      <x:c r="A144" s="33" t="n">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="B144" s="42" t="str">
-        <x:v>أصول الفقه</x:v>
-      </x:c>
-      <x:c r="C144" s="42" t="str">
-        <x:v>دكتوراه</x:v>
-      </x:c>
-      <x:c r="D144" s="42" t="str">
-        <x:v>جديدة</x:v>
-      </x:c>
-      <x:c r="E144" s="43" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F144" s="43" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G144" s="43" t="str">
-        <x:v>2001903-4</x:v>
-      </x:c>
-      <x:c r="H144" s="42" t="str">
-        <x:v>الاجتهاد الاستدلالي والفتوى</x:v>
-      </x:c>
-      <x:c r="I144" s="43" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="J144" s="42" t="str">
-        <x:v>نظري</x:v>
-      </x:c>
-      <x:c r="K144" s="42" t="str">
-        <x:v>إجبارية القسم</x:v>
-      </x:c>
-      <x:c r="L144" s="42" t="str">
-        <x:v>الدكتوراه في أصول الفقه.pdf</x:v>
-      </x:c>
-      <x:c r="M144" s="42" t="str">
-        <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
-      </x:c>
-      <x:c r="N144" s="42" t="str"/>
-      <x:c r="O144" s="42" t="str">
-        <x:v>2001903-4||الاجتهادالاستدلاليوالفتوي</x:v>
-      </x:c>
+      <x:c r="A144" s="33"/>
+      <x:c r="B144" s="42"/>
+      <x:c r="C144" s="42"/>
+      <x:c r="D144" s="42"/>
+      <x:c r="E144" s="43"/>
+      <x:c r="F144" s="43"/>
+      <x:c r="G144" s="43"/>
+      <x:c r="H144" s="42"/>
+      <x:c r="I144" s="43"/>
+      <x:c r="J144" s="42"/>
+      <x:c r="K144" s="42"/>
+      <x:c r="L144" s="42"/>
+      <x:c r="M144" s="42"/>
+      <x:c r="N144" s="42"/>
+      <x:c r="O144" s="42"/>
     </x:row>
     <x:row r="145" ht="34" customHeight="1">
-      <x:c r="A145" s="33" t="n">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="B145" s="42" t="str">
-        <x:v>الفقه</x:v>
-      </x:c>
-      <x:c r="C145" s="42" t="str">
-        <x:v>ماجستير</x:v>
-      </x:c>
-      <x:c r="D145" s="42" t="str">
-        <x:v>جديدة</x:v>
-      </x:c>
-      <x:c r="E145" s="43" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F145" s="43" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G145" s="43" t="str">
-        <x:v>2003880-2</x:v>
-      </x:c>
-      <x:c r="H145" s="42" t="str">
-        <x:v>الأنظمة العدلية في السعودية</x:v>
-      </x:c>
-      <x:c r="I145" s="43" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J145" s="42" t="str">
-        <x:v>نظري</x:v>
-      </x:c>
-      <x:c r="K145" s="42" t="str">
-        <x:v>إجبارية القسم</x:v>
-      </x:c>
-      <x:c r="L145" s="42" t="str">
-        <x:v>الماجستير في الفقه.pdf</x:v>
-      </x:c>
-      <x:c r="M145" s="42" t="str">
-        <x:v>لا يوجد توصيف تحت الرمز في المستودع</x:v>
-      </x:c>
-      <x:c r="N145" s="42" t="str"/>
-      <x:c r="O145" s="42" t="str">
-        <x:v>2003880-2||الانظمةالعدليةفيالسعودية</x:v>
-      </x:c>
+      <x:c r="A145" s="33"/>
+      <x:c r="B145" s="42"/>
+      <x:c r="C145" s="42"/>
+      <x:c r="D145" s="42"/>
+      <x:c r="E145" s="43"/>
+      <x:c r="F145" s="43"/>
+      <x:c r="G145" s="43"/>
+      <x:c r="H145" s="42"/>
+      <x:c r="I145" s="43"/>
+      <x:c r="J145" s="42"/>
+      <x:c r="K145" s="42"/>
+      <x:c r="L145" s="42"/>
+      <x:c r="M145" s="42"/>
+      <x:c r="N145" s="42"/>
+      <x:c r="O145" s="42"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -11467,7 +11092,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re99a99b9a1eb4924"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb91c256e77a4ec1"/>
   </x:tableParts>
 </x:worksheet>
 </file>